--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129221374</v>
       </c>
       <c r="B3" t="n">
-        <v>96958</v>
+        <v>96960</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129221376</v>
       </c>
       <c r="B4" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129221368</v>
       </c>
       <c r="B7" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129221371</v>
       </c>
       <c r="B8" t="n">
-        <v>96958</v>
+        <v>96960</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>129221369</v>
       </c>
       <c r="B9" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129221372</v>
+        <v>129221374</v>
       </c>
       <c r="B2" t="n">
-        <v>43982</v>
+        <v>96960</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101735</v>
+        <v>2590</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317072</v>
+        <v>317070</v>
       </c>
       <c r="R2" t="n">
-        <v>6550991</v>
+        <v>6550980</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,21 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129221374</v>
+        <v>129221372</v>
       </c>
       <c r="B3" t="n">
-        <v>96960</v>
+        <v>43982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2590</v>
+        <v>101735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317070</v>
+        <v>317072</v>
       </c>
       <c r="R3" t="n">
-        <v>6550980</v>
+        <v>6550991</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -873,6 +858,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129221374</v>
+        <v>129221372</v>
       </c>
       <c r="B2" t="n">
-        <v>96960</v>
+        <v>43982</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2590</v>
+        <v>101735</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317070</v>
+        <v>317072</v>
       </c>
       <c r="R2" t="n">
-        <v>6550980</v>
+        <v>6550991</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -756,6 +761,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -772,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129221372</v>
+        <v>129221374</v>
       </c>
       <c r="B3" t="n">
-        <v>43982</v>
+        <v>96986</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101735</v>
+        <v>2590</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317072</v>
+        <v>317070</v>
       </c>
       <c r="R3" t="n">
-        <v>6550991</v>
+        <v>6550980</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -858,21 +873,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -892,7 +892,7 @@
         <v>129221376</v>
       </c>
       <c r="B4" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129221368</v>
       </c>
       <c r="B7" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129221371</v>
       </c>
       <c r="B8" t="n">
-        <v>96960</v>
+        <v>96986</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>129221369</v>
       </c>
       <c r="B9" t="n">
-        <v>93031</v>
+        <v>91592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>129221374</v>
       </c>
       <c r="B3" t="n">
-        <v>96986</v>
+        <v>96987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129221376</v>
       </c>
       <c r="B4" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129221368</v>
       </c>
       <c r="B7" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129221371</v>
       </c>
       <c r="B8" t="n">
-        <v>96986</v>
+        <v>96987</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>129221369</v>
       </c>
       <c r="B9" t="n">
-        <v>91592</v>
+        <v>91593</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129221372</v>
+        <v>129221374</v>
       </c>
       <c r="B2" t="n">
-        <v>43982</v>
+        <v>96988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101735</v>
+        <v>2590</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317072</v>
+        <v>317070</v>
       </c>
       <c r="R2" t="n">
-        <v>6550991</v>
+        <v>6550980</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,21 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129221374</v>
+        <v>129221372</v>
       </c>
       <c r="B3" t="n">
-        <v>96987</v>
+        <v>43982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2590</v>
+        <v>101735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317070</v>
+        <v>317072</v>
       </c>
       <c r="R3" t="n">
-        <v>6550980</v>
+        <v>6550991</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -873,6 +858,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -1320,7 +1320,7 @@
         <v>129221371</v>
       </c>
       <c r="B8" t="n">
-        <v>96987</v>
+        <v>96988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129221374</v>
       </c>
       <c r="B2" t="n">
-        <v>96988</v>
+        <v>96992</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129221376</v>
       </c>
       <c r="B4" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129221368</v>
       </c>
       <c r="B7" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129221371</v>
       </c>
       <c r="B8" t="n">
-        <v>96988</v>
+        <v>96992</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>129221369</v>
       </c>
       <c r="B9" t="n">
-        <v>91593</v>
+        <v>91596</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129221374</v>
+        <v>129221372</v>
       </c>
       <c r="B2" t="n">
-        <v>96992</v>
+        <v>43982</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2590</v>
+        <v>101735</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317070</v>
+        <v>317072</v>
       </c>
       <c r="R2" t="n">
-        <v>6550980</v>
+        <v>6550991</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -756,6 +761,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -772,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129221372</v>
+        <v>129221374</v>
       </c>
       <c r="B3" t="n">
-        <v>43982</v>
+        <v>96992</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101735</v>
+        <v>2590</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317072</v>
+        <v>317070</v>
       </c>
       <c r="R3" t="n">
-        <v>6550991</v>
+        <v>6550980</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -858,21 +873,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129221372</v>
+        <v>129221374</v>
       </c>
       <c r="B2" t="n">
-        <v>43982</v>
+        <v>96994</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101735</v>
+        <v>2590</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317072</v>
+        <v>317070</v>
       </c>
       <c r="R2" t="n">
-        <v>6550991</v>
+        <v>6550980</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,21 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129221374</v>
+        <v>129221372</v>
       </c>
       <c r="B3" t="n">
-        <v>96992</v>
+        <v>43982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2590</v>
+        <v>101735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317070</v>
+        <v>317072</v>
       </c>
       <c r="R3" t="n">
-        <v>6550980</v>
+        <v>6550991</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -873,6 +858,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -892,7 +892,7 @@
         <v>129221376</v>
       </c>
       <c r="B4" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129221368</v>
       </c>
       <c r="B7" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129221371</v>
       </c>
       <c r="B8" t="n">
-        <v>96992</v>
+        <v>96994</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>129221369</v>
       </c>
       <c r="B9" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129221374</v>
       </c>
       <c r="B2" t="n">
-        <v>96994</v>
+        <v>96998</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129221376</v>
       </c>
       <c r="B4" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129221368</v>
       </c>
       <c r="B7" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129221371</v>
       </c>
       <c r="B8" t="n">
-        <v>96994</v>
+        <v>96998</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>129221369</v>
       </c>
       <c r="B9" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129221374</v>
       </c>
       <c r="B2" t="n">
-        <v>96998</v>
+        <v>97006</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129221376</v>
       </c>
       <c r="B4" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129221368</v>
       </c>
       <c r="B7" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129221371</v>
       </c>
       <c r="B8" t="n">
-        <v>96998</v>
+        <v>97006</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>129221369</v>
       </c>
       <c r="B9" t="n">
-        <v>91602</v>
+        <v>91603</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129221374</v>
+        <v>129221372</v>
       </c>
       <c r="B2" t="n">
-        <v>97006</v>
+        <v>43982</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2590</v>
+        <v>101735</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317070</v>
+        <v>317072</v>
       </c>
       <c r="R2" t="n">
-        <v>6550980</v>
+        <v>6550991</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -756,6 +761,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -772,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129221372</v>
+        <v>129221374</v>
       </c>
       <c r="B3" t="n">
-        <v>43982</v>
+        <v>97006</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101735</v>
+        <v>2590</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317072</v>
+        <v>317070</v>
       </c>
       <c r="R3" t="n">
-        <v>6550991</v>
+        <v>6550980</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -858,21 +873,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129221376</v>
+        <v>129221370</v>
       </c>
       <c r="B4" t="n">
-        <v>92832</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317145</v>
+        <v>317034</v>
       </c>
       <c r="R4" t="n">
-        <v>6550981</v>
+        <v>6550962</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -970,6 +975,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -986,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129221370</v>
+        <v>129221376</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>92832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,39 +1017,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317034</v>
+        <v>317145</v>
       </c>
       <c r="R5" t="n">
-        <v>6550962</v>
+        <v>6550981</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1072,21 +1087,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129221372</v>
+        <v>129221374</v>
       </c>
       <c r="B2" t="n">
-        <v>43982</v>
+        <v>97009</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101735</v>
+        <v>2590</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317072</v>
+        <v>317070</v>
       </c>
       <c r="R2" t="n">
-        <v>6550991</v>
+        <v>6550980</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,21 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129221374</v>
+        <v>129221372</v>
       </c>
       <c r="B3" t="n">
-        <v>97006</v>
+        <v>43982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2590</v>
+        <v>101735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317070</v>
+        <v>317072</v>
       </c>
       <c r="R3" t="n">
-        <v>6550980</v>
+        <v>6550991</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -873,6 +858,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129221370</v>
+        <v>129221376</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>92835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317034</v>
+        <v>317145</v>
       </c>
       <c r="R4" t="n">
-        <v>6550962</v>
+        <v>6550981</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -975,21 +970,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1006,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129221376</v>
+        <v>129221370</v>
       </c>
       <c r="B5" t="n">
-        <v>92832</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,34 +997,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317145</v>
+        <v>317034</v>
       </c>
       <c r="R5" t="n">
-        <v>6550981</v>
+        <v>6550962</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1087,6 +1072,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1223,7 +1223,7 @@
         <v>129221368</v>
       </c>
       <c r="B7" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129221371</v>
       </c>
       <c r="B8" t="n">
-        <v>97006</v>
+        <v>97009</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>129221369</v>
       </c>
       <c r="B9" t="n">
-        <v>91603</v>
+        <v>91606</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1526,50 +1526,52 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129221378</v>
+        <v>129607034</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>92195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>5454</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norra Rävmarken, Dls</t>
+          <t>Hökelshöljen V., Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>317180</v>
+        <v>316863</v>
       </c>
       <c r="R10" t="n">
-        <v>6550867</v>
+        <v>6551063</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1596,12 +1598,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1610,9 +1612,15 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Bärljungtallskog.</t>
+        </is>
+      </c>
       <c r="AJ10" t="inlineStr">
         <is>
           <t>tall</t>
@@ -1625,21 +1633,1143 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129606816</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92036</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5467</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kådvaxskinn</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phlebia serialis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hökelshöljen S., Dls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>316887</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6551018</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog.</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129221378</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>317180</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6550867</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Anton Larsson</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Anton Larsson</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129605837</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91606</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>317508</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6550898</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Ljungbarrskog.</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129607900</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91726</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Pengehöljen O., Dls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>317270</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6550906</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Bärljungtallskog.</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129606260</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90935</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>317465</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6550940</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Bärljunggranskog.</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129606938</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92036</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5467</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kådvaxskinn</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phlebia serialis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Pengehöljen O., Dls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>317398</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6550916</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Bärljunggranskog.</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129607603</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78710</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>353</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Pengehöljen O., Dls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>317271</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6550912</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Bärljungtallskog.</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Rot # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129605988</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92036</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5467</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kådvaxskinn</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phlebia serialis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lögarehöljen S., Dls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>317301</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6551026</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Särskilt långa fruktkroppar på två lågor.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Mossegranskog m löv</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129607723</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78801</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Pengehöljen O., Dls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>317272</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6550913</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Bärljungtallskog.</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129221374</v>
+        <v>129221372</v>
       </c>
       <c r="B2" t="n">
-        <v>97009</v>
+        <v>43982</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2590</v>
+        <v>101735</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317070</v>
+        <v>317072</v>
       </c>
       <c r="R2" t="n">
-        <v>6550980</v>
+        <v>6550991</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -756,6 +761,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -772,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129221372</v>
+        <v>129221374</v>
       </c>
       <c r="B3" t="n">
-        <v>43982</v>
+        <v>97009</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101735</v>
+        <v>2590</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317072</v>
+        <v>317070</v>
       </c>
       <c r="R3" t="n">
-        <v>6550991</v>
+        <v>6550980</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -858,21 +873,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129221372</v>
+        <v>129221374</v>
       </c>
       <c r="B2" t="n">
-        <v>43982</v>
+        <v>97009</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101735</v>
+        <v>2590</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317072</v>
+        <v>317070</v>
       </c>
       <c r="R2" t="n">
-        <v>6550991</v>
+        <v>6550980</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -761,21 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129221374</v>
+        <v>129221372</v>
       </c>
       <c r="B3" t="n">
-        <v>97009</v>
+        <v>43982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2590</v>
+        <v>101735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317070</v>
+        <v>317072</v>
       </c>
       <c r="R3" t="n">
-        <v>6550980</v>
+        <v>6550991</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -873,6 +858,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2771,6 +2771,131 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129654925</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lögarehöljen S/O., Dls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>317454</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6550923</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Mosseblåbärgranskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Låga # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129221376</v>
+        <v>129221370</v>
       </c>
       <c r="B4" t="n">
-        <v>92835</v>
+        <v>8450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317145</v>
+        <v>317034</v>
       </c>
       <c r="R4" t="n">
-        <v>6550981</v>
+        <v>6550962</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -970,6 +975,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -986,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129221370</v>
+        <v>129221376</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>92835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,39 +1017,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317034</v>
+        <v>317145</v>
       </c>
       <c r="R5" t="n">
-        <v>6550962</v>
+        <v>6550981</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1072,21 +1087,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129221374</v>
       </c>
       <c r="B2" t="n">
-        <v>97009</v>
+        <v>97038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129221372</v>
       </c>
       <c r="B3" t="n">
-        <v>43982</v>
+        <v>43985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129221370</v>
+        <v>129221376</v>
       </c>
       <c r="B4" t="n">
-        <v>8450</v>
+        <v>92863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317034</v>
+        <v>317145</v>
       </c>
       <c r="R4" t="n">
-        <v>6550962</v>
+        <v>6550981</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -975,21 +970,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1006,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129221376</v>
+        <v>129221370</v>
       </c>
       <c r="B5" t="n">
-        <v>92835</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,34 +997,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317145</v>
+        <v>317034</v>
       </c>
       <c r="R5" t="n">
-        <v>6550981</v>
+        <v>6550962</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1087,6 +1072,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1223,7 +1223,7 @@
         <v>129221368</v>
       </c>
       <c r="B7" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>129221371</v>
       </c>
       <c r="B8" t="n">
-        <v>97009</v>
+        <v>97038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>129221369</v>
       </c>
       <c r="B9" t="n">
-        <v>91606</v>
+        <v>91634</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>129607034</v>
       </c>
       <c r="B10" t="n">
-        <v>92195</v>
+        <v>92223</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>129606816</v>
       </c>
       <c r="B11" t="n">
-        <v>92036</v>
+        <v>92064</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>129605837</v>
       </c>
       <c r="B13" t="n">
-        <v>91606</v>
+        <v>91634</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>129607900</v>
       </c>
       <c r="B14" t="n">
-        <v>91726</v>
+        <v>91754</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>129606260</v>
       </c>
       <c r="B15" t="n">
-        <v>90935</v>
+        <v>90963</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>129606938</v>
       </c>
       <c r="B16" t="n">
-        <v>92036</v>
+        <v>92064</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129607603</v>
       </c>
       <c r="B17" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129605988</v>
       </c>
       <c r="B18" t="n">
-        <v>92036</v>
+        <v>92064</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>129607723</v>
       </c>
       <c r="B19" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>129654925</v>
       </c>
       <c r="B20" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -1529,7 +1529,7 @@
         <v>129607034</v>
       </c>
       <c r="B10" t="n">
-        <v>92223</v>
+        <v>92229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>129606816</v>
       </c>
       <c r="B11" t="n">
-        <v>92064</v>
+        <v>92070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>129605837</v>
       </c>
       <c r="B13" t="n">
-        <v>91634</v>
+        <v>91640</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>129607900</v>
       </c>
       <c r="B14" t="n">
-        <v>91754</v>
+        <v>91760</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>129606260</v>
       </c>
       <c r="B15" t="n">
-        <v>90963</v>
+        <v>90969</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>129606938</v>
       </c>
       <c r="B16" t="n">
-        <v>92064</v>
+        <v>92070</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129607603</v>
       </c>
       <c r="B17" t="n">
-        <v>78736</v>
+        <v>78741</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129605988</v>
       </c>
       <c r="B18" t="n">
-        <v>92064</v>
+        <v>92070</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>129607723</v>
       </c>
       <c r="B19" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>129654925</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -1529,7 +1529,7 @@
         <v>129607034</v>
       </c>
       <c r="B10" t="n">
-        <v>92229</v>
+        <v>92230</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>129606816</v>
       </c>
       <c r="B11" t="n">
-        <v>92070</v>
+        <v>92071</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>129605837</v>
       </c>
       <c r="B13" t="n">
-        <v>91640</v>
+        <v>91641</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>129607900</v>
       </c>
       <c r="B14" t="n">
-        <v>91760</v>
+        <v>91761</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>129606260</v>
       </c>
       <c r="B15" t="n">
-        <v>90969</v>
+        <v>90970</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>129606938</v>
       </c>
       <c r="B16" t="n">
-        <v>92070</v>
+        <v>92071</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129607603</v>
       </c>
       <c r="B17" t="n">
-        <v>78741</v>
+        <v>78742</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129605988</v>
       </c>
       <c r="B18" t="n">
-        <v>92070</v>
+        <v>92071</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>129607723</v>
       </c>
       <c r="B19" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>129654925</v>
       </c>
       <c r="B20" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -1529,7 +1529,7 @@
         <v>129607034</v>
       </c>
       <c r="B10" t="n">
-        <v>92230</v>
+        <v>92235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>129606816</v>
       </c>
       <c r="B11" t="n">
-        <v>92071</v>
+        <v>92076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>129605837</v>
       </c>
       <c r="B13" t="n">
-        <v>91641</v>
+        <v>91646</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>129607900</v>
       </c>
       <c r="B14" t="n">
-        <v>91761</v>
+        <v>91766</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>129606260</v>
       </c>
       <c r="B15" t="n">
-        <v>90970</v>
+        <v>90975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>129606938</v>
       </c>
       <c r="B16" t="n">
-        <v>92071</v>
+        <v>92076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129607603</v>
       </c>
       <c r="B17" t="n">
-        <v>78742</v>
+        <v>78747</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>129605988</v>
       </c>
       <c r="B18" t="n">
-        <v>92071</v>
+        <v>92076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>129607723</v>
       </c>
       <c r="B19" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2393,10 +2393,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129607603</v>
+        <v>129605988</v>
       </c>
       <c r="B17" t="n">
-        <v>78747</v>
+        <v>92076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2404,41 +2404,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>5467</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Lögarehöljen S., Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>317271</v>
+        <v>317301</v>
       </c>
       <c r="R17" t="n">
-        <v>6550912</v>
+        <v>6551026</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2473,6 +2473,11 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Särskilt långa fruktkroppar på två lågor.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2485,7 +2490,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Bärljungtallskog.</t>
+          <t>Mossegranskog m löv</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2500,7 +2505,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Rot # Pinus sylvestris</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2518,10 +2523,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129605988</v>
+        <v>129607723</v>
       </c>
       <c r="B18" t="n">
-        <v>92076</v>
+        <v>78838</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2529,41 +2534,41 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5467</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lögarehöljen S., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>317301</v>
+        <v>317272</v>
       </c>
       <c r="R18" t="n">
-        <v>6551026</v>
+        <v>6550913</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2598,11 +2603,6 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Särskilt långa fruktkroppar på två lågor.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Mossegranskog m löv</t>
+          <t>Bärljungtallskog.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2648,10 +2648,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129607723</v>
+        <v>129654925</v>
       </c>
       <c r="B19" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2659,41 +2659,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Lögarehöljen S/O., Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>317272</v>
+        <v>317454</v>
       </c>
       <c r="R19" t="n">
-        <v>6550913</v>
+        <v>6550923</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2734,28 +2735,27 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Bärljungtallskog.</t>
+          <t>Mosseblåbärgranskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Låga # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129654925</v>
+        <v>129835851</v>
       </c>
       <c r="B20" t="n">
-        <v>57733</v>
+        <v>91614</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2784,42 +2784,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lögarehöljen S/O., Dls</t>
+          <t>Hökelshöljen S., Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>317454</v>
+        <v>317233</v>
       </c>
       <c r="R20" t="n">
-        <v>6550923</v>
+        <v>6550972</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2846,12 +2849,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,27 +2863,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Mosseblåbärgranskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Låga # Picea abies</t>
+          <t>Död ticka på död tall.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2895,6 +2889,2266 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129835373</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78747</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>353</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Pengehöljen O., Dls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>317330</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6550900</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Bærljungtallskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129835818</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Pengehöljen O., Dls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>317365</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6550833</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Dödt träd # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129835710</v>
+      </c>
+      <c r="B23" t="n">
+        <v>43991</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mattishöljen N/O., Dls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>317372</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6550741</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129835838</v>
+      </c>
+      <c r="B24" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hökelshöljen S., Dls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>317217</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6550953</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129835991</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91403</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6006</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Oljeporing</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Sistotrema alboluteum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Bourdot &amp; Galzin) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Pengehöljen O., Dls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>317371</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6550814</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129836196</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91835</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5260</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lateritticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Postia lateritia</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Renvall</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Pengehöljen O., Dls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>317366</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6550921</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129835737</v>
+      </c>
+      <c r="B27" t="n">
+        <v>43991</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Pengehöljen N/O., Dls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>317254</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6550959</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129835344</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78747</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>353</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Pengehöljen O., Dls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>317307</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6550845</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Bærljungtallskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129836143</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91835</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5260</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lateritticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Postia lateritia</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Renvall</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Pengehöljen O., Dls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>317353</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6550899</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129835752</v>
+      </c>
+      <c r="B30" t="n">
+        <v>43991</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lögarehöljen S., Dls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>317326</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6550956</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129835803</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Pengehöljen O., Dls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>317185</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6550868</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129835977</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91866</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>65</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Fläckporing</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Pengehöljen O., Dls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>317373</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6550816</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129607603</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78747</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>353</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Pengehöljen O., Dls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>317271</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6550912</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Bärljungtallskog.</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Rot # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129835810</v>
+      </c>
+      <c r="B34" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Pengehöljen O., Dls</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>317189</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6550878</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Dödt träd # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129835794</v>
+      </c>
+      <c r="B35" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Pengehöljen O., Dls</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>317350</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6550799</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Dödt träd # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129835724</v>
+      </c>
+      <c r="B36" t="n">
+        <v>43991</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Pengehöljen O., Dls</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>317204</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6550903</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129836131</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91835</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5260</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lateritticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Postia lateritia</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Renvall</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Pengehöljen O., Dls</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>317417</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6550843</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129835784</v>
+      </c>
+      <c r="B38" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Mattishöljen N/O., Dls</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>317351</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6550761</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Dödt träd # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -2773,10 +2773,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129835851</v>
+        <v>129835373</v>
       </c>
       <c r="B20" t="n">
-        <v>91614</v>
+        <v>78747</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2784,45 +2784,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hökelshöljen S., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>317233</v>
+        <v>317330</v>
       </c>
       <c r="R20" t="n">
-        <v>6550972</v>
+        <v>6550900</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2869,12 +2865,22 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Bærljungtallskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Död ticka på död tall.</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2892,10 +2898,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129835373</v>
+        <v>129835851</v>
       </c>
       <c r="B21" t="n">
-        <v>78747</v>
+        <v>91614</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,41 +2909,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Hökelshöljen S., Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>317330</v>
+        <v>317233</v>
       </c>
       <c r="R21" t="n">
-        <v>6550900</v>
+        <v>6550972</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2984,22 +2994,12 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Bærljungtallskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Död ticka på död tall.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3144,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129835710</v>
+        <v>129835838</v>
       </c>
       <c r="B23" t="n">
-        <v>43991</v>
+        <v>8439</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101735</v>
+        <v>106554</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3184,14 +3184,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mattishöljen N/O., Dls</t>
+          <t>Hökelshöljen S., Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>317372</v>
+        <v>317217</v>
       </c>
       <c r="R23" t="n">
-        <v>6550741</v>
+        <v>6550953</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3241,9 +3241,19 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3261,10 +3271,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129835838</v>
+        <v>129835710</v>
       </c>
       <c r="B24" t="n">
-        <v>8439</v>
+        <v>43991</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3272,21 +3282,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106554</v>
+        <v>101735</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3301,14 +3311,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hökelshöljen S., Dls</t>
+          <t>Mattishöljen N/O., Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>317217</v>
+        <v>317372</v>
       </c>
       <c r="R24" t="n">
-        <v>6550953</v>
+        <v>6550741</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3358,19 +3368,9 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Fnöskticka på björk</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3513,52 +3513,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129836196</v>
+        <v>129835737</v>
       </c>
       <c r="B26" t="n">
-        <v>91835</v>
+        <v>43991</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5260</v>
+        <v>101735</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Pengehöljen N/O., Dls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>317366</v>
+        <v>317254</v>
       </c>
       <c r="R26" t="n">
-        <v>6550921</v>
+        <v>6550959</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3610,17 +3612,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3638,54 +3640,52 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129835737</v>
+        <v>129836196</v>
       </c>
       <c r="B27" t="n">
-        <v>43991</v>
+        <v>91835</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101735</v>
+        <v>5260</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pengehöljen N/O., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>317254</v>
+        <v>317366</v>
       </c>
       <c r="R27" t="n">
-        <v>6550959</v>
+        <v>6550921</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3737,17 +3737,17 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk # Fomes fomentarius</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -1529,7 +1529,7 @@
         <v>129607034</v>
       </c>
       <c r="B10" t="n">
-        <v>92235</v>
+        <v>92239</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>129606816</v>
       </c>
       <c r="B11" t="n">
-        <v>92076</v>
+        <v>92080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>129605837</v>
       </c>
       <c r="B13" t="n">
-        <v>91646</v>
+        <v>91650</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>129607900</v>
       </c>
       <c r="B14" t="n">
-        <v>91766</v>
+        <v>91770</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>129606260</v>
       </c>
       <c r="B15" t="n">
-        <v>90975</v>
+        <v>90979</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>129606938</v>
       </c>
       <c r="B16" t="n">
-        <v>92076</v>
+        <v>92080</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129605988</v>
       </c>
       <c r="B17" t="n">
-        <v>92076</v>
+        <v>92080</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2773,10 +2773,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129835373</v>
+        <v>129835851</v>
       </c>
       <c r="B20" t="n">
-        <v>78747</v>
+        <v>91618</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2784,41 +2784,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Hökelshöljen S., Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>317330</v>
+        <v>317233</v>
       </c>
       <c r="R20" t="n">
-        <v>6550900</v>
+        <v>6550972</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2865,22 +2869,12 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Bærljungtallskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Död ticka på död tall.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2898,10 +2892,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129835851</v>
+        <v>129835373</v>
       </c>
       <c r="B21" t="n">
-        <v>91614</v>
+        <v>78747</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2909,45 +2903,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hökelshöljen S., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>317233</v>
+        <v>317330</v>
       </c>
       <c r="R21" t="n">
-        <v>6550972</v>
+        <v>6550900</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2994,12 +2984,22 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Bærljungtallskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Död ticka på död tall.</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3144,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129835838</v>
+        <v>129835710</v>
       </c>
       <c r="B23" t="n">
-        <v>8439</v>
+        <v>43991</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106554</v>
+        <v>101735</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3184,14 +3184,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hökelshöljen S., Dls</t>
+          <t>Mattishöljen N/O., Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>317217</v>
+        <v>317372</v>
       </c>
       <c r="R23" t="n">
-        <v>6550953</v>
+        <v>6550741</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3241,19 +3241,9 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Fnöskticka på björk</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3271,10 +3261,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129835710</v>
+        <v>129835838</v>
       </c>
       <c r="B24" t="n">
-        <v>43991</v>
+        <v>8439</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3282,21 +3272,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>101735</v>
+        <v>106554</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3311,14 +3301,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mattishöljen N/O., Dls</t>
+          <t>Hökelshöljen S., Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>317372</v>
+        <v>317217</v>
       </c>
       <c r="R24" t="n">
-        <v>6550741</v>
+        <v>6550953</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3368,9 +3358,19 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3391,7 +3391,7 @@
         <v>129835991</v>
       </c>
       <c r="B25" t="n">
-        <v>91403</v>
+        <v>91407</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3640,38 +3640,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129836196</v>
+        <v>129835344</v>
       </c>
       <c r="B27" t="n">
-        <v>91835</v>
+        <v>78747</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5260</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>317366</v>
+        <v>317307</v>
       </c>
       <c r="R27" t="n">
-        <v>6550921</v>
+        <v>6550845</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Bærljungtallskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -3765,38 +3765,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129835344</v>
+        <v>129836196</v>
       </c>
       <c r="B28" t="n">
-        <v>78747</v>
+        <v>91839</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>5260</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>317307</v>
+        <v>317366</v>
       </c>
       <c r="R28" t="n">
-        <v>6550845</v>
+        <v>6550921</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Bærljungtallskog</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -3893,7 +3893,7 @@
         <v>129836143</v>
       </c>
       <c r="B29" t="n">
-        <v>91835</v>
+        <v>91839</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4015,54 +4015,52 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129835752</v>
+        <v>129835977</v>
       </c>
       <c r="B30" t="n">
-        <v>43991</v>
+        <v>91870</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>101735</v>
+        <v>65</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lögarehöljen S., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>317326</v>
+        <v>317373</v>
       </c>
       <c r="R30" t="n">
-        <v>6550956</v>
+        <v>6550816</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4114,17 +4112,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk # Fomes fomentarius</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4142,10 +4140,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129835803</v>
+        <v>129835752</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>43991</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4153,21 +4151,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>101735</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4182,14 +4180,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Lögarehöljen S., Dls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>317185</v>
+        <v>317326</v>
       </c>
       <c r="R31" t="n">
-        <v>6550868</v>
+        <v>6550956</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4241,17 +4239,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4269,41 +4267,43 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129835977</v>
+        <v>129835803</v>
       </c>
       <c r="B32" t="n">
-        <v>91866</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>65</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>317373</v>
+        <v>317185</v>
       </c>
       <c r="R32" t="n">
-        <v>6550816</v>
+        <v>6550868</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4394,41 +4394,43 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129607603</v>
+        <v>129835810</v>
       </c>
       <c r="B33" t="n">
-        <v>78747</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4436,10 +4438,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>317271</v>
+        <v>317189</v>
       </c>
       <c r="R33" t="n">
-        <v>6550912</v>
+        <v>6550878</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4466,12 +4468,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4486,7 +4488,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Bärljungtallskog.</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4501,7 +4503,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Rot # Pinus sylvestris</t>
+          <t>Dödt träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4519,7 +4521,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129835810</v>
+        <v>129835794</v>
       </c>
       <c r="B34" t="n">
         <v>8450</v>
@@ -4563,10 +4565,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>317189</v>
+        <v>317350</v>
       </c>
       <c r="R34" t="n">
-        <v>6550878</v>
+        <v>6550799</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4646,10 +4648,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129835794</v>
+        <v>129835724</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>43991</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4657,21 +4659,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>101735</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4690,10 +4692,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>317350</v>
+        <v>317204</v>
       </c>
       <c r="R35" t="n">
-        <v>6550799</v>
+        <v>6550903</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4745,17 +4747,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Dödt träd # Pinus sylvestris</t>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4773,43 +4775,41 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129835724</v>
+        <v>129836131</v>
       </c>
       <c r="B36" t="n">
-        <v>43991</v>
+        <v>91839</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>101735</v>
+        <v>5260</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4817,10 +4817,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>317204</v>
+        <v>317417</v>
       </c>
       <c r="R36" t="n">
-        <v>6550903</v>
+        <v>6550843</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4872,17 +4872,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk # Fomes fomentarius</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4900,52 +4900,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129836131</v>
+        <v>129835784</v>
       </c>
       <c r="B37" t="n">
-        <v>91835</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5260</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Mattishöljen N/O., Dls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>317417</v>
+        <v>317351</v>
       </c>
       <c r="R37" t="n">
-        <v>6550843</v>
+        <v>6550761</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5007,7 +5009,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Dödt träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5025,54 +5027,52 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129835784</v>
+        <v>129607603</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>78747</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mattishöljen N/O., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>317351</v>
+        <v>317271</v>
       </c>
       <c r="R38" t="n">
-        <v>6550761</v>
+        <v>6550912</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5099,12 +5099,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Bärljungtallskog.</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Dödt träd # Pinus sylvestris</t>
+          <t>Rot # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -1529,7 +1529,7 @@
         <v>129607034</v>
       </c>
       <c r="B10" t="n">
-        <v>92239</v>
+        <v>92241</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>129606816</v>
       </c>
       <c r="B11" t="n">
-        <v>92080</v>
+        <v>92082</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>129605837</v>
       </c>
       <c r="B13" t="n">
-        <v>91650</v>
+        <v>91652</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>129607900</v>
       </c>
       <c r="B14" t="n">
-        <v>91770</v>
+        <v>91772</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>129606260</v>
       </c>
       <c r="B15" t="n">
-        <v>90979</v>
+        <v>90981</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>129606938</v>
       </c>
       <c r="B16" t="n">
-        <v>92080</v>
+        <v>92082</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129605988</v>
       </c>
       <c r="B17" t="n">
-        <v>92080</v>
+        <v>92082</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2773,10 +2773,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129835851</v>
+        <v>129835373</v>
       </c>
       <c r="B20" t="n">
-        <v>91618</v>
+        <v>78747</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2784,45 +2784,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hökelshöljen S., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>317233</v>
+        <v>317330</v>
       </c>
       <c r="R20" t="n">
-        <v>6550972</v>
+        <v>6550900</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2869,12 +2865,22 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Bærljungtallskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Död ticka på död tall.</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2892,10 +2898,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129835373</v>
+        <v>129835851</v>
       </c>
       <c r="B21" t="n">
-        <v>78747</v>
+        <v>91620</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,41 +2909,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Hökelshöljen S., Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>317330</v>
+        <v>317233</v>
       </c>
       <c r="R21" t="n">
-        <v>6550900</v>
+        <v>6550972</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2984,22 +2994,12 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Bærljungtallskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Död ticka på död tall.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3144,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129835710</v>
+        <v>129835838</v>
       </c>
       <c r="B23" t="n">
-        <v>43991</v>
+        <v>8439</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101735</v>
+        <v>106554</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3184,14 +3184,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mattishöljen N/O., Dls</t>
+          <t>Hökelshöljen S., Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>317372</v>
+        <v>317217</v>
       </c>
       <c r="R23" t="n">
-        <v>6550741</v>
+        <v>6550953</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3241,9 +3241,19 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3261,10 +3271,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129835838</v>
+        <v>129835710</v>
       </c>
       <c r="B24" t="n">
-        <v>8439</v>
+        <v>43991</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3272,21 +3282,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106554</v>
+        <v>101735</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3301,14 +3311,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hökelshöljen S., Dls</t>
+          <t>Mattishöljen N/O., Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>317217</v>
+        <v>317372</v>
       </c>
       <c r="R24" t="n">
-        <v>6550953</v>
+        <v>6550741</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3358,19 +3368,9 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Fnöskticka på björk</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3391,7 +3391,7 @@
         <v>129835991</v>
       </c>
       <c r="B25" t="n">
-        <v>91407</v>
+        <v>91409</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3513,54 +3513,52 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129835737</v>
+        <v>129836196</v>
       </c>
       <c r="B26" t="n">
-        <v>43991</v>
+        <v>91841</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>101735</v>
+        <v>5260</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pengehöljen N/O., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>317254</v>
+        <v>317366</v>
       </c>
       <c r="R26" t="n">
-        <v>6550959</v>
+        <v>6550921</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3612,17 +3610,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk # Fomes fomentarius</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3765,52 +3763,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129836196</v>
+        <v>129835737</v>
       </c>
       <c r="B28" t="n">
-        <v>91839</v>
+        <v>43991</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5260</v>
+        <v>101735</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Pengehöljen N/O., Dls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>317366</v>
+        <v>317254</v>
       </c>
       <c r="R28" t="n">
-        <v>6550921</v>
+        <v>6550959</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3862,17 +3862,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3893,7 +3893,7 @@
         <v>129836143</v>
       </c>
       <c r="B29" t="n">
-        <v>91839</v>
+        <v>91841</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>129835977</v>
       </c>
       <c r="B30" t="n">
-        <v>91870</v>
+        <v>91872</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4140,10 +4140,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129835752</v>
+        <v>129835803</v>
       </c>
       <c r="B31" t="n">
-        <v>43991</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4151,21 +4151,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>101735</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4180,14 +4180,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lögarehöljen S., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>317326</v>
+        <v>317185</v>
       </c>
       <c r="R31" t="n">
-        <v>6550956</v>
+        <v>6550868</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4239,17 +4239,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk # Fomes fomentarius</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4267,10 +4267,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129835803</v>
+        <v>129835752</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>43991</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4278,21 +4278,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>101735</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4307,14 +4307,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Lögarehöljen S., Dls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>317185</v>
+        <v>317326</v>
       </c>
       <c r="R32" t="n">
-        <v>6550868</v>
+        <v>6550956</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4366,17 +4366,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4778,7 +4778,7 @@
         <v>129836131</v>
       </c>
       <c r="B36" t="n">
-        <v>91839</v>
+        <v>91841</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3144,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129835838</v>
+        <v>129835710</v>
       </c>
       <c r="B23" t="n">
-        <v>8439</v>
+        <v>43991</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106554</v>
+        <v>101735</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3184,14 +3184,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hökelshöljen S., Dls</t>
+          <t>Mattishöljen N/O., Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>317217</v>
+        <v>317372</v>
       </c>
       <c r="R23" t="n">
-        <v>6550953</v>
+        <v>6550741</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3241,19 +3241,9 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Fnöskticka på björk</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3271,10 +3261,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129835710</v>
+        <v>129835838</v>
       </c>
       <c r="B24" t="n">
-        <v>43991</v>
+        <v>8439</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3282,21 +3272,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>101735</v>
+        <v>106554</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3311,14 +3301,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mattishöljen N/O., Dls</t>
+          <t>Hökelshöljen S., Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>317372</v>
+        <v>317217</v>
       </c>
       <c r="R24" t="n">
-        <v>6550741</v>
+        <v>6550953</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3368,9 +3358,19 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3513,38 +3513,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129836196</v>
+        <v>129835344</v>
       </c>
       <c r="B26" t="n">
-        <v>91841</v>
+        <v>78747</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5260</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -3555,10 +3555,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>317366</v>
+        <v>317307</v>
       </c>
       <c r="R26" t="n">
-        <v>6550921</v>
+        <v>6550845</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Bærljungtallskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3638,52 +3638,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129835344</v>
+        <v>129835737</v>
       </c>
       <c r="B27" t="n">
-        <v>78747</v>
+        <v>43991</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>101735</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Pengehöljen N/O., Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>317307</v>
+        <v>317254</v>
       </c>
       <c r="R27" t="n">
-        <v>6550845</v>
+        <v>6550959</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3730,22 +3732,22 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Bærljungtallskog</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3763,54 +3765,52 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129835737</v>
+        <v>129835977</v>
       </c>
       <c r="B28" t="n">
-        <v>43991</v>
+        <v>91872</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101735</v>
+        <v>65</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pengehöljen N/O., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>317254</v>
+        <v>317373</v>
       </c>
       <c r="R28" t="n">
-        <v>6550959</v>
+        <v>6550816</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3862,17 +3862,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk # Fomes fomentarius</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3890,52 +3890,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129836143</v>
+        <v>129835752</v>
       </c>
       <c r="B29" t="n">
-        <v>91841</v>
+        <v>43991</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5260</v>
+        <v>101735</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Lögarehöljen S., Dls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>317353</v>
+        <v>317326</v>
       </c>
       <c r="R29" t="n">
-        <v>6550899</v>
+        <v>6550956</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3987,17 +3989,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4015,41 +4017,43 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129835977</v>
+        <v>129835803</v>
       </c>
       <c r="B30" t="n">
-        <v>91872</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>65</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4057,10 +4061,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>317373</v>
+        <v>317185</v>
       </c>
       <c r="R30" t="n">
-        <v>6550816</v>
+        <v>6550868</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4140,7 +4144,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129835803</v>
+        <v>129835810</v>
       </c>
       <c r="B31" t="n">
         <v>8450</v>
@@ -4184,10 +4188,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>317185</v>
+        <v>317189</v>
       </c>
       <c r="R31" t="n">
-        <v>6550868</v>
+        <v>6550878</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4249,7 +4253,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Dödt träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4267,10 +4271,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129835752</v>
+        <v>129835794</v>
       </c>
       <c r="B32" t="n">
-        <v>43991</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4278,21 +4282,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>101735</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4307,14 +4311,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lögarehöljen S., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>317326</v>
+        <v>317350</v>
       </c>
       <c r="R32" t="n">
-        <v>6550956</v>
+        <v>6550799</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4366,17 +4370,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk # Fomes fomentarius</t>
+          <t>Dödt träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4394,10 +4398,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129835810</v>
+        <v>129835724</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>43991</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4405,21 +4409,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>101735</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4438,10 +4442,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>317189</v>
+        <v>317204</v>
       </c>
       <c r="R33" t="n">
-        <v>6550878</v>
+        <v>6550903</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4493,17 +4497,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Dödt träd # Pinus sylvestris</t>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4521,7 +4525,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129835794</v>
+        <v>129835784</v>
       </c>
       <c r="B34" t="n">
         <v>8450</v>
@@ -4561,14 +4565,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Mattishöljen N/O., Dls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>317350</v>
+        <v>317351</v>
       </c>
       <c r="R34" t="n">
-        <v>6550799</v>
+        <v>6550761</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4648,43 +4652,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129835724</v>
+        <v>129607603</v>
       </c>
       <c r="B35" t="n">
-        <v>43991</v>
+        <v>78747</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>101735</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4692,10 +4694,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>317204</v>
+        <v>317271</v>
       </c>
       <c r="R35" t="n">
-        <v>6550903</v>
+        <v>6550912</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4722,12 +4724,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4742,22 +4744,22 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Bärljungtallskog.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk # Fomes fomentarius</t>
+          <t>Rot # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4772,383 +4774,6 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>129836131</v>
-      </c>
-      <c r="B36" t="n">
-        <v>91841</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>5260</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Lateritticka</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Postia lateritia</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Renvall</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Pengehöljen O., Dls</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>317417</v>
-      </c>
-      <c r="R36" t="n">
-        <v>6550843</v>
-      </c>
-      <c r="S36" t="n">
-        <v>5</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Dals-Ed</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Dalsland</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Nössemark</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Tommy Solberg</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Tommy Solberg</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>129835784</v>
-      </c>
-      <c r="B37" t="n">
-        <v>8450</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>106545</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Tomicus minor</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Mattishöljen N/O., Dls</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>317351</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6550761</v>
-      </c>
-      <c r="S37" t="n">
-        <v>5</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Dals-Ed</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Dalsland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Nössemark</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Dödt träd # Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Tommy Solberg</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Tommy Solberg</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>129607603</v>
-      </c>
-      <c r="B38" t="n">
-        <v>78747</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>353</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Cladonia parasitica</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Pengehöljen O., Dls</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>317271</v>
-      </c>
-      <c r="R38" t="n">
-        <v>6550912</v>
-      </c>
-      <c r="S38" t="n">
-        <v>5</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Dals-Ed</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Dalsland</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Nössemark</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Bärljungtallskog.</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Rot # Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Tommy Solberg</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Tommy Solberg</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -3890,10 +3890,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129835752</v>
+        <v>129835803</v>
       </c>
       <c r="B29" t="n">
-        <v>43991</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3901,21 +3901,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>101735</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3930,14 +3930,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lögarehöljen S., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>317326</v>
+        <v>317185</v>
       </c>
       <c r="R29" t="n">
-        <v>6550956</v>
+        <v>6550868</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3989,17 +3989,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk # Fomes fomentarius</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4017,10 +4017,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129835803</v>
+        <v>129835752</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>43991</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4028,21 +4028,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>101735</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4057,14 +4057,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Lögarehöljen S., Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>317185</v>
+        <v>317326</v>
       </c>
       <c r="R30" t="n">
-        <v>6550868</v>
+        <v>6550956</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4116,17 +4116,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -3513,52 +3513,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129835344</v>
+        <v>129835737</v>
       </c>
       <c r="B26" t="n">
-        <v>78747</v>
+        <v>43991</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>101735</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Pengehöljen N/O., Dls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>317307</v>
+        <v>317254</v>
       </c>
       <c r="R26" t="n">
-        <v>6550845</v>
+        <v>6550959</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3605,22 +3607,22 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Bærljungtallskog</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3638,54 +3640,52 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129835737</v>
+        <v>129835344</v>
       </c>
       <c r="B27" t="n">
-        <v>43991</v>
+        <v>78747</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101735</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pengehöljen N/O., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>317254</v>
+        <v>317307</v>
       </c>
       <c r="R27" t="n">
-        <v>6550959</v>
+        <v>6550845</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3732,22 +3732,22 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Bærljungtallskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk # Fomes fomentarius</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -2773,10 +2773,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129835373</v>
+        <v>129835851</v>
       </c>
       <c r="B20" t="n">
-        <v>78747</v>
+        <v>91620</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2784,41 +2784,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Hökelshöljen S., Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>317330</v>
+        <v>317233</v>
       </c>
       <c r="R20" t="n">
-        <v>6550900</v>
+        <v>6550972</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2865,22 +2869,12 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Bærljungtallskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Död ticka på död tall.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2898,10 +2892,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129835851</v>
+        <v>129835373</v>
       </c>
       <c r="B21" t="n">
-        <v>91620</v>
+        <v>78747</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2909,45 +2903,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hökelshöljen S., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>317233</v>
+        <v>317330</v>
       </c>
       <c r="R21" t="n">
-        <v>6550972</v>
+        <v>6550900</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2994,12 +2984,22 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Bærljungtallskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Död ticka på död tall.</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3144,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129835710</v>
+        <v>129835838</v>
       </c>
       <c r="B23" t="n">
-        <v>43991</v>
+        <v>8439</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101735</v>
+        <v>106554</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3184,14 +3184,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mattishöljen N/O., Dls</t>
+          <t>Hökelshöljen S., Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>317372</v>
+        <v>317217</v>
       </c>
       <c r="R23" t="n">
-        <v>6550741</v>
+        <v>6550953</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3241,9 +3241,19 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3261,10 +3271,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129835838</v>
+        <v>129835710</v>
       </c>
       <c r="B24" t="n">
-        <v>8439</v>
+        <v>43991</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3272,21 +3282,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106554</v>
+        <v>101735</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3301,14 +3311,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hökelshöljen S., Dls</t>
+          <t>Mattishöljen N/O., Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>317217</v>
+        <v>317372</v>
       </c>
       <c r="R24" t="n">
-        <v>6550953</v>
+        <v>6550741</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3358,19 +3368,9 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Fnöskticka på björk</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3513,54 +3513,52 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129835737</v>
+        <v>129835344</v>
       </c>
       <c r="B26" t="n">
-        <v>43991</v>
+        <v>78747</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>101735</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pengehöljen N/O., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>317254</v>
+        <v>317307</v>
       </c>
       <c r="R26" t="n">
-        <v>6550959</v>
+        <v>6550845</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3607,22 +3605,22 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Bærljungtallskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk # Fomes fomentarius</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3640,52 +3638,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129835344</v>
+        <v>129835737</v>
       </c>
       <c r="B27" t="n">
-        <v>78747</v>
+        <v>43991</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>101735</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Pengehöljen N/O., Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>317307</v>
+        <v>317254</v>
       </c>
       <c r="R27" t="n">
-        <v>6550845</v>
+        <v>6550959</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3732,22 +3732,22 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Bærljungtallskog</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -3144,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129835838</v>
+        <v>129835710</v>
       </c>
       <c r="B23" t="n">
-        <v>8439</v>
+        <v>43991</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106554</v>
+        <v>101735</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3184,14 +3184,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hökelshöljen S., Dls</t>
+          <t>Mattishöljen N/O., Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>317217</v>
+        <v>317372</v>
       </c>
       <c r="R23" t="n">
-        <v>6550953</v>
+        <v>6550741</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3241,19 +3241,9 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Fnöskticka på björk</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3271,10 +3261,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129835710</v>
+        <v>129835838</v>
       </c>
       <c r="B24" t="n">
-        <v>43991</v>
+        <v>8439</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3282,21 +3272,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>101735</v>
+        <v>106554</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3311,14 +3301,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mattishöljen N/O., Dls</t>
+          <t>Hökelshöljen S., Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>317372</v>
+        <v>317217</v>
       </c>
       <c r="R24" t="n">
-        <v>6550741</v>
+        <v>6550953</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3368,9 +3358,19 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3890,10 +3890,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129835803</v>
+        <v>129835752</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>43991</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3901,21 +3901,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>101735</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3930,14 +3930,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Lögarehöljen S., Dls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>317185</v>
+        <v>317326</v>
       </c>
       <c r="R29" t="n">
-        <v>6550868</v>
+        <v>6550956</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3989,17 +3989,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4017,10 +4017,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129835752</v>
+        <v>129835803</v>
       </c>
       <c r="B30" t="n">
-        <v>43991</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4028,21 +4028,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>101735</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4057,14 +4057,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lögarehöljen S., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>317326</v>
+        <v>317185</v>
       </c>
       <c r="R30" t="n">
-        <v>6550956</v>
+        <v>6550868</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4116,17 +4116,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk # Fomes fomentarius</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -2776,7 +2776,7 @@
         <v>129835851</v>
       </c>
       <c r="B20" t="n">
-        <v>91620</v>
+        <v>91623</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>129835373</v>
       </c>
       <c r="B21" t="n">
-        <v>78747</v>
+        <v>78750</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>129835991</v>
       </c>
       <c r="B25" t="n">
-        <v>91409</v>
+        <v>91412</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>129835344</v>
       </c>
       <c r="B26" t="n">
-        <v>78747</v>
+        <v>78750</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>129835977</v>
       </c>
       <c r="B28" t="n">
-        <v>91872</v>
+        <v>91875</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>129607603</v>
       </c>
       <c r="B35" t="n">
-        <v>78747</v>
+        <v>78750</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -1529,7 +1529,7 @@
         <v>129607034</v>
       </c>
       <c r="B10" t="n">
-        <v>92241</v>
+        <v>92244</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>129606816</v>
       </c>
       <c r="B11" t="n">
-        <v>92082</v>
+        <v>92085</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>129605837</v>
       </c>
       <c r="B13" t="n">
-        <v>91652</v>
+        <v>91655</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>129607900</v>
       </c>
       <c r="B14" t="n">
-        <v>91772</v>
+        <v>91775</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>129606260</v>
       </c>
       <c r="B15" t="n">
-        <v>90981</v>
+        <v>90984</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>129606938</v>
       </c>
       <c r="B16" t="n">
-        <v>92082</v>
+        <v>92085</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129605988</v>
       </c>
       <c r="B17" t="n">
-        <v>92082</v>
+        <v>92085</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>129607723</v>
       </c>
       <c r="B18" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>129654925</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2773,10 +2773,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129835851</v>
+        <v>129835373</v>
       </c>
       <c r="B20" t="n">
-        <v>91623</v>
+        <v>78750</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2784,45 +2784,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hökelshöljen S., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>317233</v>
+        <v>317330</v>
       </c>
       <c r="R20" t="n">
-        <v>6550972</v>
+        <v>6550900</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2869,12 +2865,22 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Bærljungtallskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Död ticka på död tall.</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2892,10 +2898,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129835373</v>
+        <v>129835851</v>
       </c>
       <c r="B21" t="n">
-        <v>78750</v>
+        <v>91623</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,41 +2909,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Hökelshöljen S., Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>317330</v>
+        <v>317233</v>
       </c>
       <c r="R21" t="n">
-        <v>6550900</v>
+        <v>6550972</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2984,22 +2994,12 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Bærljungtallskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Död ticka på död tall.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3144,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129835710</v>
+        <v>129835838</v>
       </c>
       <c r="B23" t="n">
-        <v>43991</v>
+        <v>8439</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101735</v>
+        <v>106554</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3184,14 +3184,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mattishöljen N/O., Dls</t>
+          <t>Hökelshöljen S., Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>317372</v>
+        <v>317217</v>
       </c>
       <c r="R23" t="n">
-        <v>6550741</v>
+        <v>6550953</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3241,9 +3241,19 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3261,10 +3271,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129835838</v>
+        <v>129835710</v>
       </c>
       <c r="B24" t="n">
-        <v>8439</v>
+        <v>43991</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3272,21 +3282,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106554</v>
+        <v>101735</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3301,14 +3311,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hökelshöljen S., Dls</t>
+          <t>Mattishöljen N/O., Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>317217</v>
+        <v>317372</v>
       </c>
       <c r="R24" t="n">
-        <v>6550953</v>
+        <v>6550741</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3358,19 +3368,9 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Fnöskticka på björk</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -2773,10 +2773,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129835373</v>
+        <v>129835851</v>
       </c>
       <c r="B20" t="n">
-        <v>78750</v>
+        <v>91623</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2784,41 +2784,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Hökelshöljen S., Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>317330</v>
+        <v>317233</v>
       </c>
       <c r="R20" t="n">
-        <v>6550900</v>
+        <v>6550972</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2865,22 +2869,12 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Bærljungtallskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Död ticka på död tall.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2898,10 +2892,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129835851</v>
+        <v>129835373</v>
       </c>
       <c r="B21" t="n">
-        <v>91623</v>
+        <v>78750</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2909,45 +2903,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hökelshöljen S., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>317233</v>
+        <v>317330</v>
       </c>
       <c r="R21" t="n">
-        <v>6550972</v>
+        <v>6550900</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2994,12 +2984,22 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Bærljungtallskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Död ticka på död tall.</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3144,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129835838</v>
+        <v>129835710</v>
       </c>
       <c r="B23" t="n">
-        <v>8439</v>
+        <v>43991</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106554</v>
+        <v>101735</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3184,14 +3184,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hökelshöljen S., Dls</t>
+          <t>Mattishöljen N/O., Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>317217</v>
+        <v>317372</v>
       </c>
       <c r="R23" t="n">
-        <v>6550953</v>
+        <v>6550741</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3241,19 +3241,9 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Fnöskticka på björk</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3271,10 +3261,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129835710</v>
+        <v>129835838</v>
       </c>
       <c r="B24" t="n">
-        <v>43991</v>
+        <v>8439</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3282,21 +3272,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>101735</v>
+        <v>106554</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3311,14 +3301,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mattishöljen N/O., Dls</t>
+          <t>Hökelshöljen S., Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>317372</v>
+        <v>317217</v>
       </c>
       <c r="R24" t="n">
-        <v>6550741</v>
+        <v>6550953</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3368,9 +3358,19 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3513,52 +3513,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129835344</v>
+        <v>129835737</v>
       </c>
       <c r="B26" t="n">
-        <v>78750</v>
+        <v>43991</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>101735</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Pengehöljen N/O., Dls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>317307</v>
+        <v>317254</v>
       </c>
       <c r="R26" t="n">
-        <v>6550845</v>
+        <v>6550959</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3605,22 +3607,22 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Bærljungtallskog</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3638,54 +3640,52 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129835737</v>
+        <v>129835344</v>
       </c>
       <c r="B27" t="n">
-        <v>43991</v>
+        <v>78750</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101735</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pengehöljen N/O., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>317254</v>
+        <v>317307</v>
       </c>
       <c r="R27" t="n">
-        <v>6550959</v>
+        <v>6550845</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3732,22 +3732,22 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Bærljungtallskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk # Fomes fomentarius</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3765,52 +3765,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129835977</v>
+        <v>129835752</v>
       </c>
       <c r="B28" t="n">
-        <v>91875</v>
+        <v>43991</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>65</v>
+        <v>101735</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Lögarehöljen S., Dls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>317373</v>
+        <v>317326</v>
       </c>
       <c r="R28" t="n">
-        <v>6550816</v>
+        <v>6550956</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3862,17 +3864,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3890,10 +3892,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129835752</v>
+        <v>129835803</v>
       </c>
       <c r="B29" t="n">
-        <v>43991</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3901,21 +3903,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>101735</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3930,14 +3932,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lögarehöljen S., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>317326</v>
+        <v>317185</v>
       </c>
       <c r="R29" t="n">
-        <v>6550956</v>
+        <v>6550868</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3989,17 +3991,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk # Fomes fomentarius</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4017,43 +4019,41 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129835803</v>
+        <v>129835977</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>91875</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>65</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>317185</v>
+        <v>317373</v>
       </c>
       <c r="R30" t="n">
-        <v>6550868</v>
+        <v>6550816</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -1529,7 +1529,7 @@
         <v>129607034</v>
       </c>
       <c r="B10" t="n">
-        <v>92244</v>
+        <v>92247</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>129606816</v>
       </c>
       <c r="B11" t="n">
-        <v>92085</v>
+        <v>92088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>129605837</v>
       </c>
       <c r="B13" t="n">
-        <v>91655</v>
+        <v>91658</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>129607900</v>
       </c>
       <c r="B14" t="n">
-        <v>91775</v>
+        <v>91778</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>129606260</v>
       </c>
       <c r="B15" t="n">
-        <v>90984</v>
+        <v>90987</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>129606938</v>
       </c>
       <c r="B16" t="n">
-        <v>92085</v>
+        <v>92088</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>129605988</v>
       </c>
       <c r="B17" t="n">
-        <v>92085</v>
+        <v>92088</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>129607723</v>
       </c>
       <c r="B18" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>129654925</v>
       </c>
       <c r="B19" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2773,10 +2773,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129835851</v>
+        <v>129835373</v>
       </c>
       <c r="B20" t="n">
-        <v>91623</v>
+        <v>78753</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2784,45 +2784,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hökelshöljen S., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>317233</v>
+        <v>317330</v>
       </c>
       <c r="R20" t="n">
-        <v>6550972</v>
+        <v>6550900</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2869,12 +2865,22 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Bærljungtallskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Död ticka på död tall.</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2892,10 +2898,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129835373</v>
+        <v>129835851</v>
       </c>
       <c r="B21" t="n">
-        <v>78750</v>
+        <v>91626</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,41 +2909,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Hökelshöljen S., Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>317330</v>
+        <v>317233</v>
       </c>
       <c r="R21" t="n">
-        <v>6550900</v>
+        <v>6550972</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2984,22 +2994,12 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Bærljungtallskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Död ticka på död tall.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3020,7 +3020,7 @@
         <v>129835818</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3144,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129835710</v>
+        <v>129835838</v>
       </c>
       <c r="B23" t="n">
-        <v>43991</v>
+        <v>8440</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101735</v>
+        <v>106554</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3184,14 +3184,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mattishöljen N/O., Dls</t>
+          <t>Hökelshöljen S., Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>317372</v>
+        <v>317217</v>
       </c>
       <c r="R23" t="n">
-        <v>6550741</v>
+        <v>6550953</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3241,9 +3241,19 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3261,10 +3271,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129835838</v>
+        <v>129835710</v>
       </c>
       <c r="B24" t="n">
-        <v>8439</v>
+        <v>43994</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3272,21 +3282,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106554</v>
+        <v>101735</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3301,14 +3311,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hökelshöljen S., Dls</t>
+          <t>Mattishöljen N/O., Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>317217</v>
+        <v>317372</v>
       </c>
       <c r="R24" t="n">
-        <v>6550953</v>
+        <v>6550741</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3358,19 +3368,9 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Fnöskticka på björk</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3391,7 +3391,7 @@
         <v>129835991</v>
       </c>
       <c r="B25" t="n">
-        <v>91412</v>
+        <v>91415</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3513,54 +3513,52 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129835737</v>
+        <v>129835344</v>
       </c>
       <c r="B26" t="n">
-        <v>43991</v>
+        <v>78753</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>101735</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pengehöljen N/O., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>317254</v>
+        <v>317307</v>
       </c>
       <c r="R26" t="n">
-        <v>6550959</v>
+        <v>6550845</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3607,22 +3605,22 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Bærljungtallskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk # Fomes fomentarius</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3640,52 +3638,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129835344</v>
+        <v>129835737</v>
       </c>
       <c r="B27" t="n">
-        <v>78750</v>
+        <v>43994</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>101735</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Pengehöljen N/O., Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>317307</v>
+        <v>317254</v>
       </c>
       <c r="R27" t="n">
-        <v>6550845</v>
+        <v>6550959</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3732,22 +3732,22 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Bærljungtallskog</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3765,54 +3765,52 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129835752</v>
+        <v>129835977</v>
       </c>
       <c r="B28" t="n">
-        <v>43991</v>
+        <v>91878</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101735</v>
+        <v>65</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lögarehöljen S., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>317326</v>
+        <v>317373</v>
       </c>
       <c r="R28" t="n">
-        <v>6550956</v>
+        <v>6550816</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3864,17 +3862,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk # Fomes fomentarius</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3892,10 +3890,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129835803</v>
+        <v>129835752</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>43994</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3903,21 +3901,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>101735</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3932,14 +3930,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Lögarehöljen S., Dls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>317185</v>
+        <v>317326</v>
       </c>
       <c r="R29" t="n">
-        <v>6550868</v>
+        <v>6550956</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3991,17 +3989,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4019,41 +4017,43 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129835977</v>
+        <v>129835803</v>
       </c>
       <c r="B30" t="n">
-        <v>91875</v>
+        <v>8451</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>65</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>317373</v>
+        <v>317185</v>
       </c>
       <c r="R30" t="n">
-        <v>6550816</v>
+        <v>6550868</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4147,7 +4147,7 @@
         <v>129835810</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>129835794</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>129835724</v>
       </c>
       <c r="B33" t="n">
-        <v>43991</v>
+        <v>43994</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>129835784</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>129607603</v>
       </c>
       <c r="B35" t="n">
-        <v>78750</v>
+        <v>78753</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -2773,10 +2773,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129835373</v>
+        <v>129835851</v>
       </c>
       <c r="B20" t="n">
-        <v>78753</v>
+        <v>91626</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2784,41 +2784,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Hökelshöljen S., Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>317330</v>
+        <v>317233</v>
       </c>
       <c r="R20" t="n">
-        <v>6550900</v>
+        <v>6550972</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2865,22 +2869,12 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Bærljungtallskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Död ticka på död tall.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2898,10 +2892,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129835851</v>
+        <v>129835373</v>
       </c>
       <c r="B21" t="n">
-        <v>91626</v>
+        <v>78753</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2909,45 +2903,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hökelshöljen S., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>317233</v>
+        <v>317330</v>
       </c>
       <c r="R21" t="n">
-        <v>6550972</v>
+        <v>6550900</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2994,12 +2984,22 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Bærljungtallskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Död ticka på död tall.</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3144,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129835838</v>
+        <v>129835710</v>
       </c>
       <c r="B23" t="n">
-        <v>8440</v>
+        <v>43994</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106554</v>
+        <v>101735</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3184,14 +3184,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hökelshöljen S., Dls</t>
+          <t>Mattishöljen N/O., Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>317217</v>
+        <v>317372</v>
       </c>
       <c r="R23" t="n">
-        <v>6550953</v>
+        <v>6550741</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3241,19 +3241,9 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Fnöskticka på björk</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3271,10 +3261,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129835710</v>
+        <v>129835838</v>
       </c>
       <c r="B24" t="n">
-        <v>43994</v>
+        <v>8440</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3282,21 +3272,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>101735</v>
+        <v>106554</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3311,14 +3301,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mattishöljen N/O., Dls</t>
+          <t>Hökelshöljen S., Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>317372</v>
+        <v>317217</v>
       </c>
       <c r="R24" t="n">
-        <v>6550741</v>
+        <v>6550953</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3368,9 +3358,19 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -3144,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129835710</v>
+        <v>129835838</v>
       </c>
       <c r="B23" t="n">
-        <v>43994</v>
+        <v>8440</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101735</v>
+        <v>106554</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3184,14 +3184,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mattishöljen N/O., Dls</t>
+          <t>Hökelshöljen S., Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>317372</v>
+        <v>317217</v>
       </c>
       <c r="R23" t="n">
-        <v>6550741</v>
+        <v>6550953</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3241,9 +3241,19 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3261,10 +3271,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129835838</v>
+        <v>129835710</v>
       </c>
       <c r="B24" t="n">
-        <v>8440</v>
+        <v>43994</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3272,21 +3282,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106554</v>
+        <v>101735</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3301,14 +3311,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hökelshöljen S., Dls</t>
+          <t>Mattishöljen N/O., Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>317217</v>
+        <v>317372</v>
       </c>
       <c r="R24" t="n">
-        <v>6550953</v>
+        <v>6550741</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3358,19 +3368,9 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Fnöskticka på björk</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -2776,7 +2776,7 @@
         <v>129835851</v>
       </c>
       <c r="B20" t="n">
-        <v>91626</v>
+        <v>91627</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>129835373</v>
       </c>
       <c r="B21" t="n">
-        <v>78753</v>
+        <v>78754</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>129835991</v>
       </c>
       <c r="B25" t="n">
-        <v>91415</v>
+        <v>91416</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>129835344</v>
       </c>
       <c r="B26" t="n">
-        <v>78753</v>
+        <v>78754</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>129835977</v>
       </c>
       <c r="B28" t="n">
-        <v>91878</v>
+        <v>91879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>129607603</v>
       </c>
       <c r="B35" t="n">
-        <v>78753</v>
+        <v>78754</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3144,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129835838</v>
+        <v>129835710</v>
       </c>
       <c r="B23" t="n">
-        <v>8440</v>
+        <v>43994</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106554</v>
+        <v>101735</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3184,14 +3184,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hökelshöljen S., Dls</t>
+          <t>Mattishöljen N/O., Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>317217</v>
+        <v>317372</v>
       </c>
       <c r="R23" t="n">
-        <v>6550953</v>
+        <v>6550741</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3241,19 +3241,9 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Fnöskticka på björk</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3271,10 +3261,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129835710</v>
+        <v>129835838</v>
       </c>
       <c r="B24" t="n">
-        <v>43994</v>
+        <v>8440</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3282,21 +3272,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>101735</v>
+        <v>106554</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3311,14 +3301,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mattishöljen N/O., Dls</t>
+          <t>Hökelshöljen S., Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>317372</v>
+        <v>317217</v>
       </c>
       <c r="R24" t="n">
-        <v>6550741</v>
+        <v>6550953</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3368,9 +3358,19 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3765,52 +3765,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129835977</v>
+        <v>129835752</v>
       </c>
       <c r="B28" t="n">
-        <v>91879</v>
+        <v>43994</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>65</v>
+        <v>101735</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Lögarehöljen S., Dls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>317373</v>
+        <v>317326</v>
       </c>
       <c r="R28" t="n">
-        <v>6550816</v>
+        <v>6550956</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3862,17 +3864,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3890,10 +3892,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129835752</v>
+        <v>129835803</v>
       </c>
       <c r="B29" t="n">
-        <v>43994</v>
+        <v>8451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3901,21 +3903,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>101735</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3930,14 +3932,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lögarehöljen S., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>317326</v>
+        <v>317185</v>
       </c>
       <c r="R29" t="n">
-        <v>6550956</v>
+        <v>6550868</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3989,17 +3991,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk # Fomes fomentarius</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4017,43 +4019,41 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129835803</v>
+        <v>129835977</v>
       </c>
       <c r="B30" t="n">
-        <v>8451</v>
+        <v>91879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>65</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>317185</v>
+        <v>317373</v>
       </c>
       <c r="R30" t="n">
-        <v>6550868</v>
+        <v>6550816</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4775,6 +4775,5035 @@
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>130072825</v>
+      </c>
+      <c r="B36" t="n">
+        <v>97048</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>53</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>317555</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6550893</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>130063347</v>
+      </c>
+      <c r="B37" t="n">
+        <v>75199</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>317459</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6550916</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>130063320</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80154</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>317410</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6550877</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>130063338</v>
+      </c>
+      <c r="B39" t="n">
+        <v>75199</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>317422</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6550917</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>130063325</v>
+      </c>
+      <c r="B40" t="n">
+        <v>97084</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>317315</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6550988</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>130063324</v>
+      </c>
+      <c r="B41" t="n">
+        <v>97084</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>317307</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6550995</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>130063356</v>
+      </c>
+      <c r="B42" t="n">
+        <v>92892</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>317537</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6550669</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>130063358</v>
+      </c>
+      <c r="B43" t="n">
+        <v>97084</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>317521</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6550632</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129836196</v>
+      </c>
+      <c r="B44" t="n">
+        <v>91852</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>5260</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Lateritticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Postia lateritia</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Renvall</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Pengehöljen O., Dls</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>317366</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6550921</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129836143</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91852</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5260</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lateritticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Postia lateritia</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Renvall</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Pengehöljen O., Dls</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>317353</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6550899</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>130063322</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80154</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>317366</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6550944</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>130063357</v>
+      </c>
+      <c r="B47" t="n">
+        <v>56930</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>317515</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6550638</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>130063331</v>
+      </c>
+      <c r="B48" t="n">
+        <v>97423</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>317408</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6550956</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>130063355</v>
+      </c>
+      <c r="B49" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>317544</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6550707</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>130063350</v>
+      </c>
+      <c r="B50" t="n">
+        <v>90992</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>317461</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6550934</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>130063345</v>
+      </c>
+      <c r="B51" t="n">
+        <v>97084</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>317456</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6550897</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>130063323</v>
+      </c>
+      <c r="B52" t="n">
+        <v>75199</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>317366</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6550944</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>130063334</v>
+      </c>
+      <c r="B53" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>317428</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6550930</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>130063327</v>
+      </c>
+      <c r="B54" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>317333</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6550980</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>130063330</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91574</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>317408</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6550961</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>130063318</v>
+      </c>
+      <c r="B56" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>317387</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6550788</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>130063336</v>
+      </c>
+      <c r="B57" t="n">
+        <v>75199</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>317424</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6550930</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>130063353</v>
+      </c>
+      <c r="B58" t="n">
+        <v>90992</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>317478</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6550898</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>130063343</v>
+      </c>
+      <c r="B59" t="n">
+        <v>91610</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>317442</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6550932</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>130063339</v>
+      </c>
+      <c r="B60" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>317422</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6550917</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>130063346</v>
+      </c>
+      <c r="B61" t="n">
+        <v>97084</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>317457</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6550912</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>130063344</v>
+      </c>
+      <c r="B62" t="n">
+        <v>97048</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>53</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>317456</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6550897</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>130063319</v>
+      </c>
+      <c r="B63" t="n">
+        <v>97048</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>53</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>317401</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6550860</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>130063321</v>
+      </c>
+      <c r="B64" t="n">
+        <v>92892</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>317373</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6550909</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>130063316</v>
+      </c>
+      <c r="B65" t="n">
+        <v>97084</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>317362</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6550742</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>130063341</v>
+      </c>
+      <c r="B66" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>317442</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6550932</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>130063332</v>
+      </c>
+      <c r="B67" t="n">
+        <v>75199</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>317425</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6550935</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>130063342</v>
+      </c>
+      <c r="B68" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>317442</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6550932</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>130063317</v>
+      </c>
+      <c r="B69" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>317378</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6550754</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>130063352</v>
+      </c>
+      <c r="B70" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>317471</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6550898</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129836131</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91852</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>5260</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Lateritticka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Postia lateritia</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Renvall</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Pengehöljen O., Dls</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>317417</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6550843</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Bärljungbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Tommy Solberg</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>130063348</v>
+      </c>
+      <c r="B72" t="n">
+        <v>75199</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>317459</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6550959</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>130063354</v>
+      </c>
+      <c r="B73" t="n">
+        <v>92892</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>317491</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6550822</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>130063326</v>
+      </c>
+      <c r="B74" t="n">
+        <v>91574</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>317328</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6550975</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>130063333</v>
+      </c>
+      <c r="B75" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>317428</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6550930</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>130063329</v>
+      </c>
+      <c r="B76" t="n">
+        <v>97423</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>317411</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6550970</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>130063340</v>
+      </c>
+      <c r="B77" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>317439</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6550940</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>130063337</v>
+      </c>
+      <c r="B78" t="n">
+        <v>97048</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>53</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>317425</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6550915</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>130063335</v>
+      </c>
+      <c r="B79" t="n">
+        <v>92892</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>317426</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6550926</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>130063359</v>
+      </c>
+      <c r="B80" t="n">
+        <v>8440</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>317525</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6550630</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>130063351</v>
+      </c>
+      <c r="B81" t="n">
+        <v>75199</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>317464</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6550904</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>130063328</v>
+      </c>
+      <c r="B82" t="n">
+        <v>80154</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>317351</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6550971</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -3765,54 +3765,52 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129835752</v>
+        <v>129835977</v>
       </c>
       <c r="B28" t="n">
-        <v>43994</v>
+        <v>91879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101735</v>
+        <v>65</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lögarehöljen S., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>317326</v>
+        <v>317373</v>
       </c>
       <c r="R28" t="n">
-        <v>6550956</v>
+        <v>6550816</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3864,17 +3862,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk # Fomes fomentarius</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4019,52 +4017,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129835977</v>
+        <v>129835752</v>
       </c>
       <c r="B30" t="n">
-        <v>91879</v>
+        <v>43994</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>65</v>
+        <v>101735</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Lögarehöljen S., Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>317373</v>
+        <v>317326</v>
       </c>
       <c r="R30" t="n">
-        <v>6550816</v>
+        <v>6550956</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4116,17 +4116,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AY80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2776,7 +2776,7 @@
         <v>129835851</v>
       </c>
       <c r="B20" t="n">
-        <v>91627</v>
+        <v>91644</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2892,41 +2892,43 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129835373</v>
+        <v>129835818</v>
       </c>
       <c r="B21" t="n">
-        <v>78754</v>
+        <v>8451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2934,10 +2936,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>317330</v>
+        <v>317365</v>
       </c>
       <c r="R21" t="n">
-        <v>6550900</v>
+        <v>6550833</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2984,7 +2986,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Bærljungtallskog</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -2999,7 +3001,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Dödt träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3017,10 +3019,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129835818</v>
+        <v>129835710</v>
       </c>
       <c r="B22" t="n">
-        <v>8451</v>
+        <v>43994</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,21 +3030,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>101735</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3057,14 +3059,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Mattishöljen N/O., Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>317365</v>
+        <v>317372</v>
       </c>
       <c r="R22" t="n">
-        <v>6550833</v>
+        <v>6550741</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3114,19 +3116,9 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Dödt träd # Pinus sylvestris</t>
+          <t>Fnöskticka på björk</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3144,10 +3136,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129835710</v>
+        <v>129835838</v>
       </c>
       <c r="B23" t="n">
-        <v>43994</v>
+        <v>8440</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,21 +3147,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101735</v>
+        <v>106554</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3184,14 +3176,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mattishöljen N/O., Dls</t>
+          <t>Hökelshöljen S., Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>317372</v>
+        <v>317217</v>
       </c>
       <c r="R23" t="n">
-        <v>6550741</v>
+        <v>6550953</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3241,9 +3233,19 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3261,54 +3263,52 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129835838</v>
+        <v>129835991</v>
       </c>
       <c r="B24" t="n">
-        <v>8440</v>
+        <v>91433</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106554</v>
+        <v>6006</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Oljeporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sistotrema alboluteum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Bourdot &amp; Galzin) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hökelshöljen S., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>317217</v>
+        <v>317371</v>
       </c>
       <c r="R24" t="n">
-        <v>6550953</v>
+        <v>6550814</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3360,17 +3360,17 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3388,52 +3388,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129835991</v>
+        <v>129835737</v>
       </c>
       <c r="B25" t="n">
-        <v>91416</v>
+        <v>43994</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6006</v>
+        <v>101735</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Oljeporing</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sistotrema alboluteum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Bondartsev &amp; Singer</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Pengehöljen N/O., Dls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>317371</v>
+        <v>317254</v>
       </c>
       <c r="R25" t="n">
-        <v>6550814</v>
+        <v>6550959</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3485,17 +3487,17 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3513,38 +3515,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129835344</v>
+        <v>129835977</v>
       </c>
       <c r="B26" t="n">
-        <v>78754</v>
+        <v>91896</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -3555,10 +3557,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>317307</v>
+        <v>317373</v>
       </c>
       <c r="R26" t="n">
-        <v>6550845</v>
+        <v>6550816</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3605,7 +3607,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Bærljungtallskog</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3638,7 +3640,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129835737</v>
+        <v>129835752</v>
       </c>
       <c r="B27" t="n">
         <v>43994</v>
@@ -3678,14 +3680,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pengehöljen N/O., Dls</t>
+          <t>Lögarehöljen S., Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>317254</v>
+        <v>317326</v>
       </c>
       <c r="R27" t="n">
-        <v>6550959</v>
+        <v>6550956</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3765,41 +3767,43 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129835977</v>
+        <v>129835803</v>
       </c>
       <c r="B28" t="n">
-        <v>91879</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>65</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3807,10 +3811,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>317373</v>
+        <v>317185</v>
       </c>
       <c r="R28" t="n">
-        <v>6550816</v>
+        <v>6550868</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3890,7 +3894,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129835803</v>
+        <v>129835810</v>
       </c>
       <c r="B29" t="n">
         <v>8451</v>
@@ -3934,10 +3938,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>317185</v>
+        <v>317189</v>
       </c>
       <c r="R29" t="n">
-        <v>6550868</v>
+        <v>6550878</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3999,7 +4003,7 @@
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Dödt träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4017,10 +4021,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129835752</v>
+        <v>129835794</v>
       </c>
       <c r="B30" t="n">
-        <v>43994</v>
+        <v>8451</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4028,21 +4032,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>101735</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4057,14 +4061,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lögarehöljen S., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>317326</v>
+        <v>317350</v>
       </c>
       <c r="R30" t="n">
-        <v>6550956</v>
+        <v>6550799</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4116,17 +4120,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk # Fomes fomentarius</t>
+          <t>Dödt träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4144,10 +4148,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129835810</v>
+        <v>129835724</v>
       </c>
       <c r="B31" t="n">
-        <v>8451</v>
+        <v>43994</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4155,21 +4159,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>101735</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4188,10 +4192,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>317189</v>
+        <v>317204</v>
       </c>
       <c r="R31" t="n">
-        <v>6550878</v>
+        <v>6550903</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4243,17 +4247,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Dödt träd # Pinus sylvestris</t>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4271,7 +4275,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129835794</v>
+        <v>129835784</v>
       </c>
       <c r="B32" t="n">
         <v>8451</v>
@@ -4311,14 +4315,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Mattishöljen N/O., Dls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>317350</v>
+        <v>317351</v>
       </c>
       <c r="R32" t="n">
-        <v>6550799</v>
+        <v>6550761</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4398,43 +4402,41 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129835724</v>
+        <v>129607603</v>
       </c>
       <c r="B33" t="n">
-        <v>43994</v>
+        <v>78755</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>101735</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4442,10 +4444,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>317204</v>
+        <v>317271</v>
       </c>
       <c r="R33" t="n">
-        <v>6550903</v>
+        <v>6550912</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4472,12 +4474,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4492,22 +4494,22 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Bärljungtallskog.</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk # Fomes fomentarius</t>
+          <t>Rot # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4525,54 +4527,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129835784</v>
+        <v>130072825</v>
       </c>
       <c r="B34" t="n">
-        <v>8451</v>
+        <v>97061</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mattishöljen N/O., Dls</t>
+          <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>317351</v>
+        <v>317555</v>
       </c>
       <c r="R34" t="n">
-        <v>6550761</v>
+        <v>6550893</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4599,12 +4592,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4613,91 +4606,63 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Dödt träd # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129607603</v>
+        <v>130063347</v>
       </c>
       <c r="B35" t="n">
-        <v>78754</v>
+        <v>75200</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>6426</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>317271</v>
+        <v>317459</v>
       </c>
       <c r="R35" t="n">
-        <v>6550912</v>
+        <v>6550916</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4724,12 +4689,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4738,71 +4703,65 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Bärljungtallskog.</t>
-        </is>
-      </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Rot # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130072825</v>
+        <v>130063320</v>
       </c>
       <c r="B36" t="n">
-        <v>97048</v>
+        <v>80154</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>229497</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4812,10 +4771,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>317555</v>
+        <v>317410</v>
       </c>
       <c r="R36" t="n">
-        <v>6550893</v>
+        <v>6550877</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4858,6 +4817,21 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4874,10 +4848,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130063347</v>
+        <v>130063338</v>
       </c>
       <c r="B37" t="n">
-        <v>75199</v>
+        <v>75200</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4909,10 +4883,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>317459</v>
+        <v>317422</v>
       </c>
       <c r="R37" t="n">
-        <v>6550916</v>
+        <v>6550917</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4986,10 +4960,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130063320</v>
+        <v>130063324</v>
       </c>
       <c r="B38" t="n">
-        <v>80154</v>
+        <v>97097</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4997,21 +4971,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229497</v>
+        <v>2590</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5021,10 +4995,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>317410</v>
+        <v>317307</v>
       </c>
       <c r="R38" t="n">
-        <v>6550877</v>
+        <v>6550995</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5067,21 +5041,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5098,10 +5057,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130063338</v>
+        <v>130063325</v>
       </c>
       <c r="B39" t="n">
-        <v>75199</v>
+        <v>97097</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5109,21 +5068,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5133,10 +5092,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>317422</v>
+        <v>317315</v>
       </c>
       <c r="R39" t="n">
-        <v>6550917</v>
+        <v>6550988</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5179,21 +5138,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5210,10 +5154,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130063325</v>
+        <v>130063358</v>
       </c>
       <c r="B40" t="n">
-        <v>97084</v>
+        <v>97097</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5245,10 +5189,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>317315</v>
+        <v>317521</v>
       </c>
       <c r="R40" t="n">
-        <v>6550988</v>
+        <v>6550632</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5307,10 +5251,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130063324</v>
+        <v>130063356</v>
       </c>
       <c r="B41" t="n">
-        <v>97084</v>
+        <v>92905</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5318,21 +5262,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5342,10 +5286,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>317307</v>
+        <v>317537</v>
       </c>
       <c r="R41" t="n">
-        <v>6550995</v>
+        <v>6550669</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5404,10 +5348,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130063356</v>
+        <v>130063322</v>
       </c>
       <c r="B42" t="n">
-        <v>92892</v>
+        <v>80154</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5415,21 +5359,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>229497</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5439,10 +5383,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>317537</v>
+        <v>317366</v>
       </c>
       <c r="R42" t="n">
-        <v>6550669</v>
+        <v>6550944</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5485,6 +5429,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5501,10 +5460,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130063358</v>
+        <v>130063331</v>
       </c>
       <c r="B43" t="n">
-        <v>97084</v>
+        <v>97436</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5512,21 +5471,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2590</v>
+        <v>2569</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5536,10 +5495,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>317521</v>
+        <v>317408</v>
       </c>
       <c r="R43" t="n">
-        <v>6550632</v>
+        <v>6550956</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5598,52 +5557,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129836196</v>
+        <v>130063357</v>
       </c>
       <c r="B44" t="n">
-        <v>91852</v>
+        <v>56930</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5260</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>317366</v>
+        <v>317515</v>
       </c>
       <c r="R44" t="n">
-        <v>6550921</v>
+        <v>6550638</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5670,12 +5627,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5684,91 +5641,63 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129836143</v>
+        <v>130063350</v>
       </c>
       <c r="B45" t="n">
-        <v>91852</v>
+        <v>91005</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5260</v>
+        <v>5685</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>317353</v>
+        <v>317461</v>
       </c>
       <c r="R45" t="n">
-        <v>6550899</v>
+        <v>6550934</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5795,12 +5724,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5809,15 +5738,9 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
       <c r="AJ45" t="inlineStr">
         <is>
           <t>tall</t>
@@ -5830,28 +5753,28 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130063322</v>
+        <v>130063355</v>
       </c>
       <c r="B46" t="n">
-        <v>80154</v>
+        <v>8451</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5859,34 +5782,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229497</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>317366</v>
+        <v>317544</v>
       </c>
       <c r="R46" t="n">
-        <v>6550944</v>
+        <v>6550707</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5932,17 +5860,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5960,10 +5888,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130063357</v>
+        <v>130063323</v>
       </c>
       <c r="B47" t="n">
-        <v>56930</v>
+        <v>75200</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5971,39 +5899,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>317515</v>
+        <v>317366</v>
       </c>
       <c r="R47" t="n">
-        <v>6550638</v>
+        <v>6550944</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6062,10 +5985,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130063331</v>
+        <v>130063345</v>
       </c>
       <c r="B48" t="n">
-        <v>97423</v>
+        <v>97097</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6073,21 +5996,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2569</v>
+        <v>2590</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6097,10 +6020,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>317408</v>
+        <v>317456</v>
       </c>
       <c r="R48" t="n">
-        <v>6550956</v>
+        <v>6550897</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6159,10 +6082,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130063355</v>
+        <v>130063327</v>
       </c>
       <c r="B49" t="n">
-        <v>8451</v>
+        <v>5197</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6170,21 +6093,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6199,10 +6122,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>317544</v>
+        <v>317333</v>
       </c>
       <c r="R49" t="n">
-        <v>6550707</v>
+        <v>6550980</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6248,17 +6171,17 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6276,10 +6199,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130063350</v>
+        <v>130063334</v>
       </c>
       <c r="B50" t="n">
-        <v>90992</v>
+        <v>5197</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6287,34 +6210,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5685</v>
+        <v>105930</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>317461</v>
+        <v>317428</v>
       </c>
       <c r="R50" t="n">
-        <v>6550934</v>
+        <v>6550930</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6360,17 +6288,17 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6388,10 +6316,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130063345</v>
+        <v>130063336</v>
       </c>
       <c r="B51" t="n">
-        <v>97084</v>
+        <v>75200</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6399,21 +6327,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6423,10 +6351,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>317456</v>
+        <v>317424</v>
       </c>
       <c r="R51" t="n">
-        <v>6550897</v>
+        <v>6550930</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6485,10 +6413,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130063323</v>
+        <v>130063353</v>
       </c>
       <c r="B52" t="n">
-        <v>75199</v>
+        <v>91005</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6496,21 +6424,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6426</v>
+        <v>5685</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6520,10 +6448,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>317366</v>
+        <v>317478</v>
       </c>
       <c r="R52" t="n">
-        <v>6550944</v>
+        <v>6550898</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6566,6 +6494,21 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6582,10 +6525,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130063334</v>
+        <v>130063330</v>
       </c>
       <c r="B53" t="n">
-        <v>5197</v>
+        <v>91587</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6593,39 +6536,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>317428</v>
+        <v>317408</v>
       </c>
       <c r="R53" t="n">
-        <v>6550930</v>
+        <v>6550961</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6699,10 +6637,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130063327</v>
+        <v>130063318</v>
       </c>
       <c r="B54" t="n">
-        <v>5197</v>
+        <v>8451</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6710,27 +6648,27 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6739,10 +6677,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>317333</v>
+        <v>317387</v>
       </c>
       <c r="R54" t="n">
-        <v>6550980</v>
+        <v>6550788</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6788,17 +6726,17 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6816,32 +6754,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130063330</v>
+        <v>130063343</v>
       </c>
       <c r="B55" t="n">
-        <v>91574</v>
+        <v>91623</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6851,10 +6789,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>317408</v>
+        <v>317442</v>
       </c>
       <c r="R55" t="n">
-        <v>6550961</v>
+        <v>6550932</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6928,10 +6866,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130063318</v>
+        <v>130063346</v>
       </c>
       <c r="B56" t="n">
-        <v>8451</v>
+        <v>97097</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6939,39 +6877,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>317387</v>
+        <v>317457</v>
       </c>
       <c r="R56" t="n">
-        <v>6550788</v>
+        <v>6550912</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7014,21 +6947,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7045,32 +6963,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130063336</v>
+        <v>130063344</v>
       </c>
       <c r="B57" t="n">
-        <v>75199</v>
+        <v>97061</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7080,10 +6998,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>317424</v>
+        <v>317456</v>
       </c>
       <c r="R57" t="n">
-        <v>6550930</v>
+        <v>6550897</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7142,32 +7060,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130063353</v>
+        <v>130063319</v>
       </c>
       <c r="B58" t="n">
-        <v>90992</v>
+        <v>97061</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5685</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7177,10 +7095,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>317478</v>
+        <v>317401</v>
       </c>
       <c r="R58" t="n">
-        <v>6550898</v>
+        <v>6550860</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7223,21 +7141,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7254,45 +7157,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130063343</v>
+        <v>130063339</v>
       </c>
       <c r="B59" t="n">
-        <v>91610</v>
+        <v>5197</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>317442</v>
+        <v>317422</v>
       </c>
       <c r="R59" t="n">
-        <v>6550932</v>
+        <v>6550917</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7366,10 +7274,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130063339</v>
+        <v>130063316</v>
       </c>
       <c r="B60" t="n">
-        <v>5197</v>
+        <v>97097</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7377,39 +7285,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>105930</v>
+        <v>2590</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>317422</v>
+        <v>317362</v>
       </c>
       <c r="R60" t="n">
-        <v>6550917</v>
+        <v>6550742</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7452,21 +7355,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7483,10 +7371,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130063346</v>
+        <v>130063321</v>
       </c>
       <c r="B61" t="n">
-        <v>97084</v>
+        <v>92905</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7494,21 +7382,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7518,10 +7406,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>317457</v>
+        <v>317373</v>
       </c>
       <c r="R61" t="n">
-        <v>6550912</v>
+        <v>6550909</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7580,32 +7468,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130063344</v>
+        <v>130063332</v>
       </c>
       <c r="B62" t="n">
-        <v>97048</v>
+        <v>75200</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7615,10 +7503,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>317456</v>
+        <v>317425</v>
       </c>
       <c r="R62" t="n">
-        <v>6550897</v>
+        <v>6550935</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7677,45 +7565,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130063319</v>
+        <v>130063342</v>
       </c>
       <c r="B63" t="n">
-        <v>97048</v>
+        <v>5177</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>317401</v>
+        <v>317442</v>
       </c>
       <c r="R63" t="n">
-        <v>6550860</v>
+        <v>6550932</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7758,6 +7651,21 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7774,10 +7682,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130063321</v>
+        <v>130063317</v>
       </c>
       <c r="B64" t="n">
-        <v>92892</v>
+        <v>8451</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7785,34 +7693,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>317373</v>
+        <v>317378</v>
       </c>
       <c r="R64" t="n">
-        <v>6550909</v>
+        <v>6550754</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7855,6 +7768,21 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7871,10 +7799,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130063316</v>
+        <v>130063341</v>
       </c>
       <c r="B65" t="n">
-        <v>97084</v>
+        <v>5197</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7882,34 +7810,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2590</v>
+        <v>105930</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>317362</v>
+        <v>317442</v>
       </c>
       <c r="R65" t="n">
-        <v>6550742</v>
+        <v>6550932</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7952,6 +7885,21 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7968,7 +7916,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130063341</v>
+        <v>130063352</v>
       </c>
       <c r="B66" t="n">
         <v>5197</v>
@@ -8008,10 +7956,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>317442</v>
+        <v>317471</v>
       </c>
       <c r="R66" t="n">
-        <v>6550932</v>
+        <v>6550898</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8085,10 +8033,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130063332</v>
+        <v>130063348</v>
       </c>
       <c r="B67" t="n">
-        <v>75199</v>
+        <v>75200</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8120,10 +8068,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>317425</v>
+        <v>317459</v>
       </c>
       <c r="R67" t="n">
-        <v>6550935</v>
+        <v>6550959</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8166,6 +8114,21 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8182,10 +8145,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130063342</v>
+        <v>130063354</v>
       </c>
       <c r="B68" t="n">
-        <v>5177</v>
+        <v>92905</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8193,39 +8156,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>317442</v>
+        <v>317491</v>
       </c>
       <c r="R68" t="n">
-        <v>6550932</v>
+        <v>6550822</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8268,21 +8226,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8299,10 +8242,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130063317</v>
+        <v>130063326</v>
       </c>
       <c r="B69" t="n">
-        <v>8451</v>
+        <v>91587</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8310,39 +8253,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>317378</v>
+        <v>317328</v>
       </c>
       <c r="R69" t="n">
-        <v>6550754</v>
+        <v>6550975</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8388,17 +8326,17 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8416,10 +8354,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130063352</v>
+        <v>130063333</v>
       </c>
       <c r="B70" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8427,21 +8365,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8456,10 +8394,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>317471</v>
+        <v>317428</v>
       </c>
       <c r="R70" t="n">
-        <v>6550898</v>
+        <v>6550930</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8533,52 +8471,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129836131</v>
+        <v>130063329</v>
       </c>
       <c r="B71" t="n">
-        <v>91852</v>
+        <v>97436</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5260</v>
+        <v>2569</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>317417</v>
+        <v>317411</v>
       </c>
       <c r="R71" t="n">
-        <v>6550843</v>
+        <v>6550970</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8605,12 +8536,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8619,49 +8550,28 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>Bärljungbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Låga # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130063348</v>
+        <v>130063340</v>
       </c>
       <c r="B72" t="n">
-        <v>75199</v>
+        <v>5177</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8669,21 +8579,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6426</v>
+        <v>100526</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8693,10 +8603,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>317459</v>
+        <v>317439</v>
       </c>
       <c r="R72" t="n">
-        <v>6550959</v>
+        <v>6550940</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8737,23 +8647,9 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8770,10 +8666,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130063354</v>
+        <v>130063335</v>
       </c>
       <c r="B73" t="n">
-        <v>92892</v>
+        <v>92905</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8805,10 +8701,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>317491</v>
+        <v>317426</v>
       </c>
       <c r="R73" t="n">
-        <v>6550822</v>
+        <v>6550926</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8867,10 +8763,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130063326</v>
+        <v>130063328</v>
       </c>
       <c r="B74" t="n">
-        <v>91574</v>
+        <v>80154</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8878,21 +8774,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>229497</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8902,10 +8798,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>317328</v>
+        <v>317351</v>
       </c>
       <c r="R74" t="n">
-        <v>6550975</v>
+        <v>6550971</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8951,17 +8847,17 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8979,50 +8875,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130063333</v>
+        <v>130063337</v>
       </c>
       <c r="B75" t="n">
-        <v>5177</v>
+        <v>97061</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>317428</v>
+        <v>317425</v>
       </c>
       <c r="R75" t="n">
-        <v>6550930</v>
+        <v>6550915</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9065,21 +8956,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9096,10 +8972,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130063329</v>
+        <v>130063351</v>
       </c>
       <c r="B76" t="n">
-        <v>97423</v>
+        <v>75200</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9107,21 +8983,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2569</v>
+        <v>6426</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9131,10 +9007,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>317411</v>
+        <v>317464</v>
       </c>
       <c r="R76" t="n">
-        <v>6550970</v>
+        <v>6550904</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9177,6 +9053,21 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9193,10 +9084,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130063340</v>
+        <v>130063359</v>
       </c>
       <c r="B77" t="n">
-        <v>5177</v>
+        <v>8440</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9204,21 +9095,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9228,10 +9119,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>317439</v>
+        <v>317525</v>
       </c>
       <c r="R77" t="n">
-        <v>6550940</v>
+        <v>6550630</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9272,7 +9163,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9291,10 +9181,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130063337</v>
+        <v>130104814</v>
       </c>
       <c r="B78" t="n">
-        <v>97048</v>
+        <v>78755</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9302,34 +9192,41 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>53</v>
+        <v>353</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Norra Rävmarken, Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>317425</v>
+        <v>317256</v>
       </c>
       <c r="R78" t="n">
-        <v>6550915</v>
+        <v>6550879</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9356,12 +9253,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9370,63 +9267,91 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Ljungtallskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Tommy Solberg</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Tommy Solberg</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130063335</v>
+        <v>130104706</v>
       </c>
       <c r="B79" t="n">
-        <v>92892</v>
+        <v>92265</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>5454</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Norra Rävmarken, Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>317426</v>
+        <v>317258</v>
       </c>
       <c r="R79" t="n">
-        <v>6550926</v>
+        <v>6550918</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9453,12 +9378,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9467,63 +9392,91 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Ljungtallskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Tommy Solberg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Tommy Solberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130063359</v>
+        <v>130104411</v>
       </c>
       <c r="B80" t="n">
-        <v>8440</v>
+        <v>78755</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106554</v>
+        <v>353</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Norra Rävmarken, Dls</t>
+          <t>Mattishöljen N/O., Dls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>317525</v>
+        <v>317444</v>
       </c>
       <c r="R80" t="n">
-        <v>6550630</v>
+        <v>6550749</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9550,12 +9503,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9564,245 +9517,42 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Ljungtallskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Låga # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Tommy Solberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Tommy Solberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>130063351</v>
-      </c>
-      <c r="B81" t="n">
-        <v>75199</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>6426</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Kattfotslav</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Felipes leucopellaeus</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Norra Rävmarken, Dls</t>
-        </is>
-      </c>
-      <c r="Q81" t="n">
-        <v>317464</v>
-      </c>
-      <c r="R81" t="n">
-        <v>6550904</v>
-      </c>
-      <c r="S81" t="n">
-        <v>5</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Dals-Ed</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Dalsland</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Nössemark</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="AD81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT81" t="inlineStr"/>
-      <c r="AW81" t="inlineStr">
-        <is>
-          <t>Anton Larsson</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>Anton Larsson</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>130063328</v>
-      </c>
-      <c r="B82" t="n">
-        <v>80154</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>229497</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Korallblylav</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Parmeliella triptophylla</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Norra Rävmarken, Dls</t>
-        </is>
-      </c>
-      <c r="Q82" t="n">
-        <v>317351</v>
-      </c>
-      <c r="R82" t="n">
-        <v>6550971</v>
-      </c>
-      <c r="S82" t="n">
-        <v>5</v>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Dals-Ed</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Dalsland</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Nössemark</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="AD82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AT82" t="inlineStr"/>
-      <c r="AW82" t="inlineStr">
-        <is>
-          <t>Anton Larsson</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>Anton Larsson</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY90"/>
+  <dimension ref="A1:AY126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3019,10 +3019,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129835838</v>
+        <v>129835710</v>
       </c>
       <c r="B22" t="n">
-        <v>8440</v>
+        <v>43995</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,21 +3030,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106554</v>
+        <v>101735</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3059,14 +3059,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hökelshöljen S., Dls</t>
+          <t>Mattishöljen N/O., Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>317217</v>
+        <v>317372</v>
       </c>
       <c r="R22" t="n">
-        <v>6550953</v>
+        <v>6550741</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3116,19 +3116,9 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Fnöskticka på björk</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3146,10 +3136,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129835710</v>
+        <v>129835838</v>
       </c>
       <c r="B23" t="n">
-        <v>43995</v>
+        <v>8440</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,21 +3147,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101735</v>
+        <v>106554</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3186,14 +3176,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mattishöljen N/O., Dls</t>
+          <t>Hökelshöljen S., Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>317372</v>
+        <v>317217</v>
       </c>
       <c r="R23" t="n">
-        <v>6550741</v>
+        <v>6550953</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3243,9 +3233,19 @@
           <t>Bärljungbarrskog</t>
         </is>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3515,52 +3515,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129835977</v>
+        <v>129835752</v>
       </c>
       <c r="B26" t="n">
-        <v>91912</v>
+        <v>43995</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>65</v>
+        <v>101735</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Lögarehöljen S., Dls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>317373</v>
+        <v>317326</v>
       </c>
       <c r="R26" t="n">
-        <v>6550816</v>
+        <v>6550956</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3612,17 +3614,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3640,54 +3642,52 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129835752</v>
+        <v>129835977</v>
       </c>
       <c r="B27" t="n">
-        <v>43995</v>
+        <v>91912</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101735</v>
+        <v>65</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lögarehöljen S., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>317326</v>
+        <v>317373</v>
       </c>
       <c r="R27" t="n">
-        <v>6550956</v>
+        <v>6550816</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3739,17 +3739,17 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk # Fomes fomentarius</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4736,10 +4736,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130063338</v>
+        <v>130063320</v>
       </c>
       <c r="B36" t="n">
-        <v>75201</v>
+        <v>80160</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4747,21 +4747,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4771,10 +4771,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>317422</v>
+        <v>317410</v>
       </c>
       <c r="R36" t="n">
-        <v>6550917</v>
+        <v>6550877</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4820,17 +4820,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130063320</v>
+        <v>130063338</v>
       </c>
       <c r="B37" t="n">
-        <v>80160</v>
+        <v>75201</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,21 +4859,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>317410</v>
+        <v>317422</v>
       </c>
       <c r="R37" t="n">
-        <v>6550877</v>
+        <v>6550917</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4932,17 +4932,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -6754,32 +6754,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130063319</v>
+        <v>130063346</v>
       </c>
       <c r="B55" t="n">
-        <v>97077</v>
+        <v>97113</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6789,10 +6789,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>317401</v>
+        <v>317457</v>
       </c>
       <c r="R55" t="n">
-        <v>6550860</v>
+        <v>6550912</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6851,10 +6851,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130063344</v>
+        <v>130063343</v>
       </c>
       <c r="B56" t="n">
-        <v>97077</v>
+        <v>91639</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6862,21 +6862,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>317456</v>
+        <v>317442</v>
       </c>
       <c r="R56" t="n">
-        <v>6550897</v>
+        <v>6550932</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6932,6 +6932,21 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6948,32 +6963,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130063346</v>
+        <v>130063319</v>
       </c>
       <c r="B57" t="n">
-        <v>97113</v>
+        <v>97077</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6983,10 +6998,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>317457</v>
+        <v>317401</v>
       </c>
       <c r="R57" t="n">
-        <v>6550912</v>
+        <v>6550860</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7045,10 +7060,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130063343</v>
+        <v>130063344</v>
       </c>
       <c r="B58" t="n">
-        <v>91639</v>
+        <v>97077</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7056,21 +7071,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7080,10 +7095,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>317442</v>
+        <v>317456</v>
       </c>
       <c r="R58" t="n">
-        <v>6550932</v>
+        <v>6550897</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7126,21 +7141,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -10804,6 +10804,3884 @@
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>130210763</v>
+      </c>
+      <c r="B91" t="n">
+        <v>97115</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>317315</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6550994</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>130210762</v>
+      </c>
+      <c r="B92" t="n">
+        <v>97079</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>53</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>317280</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6550981</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>130210755</v>
+      </c>
+      <c r="B93" t="n">
+        <v>91605</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>317405</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6550943</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>130210782</v>
+      </c>
+      <c r="B94" t="n">
+        <v>97079</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>53</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>317282</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6550790</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>130210783</v>
+      </c>
+      <c r="B95" t="n">
+        <v>97115</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>317282</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6550790</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>130210766</v>
+      </c>
+      <c r="B96" t="n">
+        <v>97115</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>317236</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6550997</v>
+      </c>
+      <c r="S96" t="n">
+        <v>5</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>130210781</v>
+      </c>
+      <c r="B97" t="n">
+        <v>97115</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>317275</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6550801</v>
+      </c>
+      <c r="S97" t="n">
+        <v>5</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>130210758</v>
+      </c>
+      <c r="B98" t="n">
+        <v>97454</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>317402</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6550941</v>
+      </c>
+      <c r="S98" t="n">
+        <v>5</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>130210765</v>
+      </c>
+      <c r="B99" t="n">
+        <v>97079</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>53</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>317236</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6550997</v>
+      </c>
+      <c r="S99" t="n">
+        <v>5</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>130210778</v>
+      </c>
+      <c r="B100" t="n">
+        <v>43995</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>317266</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6550821</v>
+      </c>
+      <c r="S100" t="n">
+        <v>5</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>130210753</v>
+      </c>
+      <c r="B101" t="n">
+        <v>75201</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>317414</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6550904</v>
+      </c>
+      <c r="S101" t="n">
+        <v>5</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>130210787</v>
+      </c>
+      <c r="B102" t="n">
+        <v>97115</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>317340</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6550747</v>
+      </c>
+      <c r="S102" t="n">
+        <v>5</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>130210788</v>
+      </c>
+      <c r="B103" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>317340</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6550747</v>
+      </c>
+      <c r="S103" t="n">
+        <v>5</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>130210775</v>
+      </c>
+      <c r="B104" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>317228</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6550896</v>
+      </c>
+      <c r="S104" t="n">
+        <v>5</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>130210776</v>
+      </c>
+      <c r="B105" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>317244</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6550846</v>
+      </c>
+      <c r="S105" t="n">
+        <v>5</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>130210779</v>
+      </c>
+      <c r="B106" t="n">
+        <v>8440</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>317266</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6550821</v>
+      </c>
+      <c r="S106" t="n">
+        <v>5</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>130210772</v>
+      </c>
+      <c r="B107" t="n">
+        <v>8440</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>317242</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6550921</v>
+      </c>
+      <c r="S107" t="n">
+        <v>5</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>130210780</v>
+      </c>
+      <c r="B108" t="n">
+        <v>97079</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>53</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>317275</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6550801</v>
+      </c>
+      <c r="S108" t="n">
+        <v>5</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>130210756</v>
+      </c>
+      <c r="B109" t="n">
+        <v>91605</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>317409</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6550951</v>
+      </c>
+      <c r="S109" t="n">
+        <v>5</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>130210759</v>
+      </c>
+      <c r="B110" t="n">
+        <v>75201</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>317390</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6550928</v>
+      </c>
+      <c r="S110" t="n">
+        <v>5</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>130210789</v>
+      </c>
+      <c r="B111" t="n">
+        <v>97115</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>317326</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6550738</v>
+      </c>
+      <c r="S111" t="n">
+        <v>5</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>130210770</v>
+      </c>
+      <c r="B112" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>317245</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6550930</v>
+      </c>
+      <c r="S112" t="n">
+        <v>5</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>130210769</v>
+      </c>
+      <c r="B113" t="n">
+        <v>97079</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>53</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>317269</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6550970</v>
+      </c>
+      <c r="S113" t="n">
+        <v>5</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>130210790</v>
+      </c>
+      <c r="B114" t="n">
+        <v>97115</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>317336</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6550733</v>
+      </c>
+      <c r="S114" t="n">
+        <v>5</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>130210760</v>
+      </c>
+      <c r="B115" t="n">
+        <v>97079</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>53</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>317334</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6550938</v>
+      </c>
+      <c r="S115" t="n">
+        <v>5</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>130210761</v>
+      </c>
+      <c r="B116" t="n">
+        <v>97115</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>317337</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6550964</v>
+      </c>
+      <c r="S116" t="n">
+        <v>5</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>130210764</v>
+      </c>
+      <c r="B117" t="n">
+        <v>97115</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>317268</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6550998</v>
+      </c>
+      <c r="S117" t="n">
+        <v>5</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>130210777</v>
+      </c>
+      <c r="B118" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>317283</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6550823</v>
+      </c>
+      <c r="S118" t="n">
+        <v>5</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>130210771</v>
+      </c>
+      <c r="B119" t="n">
+        <v>92923</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>317240</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6550922</v>
+      </c>
+      <c r="S119" t="n">
+        <v>5</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>130210786</v>
+      </c>
+      <c r="B120" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>317303</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6550763</v>
+      </c>
+      <c r="S120" t="n">
+        <v>5</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>130210768</v>
+      </c>
+      <c r="B121" t="n">
+        <v>97079</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>53</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>317274</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6550981</v>
+      </c>
+      <c r="S121" t="n">
+        <v>5</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>130210757</v>
+      </c>
+      <c r="B122" t="n">
+        <v>75201</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>317402</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6550941</v>
+      </c>
+      <c r="S122" t="n">
+        <v>5</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>130210752</v>
+      </c>
+      <c r="B123" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>317348</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6550887</v>
+      </c>
+      <c r="S123" t="n">
+        <v>5</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>130210773</v>
+      </c>
+      <c r="B124" t="n">
+        <v>92923</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>317245</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6550914</v>
+      </c>
+      <c r="S124" t="n">
+        <v>5</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>130210754</v>
+      </c>
+      <c r="B125" t="n">
+        <v>75201</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>317405</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6550943</v>
+      </c>
+      <c r="S125" t="n">
+        <v>5</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>130210767</v>
+      </c>
+      <c r="B126" t="n">
+        <v>97115</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>317271</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6550985</v>
+      </c>
+      <c r="S126" t="n">
+        <v>5</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -8666,32 +8666,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130063337</v>
+        <v>130063359</v>
       </c>
       <c r="B73" t="n">
-        <v>97077</v>
+        <v>8440</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>317425</v>
+        <v>317525</v>
       </c>
       <c r="R73" t="n">
-        <v>6550915</v>
+        <v>6550630</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8763,32 +8763,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130063328</v>
+        <v>130063337</v>
       </c>
       <c r="B74" t="n">
-        <v>80160</v>
+        <v>97077</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229497</v>
+        <v>53</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8798,10 +8798,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>317351</v>
+        <v>317425</v>
       </c>
       <c r="R74" t="n">
-        <v>6550971</v>
+        <v>6550915</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8844,21 +8844,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9084,10 +9069,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130063359</v>
+        <v>130063328</v>
       </c>
       <c r="B77" t="n">
-        <v>8440</v>
+        <v>80160</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9095,21 +9080,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106554</v>
+        <v>229497</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9119,10 +9104,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>317525</v>
+        <v>317351</v>
       </c>
       <c r="R77" t="n">
-        <v>6550630</v>
+        <v>6550971</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9165,6 +9150,21 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -10062,38 +10062,38 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130177671</v>
+        <v>130175755</v>
       </c>
       <c r="B85" t="n">
-        <v>75201</v>
+        <v>92425</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6426</v>
+        <v>1975</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Liten kandelabersvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Artomyces cristatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Kauffman) Jülich</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -10104,10 +10104,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>317416</v>
+        <v>317417</v>
       </c>
       <c r="R85" t="n">
-        <v>6550960</v>
+        <v>6550843</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10134,12 +10134,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Mosseblåbärgranskog</t>
+          <t>Bärljungbarrskog</t>
         </is>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>På bark # Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10187,41 +10187,38 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130175755</v>
+        <v>130177191</v>
       </c>
       <c r="B86" t="n">
-        <v>92425</v>
+        <v>97113</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1975</v>
+        <v>2590</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Liten kandelabersvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Artomyces cristatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Kauffman) Jülich</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10229,10 +10226,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>317417</v>
+        <v>317331</v>
       </c>
       <c r="R86" t="n">
-        <v>6550843</v>
+        <v>6550757</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10259,12 +10256,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10279,7 +10276,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Bärljungbarrskog</t>
+          <t>Blåbärgranskog</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -10312,38 +10309,41 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130177191</v>
+        <v>130175870</v>
       </c>
       <c r="B87" t="n">
-        <v>97113</v>
+        <v>92122</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2590</v>
+        <v>5467</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -10351,10 +10351,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>317331</v>
+        <v>317429</v>
       </c>
       <c r="R87" t="n">
-        <v>6550757</v>
+        <v>6550919</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
+          <t>Moseblåbärgranskog</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
@@ -10434,41 +10434,38 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130175870</v>
+        <v>130177180</v>
       </c>
       <c r="B88" t="n">
-        <v>92122</v>
+        <v>97113</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5467</v>
+        <v>2590</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -10476,10 +10473,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>317429</v>
+        <v>317344</v>
       </c>
       <c r="R88" t="n">
-        <v>6550919</v>
+        <v>6550753</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10526,7 +10523,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Moseblåbärgranskog</t>
+          <t>Blåbärgranskog</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
@@ -10559,10 +10556,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130177180</v>
+        <v>130177708</v>
       </c>
       <c r="B89" t="n">
-        <v>97113</v>
+        <v>75201</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10570,27 +10567,30 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>317344</v>
+        <v>317400</v>
       </c>
       <c r="R89" t="n">
-        <v>6550753</v>
+        <v>6550946</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10648,22 +10648,22 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
+          <t>Mosseblåbärgranskog</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>På bark # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10681,10 +10681,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130177708</v>
+        <v>130210763</v>
       </c>
       <c r="B90" t="n">
-        <v>75201</v>
+        <v>97115</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10692,41 +10692,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>317400</v>
+        <v>317315</v>
       </c>
       <c r="R90" t="n">
-        <v>6550946</v>
+        <v>6550994</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10753,12 +10746,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10767,71 +10760,50 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>Mosseblåbärgranskog</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>På bark # Picea abies</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Tommy Solberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130210763</v>
+        <v>130210762</v>
       </c>
       <c r="B91" t="n">
-        <v>97115</v>
+        <v>97079</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10841,10 +10813,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>317315</v>
+        <v>317280</v>
       </c>
       <c r="R91" t="n">
-        <v>6550994</v>
+        <v>6550981</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10903,32 +10875,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130210762</v>
+        <v>130210755</v>
       </c>
       <c r="B92" t="n">
-        <v>97079</v>
+        <v>91605</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10938,10 +10910,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>317280</v>
+        <v>317405</v>
       </c>
       <c r="R92" t="n">
-        <v>6550981</v>
+        <v>6550943</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10984,6 +10956,21 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -11000,32 +10987,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130210755</v>
+        <v>130210782</v>
       </c>
       <c r="B93" t="n">
-        <v>91605</v>
+        <v>97079</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11035,10 +11022,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>317405</v>
+        <v>317282</v>
       </c>
       <c r="R93" t="n">
-        <v>6550943</v>
+        <v>6550790</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11084,17 +11071,17 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11112,32 +11099,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130210782</v>
+        <v>130210783</v>
       </c>
       <c r="B94" t="n">
-        <v>97079</v>
+        <v>97115</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11224,7 +11211,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130210783</v>
+        <v>130210766</v>
       </c>
       <c r="B95" t="n">
         <v>97115</v>
@@ -11259,10 +11246,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>317282</v>
+        <v>317236</v>
       </c>
       <c r="R95" t="n">
-        <v>6550790</v>
+        <v>6550997</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11305,21 +11292,6 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11336,7 +11308,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130210766</v>
+        <v>130210781</v>
       </c>
       <c r="B96" t="n">
         <v>97115</v>
@@ -11371,10 +11343,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>317236</v>
+        <v>317275</v>
       </c>
       <c r="R96" t="n">
-        <v>6550997</v>
+        <v>6550801</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11415,8 +11387,24 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11433,10 +11421,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>130210781</v>
+        <v>130210758</v>
       </c>
       <c r="B97" t="n">
-        <v>97115</v>
+        <v>97454</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11444,21 +11432,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2590</v>
+        <v>2569</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11468,10 +11456,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>317275</v>
+        <v>317402</v>
       </c>
       <c r="R97" t="n">
-        <v>6550801</v>
+        <v>6550941</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11512,24 +11500,8 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -11546,32 +11518,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130210758</v>
+        <v>130210765</v>
       </c>
       <c r="B98" t="n">
-        <v>97454</v>
+        <v>97079</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2569</v>
+        <v>53</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11581,10 +11553,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>317402</v>
+        <v>317236</v>
       </c>
       <c r="R98" t="n">
-        <v>6550941</v>
+        <v>6550997</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11643,45 +11615,54 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130210765</v>
+        <v>130210778</v>
       </c>
       <c r="B99" t="n">
-        <v>97079</v>
+        <v>43995</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>53</v>
+        <v>101735</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>317236</v>
+        <v>317266</v>
       </c>
       <c r="R99" t="n">
-        <v>6550997</v>
+        <v>6550821</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11722,6 +11703,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11740,10 +11722,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130210778</v>
+        <v>130210753</v>
       </c>
       <c r="B100" t="n">
-        <v>43995</v>
+        <v>75201</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11751,43 +11733,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>101735</v>
+        <v>6426</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>317266</v>
+        <v>317414</v>
       </c>
       <c r="R100" t="n">
-        <v>6550821</v>
+        <v>6550904</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11828,9 +11801,23 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11847,10 +11834,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130210753</v>
+        <v>130210787</v>
       </c>
       <c r="B101" t="n">
-        <v>75201</v>
+        <v>97115</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11858,21 +11845,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11882,10 +11869,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>317414</v>
+        <v>317340</v>
       </c>
       <c r="R101" t="n">
-        <v>6550904</v>
+        <v>6550747</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11931,17 +11918,17 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -11959,10 +11946,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130210787</v>
+        <v>130210788</v>
       </c>
       <c r="B102" t="n">
-        <v>97115</v>
+        <v>8451</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11970,24 +11957,29 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
@@ -12071,7 +12063,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130210788</v>
+        <v>130210775</v>
       </c>
       <c r="B103" t="n">
         <v>8451</v>
@@ -12111,10 +12103,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>317340</v>
+        <v>317228</v>
       </c>
       <c r="R103" t="n">
-        <v>6550747</v>
+        <v>6550896</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12188,7 +12180,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130210775</v>
+        <v>130210776</v>
       </c>
       <c r="B104" t="n">
         <v>8451</v>
@@ -12228,10 +12220,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>317228</v>
+        <v>317244</v>
       </c>
       <c r="R104" t="n">
-        <v>6550896</v>
+        <v>6550846</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12305,10 +12297,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130210776</v>
+        <v>130210779</v>
       </c>
       <c r="B105" t="n">
-        <v>8451</v>
+        <v>8440</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12316,21 +12308,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12345,10 +12337,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>317244</v>
+        <v>317266</v>
       </c>
       <c r="R105" t="n">
-        <v>6550846</v>
+        <v>6550821</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12394,17 +12386,17 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>vårtbjörk</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pendula</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula pendula</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12422,7 +12414,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130210779</v>
+        <v>130210772</v>
       </c>
       <c r="B106" t="n">
         <v>8440</v>
@@ -12462,10 +12454,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>317266</v>
+        <v>317242</v>
       </c>
       <c r="R106" t="n">
-        <v>6550821</v>
+        <v>6550921</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12539,50 +12531,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>130210772</v>
+        <v>130210780</v>
       </c>
       <c r="B107" t="n">
-        <v>8440</v>
+        <v>97079</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>317242</v>
+        <v>317275</v>
       </c>
       <c r="R107" t="n">
-        <v>6550921</v>
+        <v>6550801</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12628,17 +12615,17 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>vårtbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12656,32 +12643,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130210780</v>
+        <v>130210756</v>
       </c>
       <c r="B108" t="n">
-        <v>97079</v>
+        <v>91605</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12691,10 +12678,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>317275</v>
+        <v>317409</v>
       </c>
       <c r="R108" t="n">
-        <v>6550801</v>
+        <v>6550951</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12740,17 +12727,17 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12768,10 +12755,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130210756</v>
+        <v>130210759</v>
       </c>
       <c r="B109" t="n">
-        <v>91605</v>
+        <v>75201</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12779,21 +12766,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12803,10 +12790,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>317409</v>
+        <v>317390</v>
       </c>
       <c r="R109" t="n">
-        <v>6550951</v>
+        <v>6550928</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12880,10 +12867,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130210759</v>
+        <v>130210789</v>
       </c>
       <c r="B110" t="n">
-        <v>75201</v>
+        <v>97115</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12891,21 +12878,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12915,10 +12902,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>317390</v>
+        <v>317326</v>
       </c>
       <c r="R110" t="n">
-        <v>6550928</v>
+        <v>6550738</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12961,21 +12948,6 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
@@ -12992,10 +12964,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>130210789</v>
+        <v>130210770</v>
       </c>
       <c r="B111" t="n">
-        <v>97115</v>
+        <v>8451</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13003,34 +12975,39 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>317326</v>
+        <v>317245</v>
       </c>
       <c r="R111" t="n">
-        <v>6550738</v>
+        <v>6550930</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -13073,6 +13050,21 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
@@ -13089,50 +13081,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130210770</v>
+        <v>130210769</v>
       </c>
       <c r="B112" t="n">
-        <v>8451</v>
+        <v>97079</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>317245</v>
+        <v>317269</v>
       </c>
       <c r="R112" t="n">
-        <v>6550930</v>
+        <v>6550970</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13206,32 +13193,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130210769</v>
+        <v>130210790</v>
       </c>
       <c r="B113" t="n">
-        <v>97079</v>
+        <v>97115</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13241,10 +13228,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>317269</v>
+        <v>317336</v>
       </c>
       <c r="R113" t="n">
-        <v>6550970</v>
+        <v>6550733</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13287,21 +13274,6 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
@@ -13318,32 +13290,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130210790</v>
+        <v>130210760</v>
       </c>
       <c r="B114" t="n">
-        <v>97115</v>
+        <v>97079</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13353,10 +13325,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>317336</v>
+        <v>317334</v>
       </c>
       <c r="R114" t="n">
-        <v>6550733</v>
+        <v>6550938</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13415,32 +13387,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130210760</v>
+        <v>130210761</v>
       </c>
       <c r="B115" t="n">
-        <v>97079</v>
+        <v>97115</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13450,10 +13422,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>317334</v>
+        <v>317337</v>
       </c>
       <c r="R115" t="n">
-        <v>6550938</v>
+        <v>6550964</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13512,7 +13484,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130210761</v>
+        <v>130210764</v>
       </c>
       <c r="B116" t="n">
         <v>97115</v>
@@ -13547,10 +13519,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>317337</v>
+        <v>317268</v>
       </c>
       <c r="R116" t="n">
-        <v>6550964</v>
+        <v>6550998</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13609,10 +13581,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130210764</v>
+        <v>130210777</v>
       </c>
       <c r="B117" t="n">
-        <v>97115</v>
+        <v>8451</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13620,34 +13592,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>317268</v>
+        <v>317283</v>
       </c>
       <c r="R117" t="n">
-        <v>6550998</v>
+        <v>6550823</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13706,10 +13683,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130210777</v>
+        <v>130210771</v>
       </c>
       <c r="B118" t="n">
-        <v>8451</v>
+        <v>92923</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13717,39 +13694,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>317283</v>
+        <v>317240</v>
       </c>
       <c r="R118" t="n">
-        <v>6550823</v>
+        <v>6550922</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13808,10 +13780,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130210771</v>
+        <v>130210786</v>
       </c>
       <c r="B119" t="n">
-        <v>92923</v>
+        <v>8451</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13819,34 +13791,39 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>317240</v>
+        <v>317303</v>
       </c>
       <c r="R119" t="n">
-        <v>6550922</v>
+        <v>6550763</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13889,6 +13866,21 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
@@ -13905,50 +13897,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130210786</v>
+        <v>130210768</v>
       </c>
       <c r="B120" t="n">
-        <v>8451</v>
+        <v>97079</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>317303</v>
+        <v>317274</v>
       </c>
       <c r="R120" t="n">
-        <v>6550763</v>
+        <v>6550981</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -14022,32 +14009,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130210768</v>
+        <v>130210757</v>
       </c>
       <c r="B121" t="n">
-        <v>97079</v>
+        <v>75201</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14057,10 +14044,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>317274</v>
+        <v>317402</v>
       </c>
       <c r="R121" t="n">
-        <v>6550981</v>
+        <v>6550941</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14106,17 +14093,17 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14134,10 +14121,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130210757</v>
+        <v>130210752</v>
       </c>
       <c r="B122" t="n">
-        <v>75201</v>
+        <v>8451</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14145,34 +14132,39 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6426</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>317402</v>
+        <v>317348</v>
       </c>
       <c r="R122" t="n">
-        <v>6550941</v>
+        <v>6550887</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14218,17 +14210,17 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -14246,10 +14238,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130210752</v>
+        <v>130210773</v>
       </c>
       <c r="B123" t="n">
-        <v>8451</v>
+        <v>92923</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14257,39 +14249,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>317348</v>
+        <v>317245</v>
       </c>
       <c r="R123" t="n">
-        <v>6550887</v>
+        <v>6550914</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -14332,21 +14319,6 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
@@ -14363,10 +14335,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130210773</v>
+        <v>130210754</v>
       </c>
       <c r="B124" t="n">
-        <v>92923</v>
+        <v>75201</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14374,21 +14346,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4364</v>
+        <v>6426</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14398,10 +14370,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>317245</v>
+        <v>317405</v>
       </c>
       <c r="R124" t="n">
-        <v>6550914</v>
+        <v>6550943</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14444,6 +14416,21 @@
       </c>
       <c r="AG124" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
@@ -14460,10 +14447,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130210754</v>
+        <v>130210767</v>
       </c>
       <c r="B125" t="n">
-        <v>75201</v>
+        <v>97115</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14471,21 +14458,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14495,10 +14482,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>317405</v>
+        <v>317271</v>
       </c>
       <c r="R125" t="n">
-        <v>6550943</v>
+        <v>6550985</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14544,17 +14531,17 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -14572,10 +14559,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130210767</v>
+        <v>130177671</v>
       </c>
       <c r="B126" t="n">
-        <v>97115</v>
+        <v>75201</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14583,34 +14570,41 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>O om Pengehöljen, Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>317271</v>
+        <v>317416</v>
       </c>
       <c r="R126" t="n">
-        <v>6550985</v>
+        <v>6550960</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -14637,12 +14631,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14651,33 +14645,39 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>Mosseblåbärgranskog</t>
+        </is>
+      </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>På bark # Picea abies</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Tommy Solberg</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Tommy Solberg</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -2776,7 +2776,7 @@
         <v>129835851</v>
       </c>
       <c r="B20" t="n">
-        <v>91660</v>
+        <v>91662</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>129835991</v>
       </c>
       <c r="B24" t="n">
-        <v>91449</v>
+        <v>91451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3515,54 +3515,52 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129835752</v>
+        <v>129835977</v>
       </c>
       <c r="B26" t="n">
-        <v>43995</v>
+        <v>91914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>101735</v>
+        <v>65</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lögarehöljen S., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>317326</v>
+        <v>317373</v>
       </c>
       <c r="R26" t="n">
-        <v>6550956</v>
+        <v>6550816</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3614,17 +3612,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk # Fomes fomentarius</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3642,41 +3640,43 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129835977</v>
+        <v>129835803</v>
       </c>
       <c r="B27" t="n">
-        <v>91912</v>
+        <v>8451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>65</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3684,10 +3684,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>317373</v>
+        <v>317185</v>
       </c>
       <c r="R27" t="n">
-        <v>6550816</v>
+        <v>6550868</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3767,10 +3767,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129835803</v>
+        <v>129835752</v>
       </c>
       <c r="B28" t="n">
-        <v>8451</v>
+        <v>43995</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3778,21 +3778,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>101735</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3807,14 +3807,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Lögarehöljen S., Dls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>317185</v>
+        <v>317326</v>
       </c>
       <c r="R28" t="n">
-        <v>6550868</v>
+        <v>6550956</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3866,17 +3866,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4530,7 +4530,7 @@
         <v>130072825</v>
       </c>
       <c r="B34" t="n">
-        <v>97077</v>
+        <v>97079</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>130063324</v>
       </c>
       <c r="B38" t="n">
-        <v>97113</v>
+        <v>97115</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>130063325</v>
       </c>
       <c r="B39" t="n">
-        <v>97113</v>
+        <v>97115</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>130063358</v>
       </c>
       <c r="B40" t="n">
-        <v>97113</v>
+        <v>97115</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>130063356</v>
       </c>
       <c r="B41" t="n">
-        <v>92921</v>
+        <v>92923</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5348,10 +5348,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130063322</v>
+        <v>130063331</v>
       </c>
       <c r="B42" t="n">
-        <v>80160</v>
+        <v>97454</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5359,21 +5359,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229497</v>
+        <v>2569</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5383,10 +5383,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>317366</v>
+        <v>317408</v>
       </c>
       <c r="R42" t="n">
-        <v>6550944</v>
+        <v>6550956</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5429,21 +5429,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5562,10 +5547,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130063331</v>
+        <v>130063322</v>
       </c>
       <c r="B44" t="n">
-        <v>97452</v>
+        <v>80160</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5573,21 +5558,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2569</v>
+        <v>229497</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5597,10 +5582,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>317408</v>
+        <v>317366</v>
       </c>
       <c r="R44" t="n">
-        <v>6550956</v>
+        <v>6550944</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5643,6 +5628,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5662,7 +5662,7 @@
         <v>130063350</v>
       </c>
       <c r="B45" t="n">
-        <v>91021</v>
+        <v>91023</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5888,10 +5888,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130063345</v>
+        <v>130063323</v>
       </c>
       <c r="B47" t="n">
-        <v>97113</v>
+        <v>75201</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5899,21 +5899,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>317456</v>
+        <v>317366</v>
       </c>
       <c r="R47" t="n">
-        <v>6550897</v>
+        <v>6550944</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5985,10 +5985,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130063323</v>
+        <v>130063345</v>
       </c>
       <c r="B48" t="n">
-        <v>75201</v>
+        <v>97115</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5996,21 +5996,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6020,10 +6020,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>317366</v>
+        <v>317456</v>
       </c>
       <c r="R48" t="n">
-        <v>6550944</v>
+        <v>6550897</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6316,10 +6316,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130063353</v>
+        <v>130063336</v>
       </c>
       <c r="B51" t="n">
-        <v>91021</v>
+        <v>75201</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6327,21 +6327,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5685</v>
+        <v>6426</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>317478</v>
+        <v>317424</v>
       </c>
       <c r="R51" t="n">
-        <v>6550898</v>
+        <v>6550930</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6397,21 +6397,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6428,10 +6413,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130063330</v>
+        <v>130063353</v>
       </c>
       <c r="B52" t="n">
-        <v>91603</v>
+        <v>91023</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6439,21 +6424,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>5685</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6463,10 +6448,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>317408</v>
+        <v>317478</v>
       </c>
       <c r="R52" t="n">
-        <v>6550961</v>
+        <v>6550898</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6512,17 +6497,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6540,10 +6525,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130063318</v>
+        <v>130063330</v>
       </c>
       <c r="B53" t="n">
-        <v>8451</v>
+        <v>91605</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6551,39 +6536,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>317387</v>
+        <v>317408</v>
       </c>
       <c r="R53" t="n">
-        <v>6550788</v>
+        <v>6550961</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6629,17 +6609,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6657,10 +6637,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130063336</v>
+        <v>130063318</v>
       </c>
       <c r="B54" t="n">
-        <v>75201</v>
+        <v>8451</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6668,34 +6648,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6426</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>317424</v>
+        <v>317387</v>
       </c>
       <c r="R54" t="n">
-        <v>6550930</v>
+        <v>6550788</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6738,6 +6723,21 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6754,32 +6754,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130063346</v>
+        <v>130063343</v>
       </c>
       <c r="B55" t="n">
-        <v>97113</v>
+        <v>91641</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2590</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6789,10 +6789,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>317457</v>
+        <v>317442</v>
       </c>
       <c r="R55" t="n">
-        <v>6550912</v>
+        <v>6550932</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6835,6 +6835,21 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6851,10 +6866,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130063343</v>
+        <v>130063319</v>
       </c>
       <c r="B56" t="n">
-        <v>91639</v>
+        <v>97079</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6862,21 +6877,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6886,10 +6901,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>317442</v>
+        <v>317401</v>
       </c>
       <c r="R56" t="n">
-        <v>6550932</v>
+        <v>6550860</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6932,21 +6947,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6963,10 +6963,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130063319</v>
+        <v>130063344</v>
       </c>
       <c r="B57" t="n">
-        <v>97077</v>
+        <v>97079</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6998,10 +6998,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>317401</v>
+        <v>317456</v>
       </c>
       <c r="R57" t="n">
-        <v>6550860</v>
+        <v>6550897</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7060,32 +7060,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130063344</v>
+        <v>130063346</v>
       </c>
       <c r="B58" t="n">
-        <v>97077</v>
+        <v>97115</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7095,10 +7095,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>317456</v>
+        <v>317457</v>
       </c>
       <c r="R58" t="n">
-        <v>6550897</v>
+        <v>6550912</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7274,10 +7274,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130063316</v>
+        <v>130063321</v>
       </c>
       <c r="B60" t="n">
-        <v>97113</v>
+        <v>92923</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7285,21 +7285,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7309,10 +7309,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>317362</v>
+        <v>317373</v>
       </c>
       <c r="R60" t="n">
-        <v>6550742</v>
+        <v>6550909</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7371,10 +7371,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130063321</v>
+        <v>130063316</v>
       </c>
       <c r="B61" t="n">
-        <v>92921</v>
+        <v>97115</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7382,21 +7382,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7406,10 +7406,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>317373</v>
+        <v>317362</v>
       </c>
       <c r="R61" t="n">
-        <v>6550909</v>
+        <v>6550742</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7468,10 +7468,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130063332</v>
+        <v>130063342</v>
       </c>
       <c r="B62" t="n">
-        <v>75201</v>
+        <v>5177</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7479,34 +7479,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6426</v>
+        <v>100526</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>317425</v>
+        <v>317442</v>
       </c>
       <c r="R62" t="n">
-        <v>6550935</v>
+        <v>6550932</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7549,6 +7554,21 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7565,10 +7585,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130063342</v>
+        <v>130063332</v>
       </c>
       <c r="B63" t="n">
-        <v>5177</v>
+        <v>75201</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7576,39 +7596,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100526</v>
+        <v>6426</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>317442</v>
+        <v>317425</v>
       </c>
       <c r="R63" t="n">
-        <v>6550932</v>
+        <v>6550935</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7651,21 +7666,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7682,10 +7682,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130063341</v>
+        <v>130063317</v>
       </c>
       <c r="B64" t="n">
-        <v>5197</v>
+        <v>8451</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7693,27 +7693,27 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7722,10 +7722,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>317442</v>
+        <v>317378</v>
       </c>
       <c r="R64" t="n">
-        <v>6550932</v>
+        <v>6550754</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7771,17 +7771,17 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7799,10 +7799,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130063317</v>
+        <v>130063341</v>
       </c>
       <c r="B65" t="n">
-        <v>8451</v>
+        <v>5197</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7810,27 +7810,27 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>317378</v>
+        <v>317442</v>
       </c>
       <c r="R65" t="n">
-        <v>6550754</v>
+        <v>6550932</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7888,17 +7888,17 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8145,10 +8145,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130063326</v>
+        <v>130063333</v>
       </c>
       <c r="B68" t="n">
-        <v>91603</v>
+        <v>5177</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8156,34 +8156,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>317328</v>
+        <v>317428</v>
       </c>
       <c r="R68" t="n">
-        <v>6550975</v>
+        <v>6550930</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8257,10 +8262,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130063333</v>
+        <v>130063326</v>
       </c>
       <c r="B69" t="n">
-        <v>5177</v>
+        <v>91605</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8268,39 +8273,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>317428</v>
+        <v>317328</v>
       </c>
       <c r="R69" t="n">
-        <v>6550930</v>
+        <v>6550975</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8377,7 +8377,7 @@
         <v>130063354</v>
       </c>
       <c r="B70" t="n">
-        <v>92921</v>
+        <v>92923</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8471,10 +8471,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130063329</v>
+        <v>130063340</v>
       </c>
       <c r="B71" t="n">
-        <v>97452</v>
+        <v>5177</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8482,21 +8482,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2569</v>
+        <v>100526</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8506,10 +8506,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>317411</v>
+        <v>317439</v>
       </c>
       <c r="R71" t="n">
-        <v>6550970</v>
+        <v>6550940</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8550,6 +8550,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8568,10 +8569,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130063340</v>
+        <v>130063329</v>
       </c>
       <c r="B72" t="n">
-        <v>5177</v>
+        <v>97454</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8579,21 +8580,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100526</v>
+        <v>2569</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8603,10 +8604,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>317439</v>
+        <v>317411</v>
       </c>
       <c r="R72" t="n">
-        <v>6550940</v>
+        <v>6550970</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8647,7 +8648,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8666,10 +8666,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130063359</v>
+        <v>130063351</v>
       </c>
       <c r="B73" t="n">
-        <v>8440</v>
+        <v>75201</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8677,21 +8677,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106554</v>
+        <v>6426</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>317525</v>
+        <v>317464</v>
       </c>
       <c r="R73" t="n">
-        <v>6550630</v>
+        <v>6550904</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8747,6 +8747,21 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8763,32 +8778,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130063337</v>
+        <v>130063335</v>
       </c>
       <c r="B74" t="n">
-        <v>97077</v>
+        <v>92923</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8798,10 +8813,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>317425</v>
+        <v>317426</v>
       </c>
       <c r="R74" t="n">
-        <v>6550915</v>
+        <v>6550926</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8860,10 +8875,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130063351</v>
+        <v>130063359</v>
       </c>
       <c r="B75" t="n">
-        <v>75201</v>
+        <v>8440</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8871,21 +8886,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6426</v>
+        <v>106554</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8895,10 +8910,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>317464</v>
+        <v>317525</v>
       </c>
       <c r="R75" t="n">
-        <v>6550904</v>
+        <v>6550630</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8941,21 +8956,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -8972,32 +8972,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130063335</v>
+        <v>130063337</v>
       </c>
       <c r="B76" t="n">
-        <v>92921</v>
+        <v>97079</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9007,10 +9007,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>317426</v>
+        <v>317425</v>
       </c>
       <c r="R76" t="n">
-        <v>6550926</v>
+        <v>6550915</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9309,7 +9309,7 @@
         <v>130104706</v>
       </c>
       <c r="B79" t="n">
-        <v>92281</v>
+        <v>92283</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>130177344</v>
       </c>
       <c r="B84" t="n">
-        <v>97113</v>
+        <v>97115</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>130175755</v>
       </c>
       <c r="B85" t="n">
-        <v>92425</v>
+        <v>92427</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10187,38 +10187,41 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130177191</v>
+        <v>130175870</v>
       </c>
       <c r="B86" t="n">
-        <v>97113</v>
+        <v>92124</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2590</v>
+        <v>5467</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10226,10 +10229,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>317331</v>
+        <v>317429</v>
       </c>
       <c r="R86" t="n">
-        <v>6550757</v>
+        <v>6550919</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10276,7 +10279,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
+          <t>Moseblåbärgranskog</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -10309,41 +10312,38 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130175870</v>
+        <v>130177191</v>
       </c>
       <c r="B87" t="n">
-        <v>92122</v>
+        <v>97115</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5467</v>
+        <v>2590</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -10351,10 +10351,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>317429</v>
+        <v>317331</v>
       </c>
       <c r="R87" t="n">
-        <v>6550919</v>
+        <v>6550757</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Moseblåbärgranskog</t>
+          <t>Blåbärgranskog</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
@@ -10437,7 +10437,7 @@
         <v>130177180</v>
       </c>
       <c r="B88" t="n">
-        <v>97113</v>
+        <v>97115</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10875,32 +10875,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130210755</v>
+        <v>130210782</v>
       </c>
       <c r="B92" t="n">
-        <v>91605</v>
+        <v>97079</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10910,10 +10910,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>317405</v>
+        <v>317282</v>
       </c>
       <c r="R92" t="n">
-        <v>6550943</v>
+        <v>6550790</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10959,17 +10959,17 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -10987,32 +10987,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130210782</v>
+        <v>130210755</v>
       </c>
       <c r="B93" t="n">
-        <v>97079</v>
+        <v>91605</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11022,10 +11022,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>317282</v>
+        <v>317405</v>
       </c>
       <c r="R93" t="n">
-        <v>6550790</v>
+        <v>6550943</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11071,17 +11071,17 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -12867,32 +12867,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130210789</v>
+        <v>130210769</v>
       </c>
       <c r="B110" t="n">
-        <v>97115</v>
+        <v>97079</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12902,10 +12902,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>317326</v>
+        <v>317269</v>
       </c>
       <c r="R110" t="n">
-        <v>6550738</v>
+        <v>6550970</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12948,6 +12948,21 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
@@ -12964,10 +12979,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>130210770</v>
+        <v>130210789</v>
       </c>
       <c r="B111" t="n">
-        <v>8451</v>
+        <v>97115</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12975,39 +12990,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>317245</v>
+        <v>317326</v>
       </c>
       <c r="R111" t="n">
-        <v>6550930</v>
+        <v>6550738</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -13050,21 +13060,6 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
@@ -13081,45 +13076,50 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130210769</v>
+        <v>130210770</v>
       </c>
       <c r="B112" t="n">
-        <v>97079</v>
+        <v>8451</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>317269</v>
+        <v>317245</v>
       </c>
       <c r="R112" t="n">
-        <v>6550970</v>
+        <v>6550930</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13193,32 +13193,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130210790</v>
+        <v>130210760</v>
       </c>
       <c r="B113" t="n">
-        <v>97115</v>
+        <v>97079</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13228,10 +13228,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>317336</v>
+        <v>317334</v>
       </c>
       <c r="R113" t="n">
-        <v>6550733</v>
+        <v>6550938</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13290,32 +13290,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130210760</v>
+        <v>130210790</v>
       </c>
       <c r="B114" t="n">
-        <v>97079</v>
+        <v>97115</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13325,10 +13325,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>317334</v>
+        <v>317336</v>
       </c>
       <c r="R114" t="n">
-        <v>6550938</v>
+        <v>6550733</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13387,7 +13387,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130210761</v>
+        <v>130210764</v>
       </c>
       <c r="B115" t="n">
         <v>97115</v>
@@ -13422,10 +13422,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>317337</v>
+        <v>317268</v>
       </c>
       <c r="R115" t="n">
-        <v>6550964</v>
+        <v>6550998</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13484,7 +13484,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130210764</v>
+        <v>130210761</v>
       </c>
       <c r="B116" t="n">
         <v>97115</v>
@@ -13519,10 +13519,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>317268</v>
+        <v>317337</v>
       </c>
       <c r="R116" t="n">
-        <v>6550998</v>
+        <v>6550964</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13581,10 +13581,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130210777</v>
+        <v>130210771</v>
       </c>
       <c r="B117" t="n">
-        <v>8451</v>
+        <v>92923</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13592,39 +13592,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>317283</v>
+        <v>317240</v>
       </c>
       <c r="R117" t="n">
-        <v>6550823</v>
+        <v>6550922</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13683,10 +13678,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130210771</v>
+        <v>130210777</v>
       </c>
       <c r="B118" t="n">
-        <v>92923</v>
+        <v>8451</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13694,34 +13689,39 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>317240</v>
+        <v>317283</v>
       </c>
       <c r="R118" t="n">
-        <v>6550922</v>
+        <v>6550823</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13897,45 +13897,50 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130210768</v>
+        <v>130210752</v>
       </c>
       <c r="B120" t="n">
-        <v>97079</v>
+        <v>8451</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>317274</v>
+        <v>317348</v>
       </c>
       <c r="R120" t="n">
-        <v>6550981</v>
+        <v>6550887</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -14121,50 +14126,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130210752</v>
+        <v>130210768</v>
       </c>
       <c r="B122" t="n">
-        <v>8451</v>
+        <v>97079</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>317348</v>
+        <v>317274</v>
       </c>
       <c r="R122" t="n">
-        <v>6550887</v>
+        <v>6550981</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14335,10 +14335,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130210754</v>
+        <v>130210767</v>
       </c>
       <c r="B124" t="n">
-        <v>75201</v>
+        <v>97115</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14346,21 +14346,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14370,10 +14370,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>317405</v>
+        <v>317271</v>
       </c>
       <c r="R124" t="n">
-        <v>6550943</v>
+        <v>6550985</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14419,17 +14419,17 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -14447,10 +14447,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130210767</v>
+        <v>130210754</v>
       </c>
       <c r="B125" t="n">
-        <v>97115</v>
+        <v>75201</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14458,21 +14458,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14482,10 +14482,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>317271</v>
+        <v>317405</v>
       </c>
       <c r="R125" t="n">
-        <v>6550985</v>
+        <v>6550943</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14531,17 +14531,17 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -2776,7 +2776,7 @@
         <v>129835851</v>
       </c>
       <c r="B20" t="n">
-        <v>91662</v>
+        <v>91749</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>129835710</v>
       </c>
       <c r="B22" t="n">
-        <v>43995</v>
+        <v>44080</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>129835991</v>
       </c>
       <c r="B24" t="n">
-        <v>91451</v>
+        <v>91538</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>129835737</v>
       </c>
       <c r="B25" t="n">
-        <v>43995</v>
+        <v>44080</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>129835977</v>
       </c>
       <c r="B26" t="n">
-        <v>91914</v>
+        <v>92001</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129835803</v>
+        <v>129835752</v>
       </c>
       <c r="B27" t="n">
-        <v>8451</v>
+        <v>44080</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3651,21 +3651,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>101735</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3680,14 +3680,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Lögarehöljen S., Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>317185</v>
+        <v>317326</v>
       </c>
       <c r="R27" t="n">
-        <v>6550868</v>
+        <v>6550956</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3739,17 +3739,17 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3767,10 +3767,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129835752</v>
+        <v>129835803</v>
       </c>
       <c r="B28" t="n">
-        <v>43995</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3778,21 +3778,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101735</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3807,14 +3807,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lögarehöljen S., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>317326</v>
+        <v>317185</v>
       </c>
       <c r="R28" t="n">
-        <v>6550956</v>
+        <v>6550868</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3866,17 +3866,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk # Fomes fomentarius</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4151,7 +4151,7 @@
         <v>129835724</v>
       </c>
       <c r="B31" t="n">
-        <v>43995</v>
+        <v>44080</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>129607603</v>
       </c>
       <c r="B33" t="n">
-        <v>78761</v>
+        <v>78846</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>130072825</v>
       </c>
       <c r="B34" t="n">
-        <v>97079</v>
+        <v>97166</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>130063347</v>
       </c>
       <c r="B35" t="n">
-        <v>75201</v>
+        <v>75286</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4736,10 +4736,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130063320</v>
+        <v>130063338</v>
       </c>
       <c r="B36" t="n">
-        <v>80160</v>
+        <v>75286</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4747,21 +4747,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4771,10 +4771,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>317410</v>
+        <v>317422</v>
       </c>
       <c r="R36" t="n">
-        <v>6550877</v>
+        <v>6550917</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4820,17 +4820,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130063338</v>
+        <v>130063320</v>
       </c>
       <c r="B37" t="n">
-        <v>75201</v>
+        <v>80245</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,21 +4859,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>317422</v>
+        <v>317410</v>
       </c>
       <c r="R37" t="n">
-        <v>6550917</v>
+        <v>6550877</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4932,17 +4932,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4963,7 +4963,7 @@
         <v>130063324</v>
       </c>
       <c r="B38" t="n">
-        <v>97115</v>
+        <v>97202</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>130063325</v>
       </c>
       <c r="B39" t="n">
-        <v>97115</v>
+        <v>97202</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5154,10 +5154,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130063358</v>
+        <v>130063356</v>
       </c>
       <c r="B40" t="n">
-        <v>97115</v>
+        <v>93010</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5165,21 +5165,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>317521</v>
+        <v>317537</v>
       </c>
       <c r="R40" t="n">
-        <v>6550632</v>
+        <v>6550669</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5251,10 +5251,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130063356</v>
+        <v>130063358</v>
       </c>
       <c r="B41" t="n">
-        <v>92923</v>
+        <v>97202</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5262,21 +5262,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5286,10 +5286,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>317537</v>
+        <v>317521</v>
       </c>
       <c r="R41" t="n">
-        <v>6550669</v>
+        <v>6550632</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5351,7 +5351,7 @@
         <v>130063331</v>
       </c>
       <c r="B42" t="n">
-        <v>97454</v>
+        <v>97541</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5445,10 +5445,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130063357</v>
+        <v>130063322</v>
       </c>
       <c r="B43" t="n">
-        <v>56931</v>
+        <v>80245</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5456,39 +5456,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>229497</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>317515</v>
+        <v>317366</v>
       </c>
       <c r="R43" t="n">
-        <v>6550638</v>
+        <v>6550944</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5531,6 +5526,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5547,10 +5557,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130063322</v>
+        <v>130063357</v>
       </c>
       <c r="B44" t="n">
-        <v>80160</v>
+        <v>57016</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5558,34 +5568,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>317366</v>
+        <v>317515</v>
       </c>
       <c r="R44" t="n">
-        <v>6550944</v>
+        <v>6550638</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5628,21 +5643,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5662,7 +5662,7 @@
         <v>130063350</v>
       </c>
       <c r="B45" t="n">
-        <v>91023</v>
+        <v>91110</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>130063323</v>
       </c>
       <c r="B47" t="n">
-        <v>75201</v>
+        <v>75286</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>130063345</v>
       </c>
       <c r="B48" t="n">
-        <v>97115</v>
+        <v>97202</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>130063336</v>
       </c>
       <c r="B51" t="n">
-        <v>75201</v>
+        <v>75286</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6413,10 +6413,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130063353</v>
+        <v>130063330</v>
       </c>
       <c r="B52" t="n">
-        <v>91023</v>
+        <v>91692</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6424,21 +6424,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5685</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6448,10 +6448,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>317478</v>
+        <v>317408</v>
       </c>
       <c r="R52" t="n">
-        <v>6550898</v>
+        <v>6550961</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6497,17 +6497,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6525,10 +6525,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130063330</v>
+        <v>130063318</v>
       </c>
       <c r="B53" t="n">
-        <v>91605</v>
+        <v>8451</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6536,34 +6536,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>317408</v>
+        <v>317387</v>
       </c>
       <c r="R53" t="n">
-        <v>6550961</v>
+        <v>6550788</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6609,17 +6614,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6637,10 +6642,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130063318</v>
+        <v>130063353</v>
       </c>
       <c r="B54" t="n">
-        <v>8451</v>
+        <v>91110</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6648,39 +6653,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>5685</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>317387</v>
+        <v>317478</v>
       </c>
       <c r="R54" t="n">
-        <v>6550788</v>
+        <v>6550898</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6754,45 +6754,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130063343</v>
+        <v>130063339</v>
       </c>
       <c r="B55" t="n">
-        <v>91641</v>
+        <v>5197</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>317442</v>
+        <v>317422</v>
       </c>
       <c r="R55" t="n">
-        <v>6550932</v>
+        <v>6550917</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6866,32 +6871,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130063319</v>
+        <v>130063346</v>
       </c>
       <c r="B56" t="n">
-        <v>97079</v>
+        <v>97202</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6901,10 +6906,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>317401</v>
+        <v>317457</v>
       </c>
       <c r="R56" t="n">
-        <v>6550860</v>
+        <v>6550912</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6963,10 +6968,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130063344</v>
+        <v>130063319</v>
       </c>
       <c r="B57" t="n">
-        <v>97079</v>
+        <v>97166</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6998,10 +7003,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>317456</v>
+        <v>317401</v>
       </c>
       <c r="R57" t="n">
-        <v>6550897</v>
+        <v>6550860</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7060,32 +7065,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130063346</v>
+        <v>130063343</v>
       </c>
       <c r="B58" t="n">
-        <v>97115</v>
+        <v>91728</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2590</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7095,10 +7100,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>317457</v>
+        <v>317442</v>
       </c>
       <c r="R58" t="n">
-        <v>6550912</v>
+        <v>6550932</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7141,6 +7146,21 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7157,50 +7177,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130063339</v>
+        <v>130063344</v>
       </c>
       <c r="B59" t="n">
-        <v>5197</v>
+        <v>97166</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>317422</v>
+        <v>317456</v>
       </c>
       <c r="R59" t="n">
-        <v>6550917</v>
+        <v>6550897</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7243,21 +7258,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7274,10 +7274,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130063321</v>
+        <v>130063316</v>
       </c>
       <c r="B60" t="n">
-        <v>92923</v>
+        <v>97202</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7285,21 +7285,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7309,10 +7309,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>317373</v>
+        <v>317362</v>
       </c>
       <c r="R60" t="n">
-        <v>6550909</v>
+        <v>6550742</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7371,10 +7371,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130063316</v>
+        <v>130063321</v>
       </c>
       <c r="B61" t="n">
-        <v>97115</v>
+        <v>93010</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7382,21 +7382,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7406,10 +7406,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>317362</v>
+        <v>317373</v>
       </c>
       <c r="R61" t="n">
-        <v>6550742</v>
+        <v>6550909</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7468,10 +7468,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130063342</v>
+        <v>130063332</v>
       </c>
       <c r="B62" t="n">
-        <v>5177</v>
+        <v>75286</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7479,39 +7479,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100526</v>
+        <v>6426</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>317442</v>
+        <v>317425</v>
       </c>
       <c r="R62" t="n">
-        <v>6550932</v>
+        <v>6550935</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7554,21 +7549,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7585,10 +7565,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130063332</v>
+        <v>130063342</v>
       </c>
       <c r="B63" t="n">
-        <v>75201</v>
+        <v>5177</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7596,34 +7576,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6426</v>
+        <v>100526</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>317425</v>
+        <v>317442</v>
       </c>
       <c r="R63" t="n">
-        <v>6550935</v>
+        <v>6550932</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7666,6 +7651,21 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -8036,7 +8036,7 @@
         <v>130063348</v>
       </c>
       <c r="B67" t="n">
-        <v>75201</v>
+        <v>75286</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8145,10 +8145,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130063333</v>
+        <v>130063326</v>
       </c>
       <c r="B68" t="n">
-        <v>5177</v>
+        <v>91692</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8156,39 +8156,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>317428</v>
+        <v>317328</v>
       </c>
       <c r="R68" t="n">
-        <v>6550930</v>
+        <v>6550975</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8262,10 +8257,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130063326</v>
+        <v>130063354</v>
       </c>
       <c r="B69" t="n">
-        <v>91605</v>
+        <v>93010</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8273,21 +8268,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8297,10 +8292,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>317328</v>
+        <v>317491</v>
       </c>
       <c r="R69" t="n">
-        <v>6550975</v>
+        <v>6550822</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8343,21 +8338,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8374,10 +8354,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130063354</v>
+        <v>130063333</v>
       </c>
       <c r="B70" t="n">
-        <v>92923</v>
+        <v>5177</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8385,34 +8365,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>317491</v>
+        <v>317428</v>
       </c>
       <c r="R70" t="n">
-        <v>6550822</v>
+        <v>6550930</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8455,6 +8440,21 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8471,10 +8471,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130063340</v>
+        <v>130063329</v>
       </c>
       <c r="B71" t="n">
-        <v>5177</v>
+        <v>97541</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8482,21 +8482,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100526</v>
+        <v>2569</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8506,10 +8506,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>317439</v>
+        <v>317411</v>
       </c>
       <c r="R71" t="n">
-        <v>6550940</v>
+        <v>6550970</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8550,7 +8550,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8569,10 +8568,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130063329</v>
+        <v>130063340</v>
       </c>
       <c r="B72" t="n">
-        <v>97454</v>
+        <v>5177</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8580,21 +8579,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2569</v>
+        <v>100526</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8604,10 +8603,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>317411</v>
+        <v>317439</v>
       </c>
       <c r="R72" t="n">
-        <v>6550970</v>
+        <v>6550940</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8648,6 +8647,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8666,10 +8666,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130063351</v>
+        <v>130063359</v>
       </c>
       <c r="B73" t="n">
-        <v>75201</v>
+        <v>8440</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8677,21 +8677,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6426</v>
+        <v>106554</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>317464</v>
+        <v>317525</v>
       </c>
       <c r="R73" t="n">
-        <v>6550904</v>
+        <v>6550630</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8747,21 +8747,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8781,7 +8766,7 @@
         <v>130063335</v>
       </c>
       <c r="B74" t="n">
-        <v>92923</v>
+        <v>93010</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8875,32 +8860,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130063359</v>
+        <v>130063337</v>
       </c>
       <c r="B75" t="n">
-        <v>8440</v>
+        <v>97166</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8910,10 +8895,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>317525</v>
+        <v>317425</v>
       </c>
       <c r="R75" t="n">
-        <v>6550630</v>
+        <v>6550915</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8972,32 +8957,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130063337</v>
+        <v>130063351</v>
       </c>
       <c r="B76" t="n">
-        <v>97079</v>
+        <v>75286</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9007,10 +8992,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>317425</v>
+        <v>317464</v>
       </c>
       <c r="R76" t="n">
-        <v>6550915</v>
+        <v>6550904</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9053,6 +9038,21 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9072,7 +9072,7 @@
         <v>130063328</v>
       </c>
       <c r="B77" t="n">
-        <v>80160</v>
+        <v>80245</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>130104814</v>
       </c>
       <c r="B78" t="n">
-        <v>78761</v>
+        <v>78846</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>130104706</v>
       </c>
       <c r="B79" t="n">
-        <v>92283</v>
+        <v>92370</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>130104411</v>
       </c>
       <c r="B80" t="n">
-        <v>78761</v>
+        <v>78846</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>130177928</v>
       </c>
       <c r="B81" t="n">
-        <v>75201</v>
+        <v>75286</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>130175963</v>
       </c>
       <c r="B82" t="n">
-        <v>78761</v>
+        <v>78846</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>130176280</v>
       </c>
       <c r="B83" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>130177344</v>
       </c>
       <c r="B84" t="n">
-        <v>97115</v>
+        <v>97202</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>130175755</v>
       </c>
       <c r="B85" t="n">
-        <v>92427</v>
+        <v>92514</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>130175870</v>
       </c>
       <c r="B86" t="n">
-        <v>92124</v>
+        <v>92211</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>130177191</v>
       </c>
       <c r="B87" t="n">
-        <v>97115</v>
+        <v>97202</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10434,10 +10434,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130177180</v>
+        <v>130177708</v>
       </c>
       <c r="B88" t="n">
-        <v>97115</v>
+        <v>75286</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10445,27 +10445,30 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -10473,10 +10476,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>317344</v>
+        <v>317400</v>
       </c>
       <c r="R88" t="n">
-        <v>6550753</v>
+        <v>6550946</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10523,22 +10526,22 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
+          <t>Mosseblåbärgranskog</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>På bark # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10556,10 +10559,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130177708</v>
+        <v>130177180</v>
       </c>
       <c r="B89" t="n">
-        <v>75201</v>
+        <v>97202</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10567,30 +10570,27 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>317400</v>
+        <v>317344</v>
       </c>
       <c r="R89" t="n">
-        <v>6550946</v>
+        <v>6550753</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10648,22 +10648,22 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Mosseblåbärgranskog</t>
+          <t>Blåbärgranskog</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>På bark # Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10684,7 +10684,7 @@
         <v>130210763</v>
       </c>
       <c r="B90" t="n">
-        <v>97115</v>
+        <v>97202</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>130210762</v>
       </c>
       <c r="B91" t="n">
-        <v>97079</v>
+        <v>97166</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10875,32 +10875,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130210782</v>
+        <v>130210783</v>
       </c>
       <c r="B92" t="n">
-        <v>97079</v>
+        <v>97202</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10987,32 +10987,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130210755</v>
+        <v>130210782</v>
       </c>
       <c r="B93" t="n">
-        <v>91605</v>
+        <v>97166</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11022,10 +11022,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>317405</v>
+        <v>317282</v>
       </c>
       <c r="R93" t="n">
-        <v>6550943</v>
+        <v>6550790</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11071,17 +11071,17 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11099,10 +11099,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130210783</v>
+        <v>130210755</v>
       </c>
       <c r="B94" t="n">
-        <v>97115</v>
+        <v>91692</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11110,21 +11110,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2590</v>
+        <v>5447</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11134,10 +11134,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>317282</v>
+        <v>317405</v>
       </c>
       <c r="R94" t="n">
-        <v>6550790</v>
+        <v>6550943</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11183,17 +11183,17 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
         <v>130210766</v>
       </c>
       <c r="B95" t="n">
-        <v>97115</v>
+        <v>97202</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>130210781</v>
       </c>
       <c r="B96" t="n">
-        <v>97115</v>
+        <v>97202</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>130210758</v>
       </c>
       <c r="B97" t="n">
-        <v>97454</v>
+        <v>97541</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11518,45 +11518,54 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130210765</v>
+        <v>130210778</v>
       </c>
       <c r="B98" t="n">
-        <v>97079</v>
+        <v>44080</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>53</v>
+        <v>101735</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>317236</v>
+        <v>317266</v>
       </c>
       <c r="R98" t="n">
-        <v>6550997</v>
+        <v>6550821</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11597,6 +11606,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11615,54 +11625,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130210778</v>
+        <v>130210765</v>
       </c>
       <c r="B99" t="n">
-        <v>43995</v>
+        <v>97166</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>101735</v>
+        <v>53</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>317266</v>
+        <v>317236</v>
       </c>
       <c r="R99" t="n">
-        <v>6550821</v>
+        <v>6550997</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11703,7 +11704,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11725,7 +11725,7 @@
         <v>130210753</v>
       </c>
       <c r="B100" t="n">
-        <v>75201</v>
+        <v>75286</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>130210787</v>
       </c>
       <c r="B101" t="n">
-        <v>97115</v>
+        <v>97202</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130210779</v>
+        <v>130210772</v>
       </c>
       <c r="B105" t="n">
         <v>8440</v>
@@ -12337,10 +12337,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>317266</v>
+        <v>317242</v>
       </c>
       <c r="R105" t="n">
-        <v>6550821</v>
+        <v>6550921</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12414,7 +12414,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130210772</v>
+        <v>130210779</v>
       </c>
       <c r="B106" t="n">
         <v>8440</v>
@@ -12454,10 +12454,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>317242</v>
+        <v>317266</v>
       </c>
       <c r="R106" t="n">
-        <v>6550921</v>
+        <v>6550821</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12534,7 +12534,7 @@
         <v>130210780</v>
       </c>
       <c r="B107" t="n">
-        <v>97079</v>
+        <v>97166</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>130210756</v>
       </c>
       <c r="B108" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>130210759</v>
       </c>
       <c r="B109" t="n">
-        <v>75201</v>
+        <v>75286</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12867,32 +12867,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130210769</v>
+        <v>130210789</v>
       </c>
       <c r="B110" t="n">
-        <v>97079</v>
+        <v>97202</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12902,10 +12902,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>317269</v>
+        <v>317326</v>
       </c>
       <c r="R110" t="n">
-        <v>6550970</v>
+        <v>6550738</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12948,21 +12948,6 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
@@ -12979,10 +12964,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>130210789</v>
+        <v>130210770</v>
       </c>
       <c r="B111" t="n">
-        <v>97115</v>
+        <v>8451</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12990,34 +12975,39 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>317326</v>
+        <v>317245</v>
       </c>
       <c r="R111" t="n">
-        <v>6550738</v>
+        <v>6550930</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -13060,6 +13050,21 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
@@ -13076,50 +13081,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130210770</v>
+        <v>130210769</v>
       </c>
       <c r="B112" t="n">
-        <v>8451</v>
+        <v>97166</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>317245</v>
+        <v>317269</v>
       </c>
       <c r="R112" t="n">
-        <v>6550930</v>
+        <v>6550970</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13193,32 +13193,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130210760</v>
+        <v>130210761</v>
       </c>
       <c r="B113" t="n">
-        <v>97079</v>
+        <v>97202</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13228,10 +13228,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>317334</v>
+        <v>317337</v>
       </c>
       <c r="R113" t="n">
-        <v>6550938</v>
+        <v>6550964</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13293,7 +13293,7 @@
         <v>130210790</v>
       </c>
       <c r="B114" t="n">
-        <v>97115</v>
+        <v>97202</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13387,32 +13387,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130210764</v>
+        <v>130210760</v>
       </c>
       <c r="B115" t="n">
-        <v>97115</v>
+        <v>97166</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13422,10 +13422,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>317268</v>
+        <v>317334</v>
       </c>
       <c r="R115" t="n">
-        <v>6550998</v>
+        <v>6550938</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13484,10 +13484,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130210761</v>
+        <v>130210764</v>
       </c>
       <c r="B116" t="n">
-        <v>97115</v>
+        <v>97202</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13519,10 +13519,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>317337</v>
+        <v>317268</v>
       </c>
       <c r="R116" t="n">
-        <v>6550964</v>
+        <v>6550998</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13581,10 +13581,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130210771</v>
+        <v>130210777</v>
       </c>
       <c r="B117" t="n">
-        <v>92923</v>
+        <v>8451</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13592,34 +13592,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>317240</v>
+        <v>317283</v>
       </c>
       <c r="R117" t="n">
-        <v>6550922</v>
+        <v>6550823</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13678,10 +13683,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130210777</v>
+        <v>130210771</v>
       </c>
       <c r="B118" t="n">
-        <v>8451</v>
+        <v>93010</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13689,39 +13694,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>317283</v>
+        <v>317240</v>
       </c>
       <c r="R118" t="n">
-        <v>6550823</v>
+        <v>6550922</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13897,10 +13897,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130210752</v>
+        <v>130210757</v>
       </c>
       <c r="B120" t="n">
-        <v>8451</v>
+        <v>75286</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13908,39 +13908,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>6426</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>317348</v>
+        <v>317402</v>
       </c>
       <c r="R120" t="n">
-        <v>6550887</v>
+        <v>6550941</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13986,17 +13981,17 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -14014,32 +14009,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130210757</v>
+        <v>130210768</v>
       </c>
       <c r="B121" t="n">
-        <v>75201</v>
+        <v>97166</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14049,10 +14044,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>317402</v>
+        <v>317274</v>
       </c>
       <c r="R121" t="n">
-        <v>6550941</v>
+        <v>6550981</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14098,17 +14093,17 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14126,45 +14121,50 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130210768</v>
+        <v>130210752</v>
       </c>
       <c r="B122" t="n">
-        <v>97079</v>
+        <v>8451</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>317274</v>
+        <v>317348</v>
       </c>
       <c r="R122" t="n">
-        <v>6550981</v>
+        <v>6550887</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14241,7 +14241,7 @@
         <v>130210773</v>
       </c>
       <c r="B123" t="n">
-        <v>92923</v>
+        <v>93010</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14335,10 +14335,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130210767</v>
+        <v>130210754</v>
       </c>
       <c r="B124" t="n">
-        <v>97115</v>
+        <v>75286</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14346,21 +14346,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14370,10 +14370,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>317271</v>
+        <v>317405</v>
       </c>
       <c r="R124" t="n">
-        <v>6550985</v>
+        <v>6550943</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14419,17 +14419,17 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -14447,10 +14447,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130210754</v>
+        <v>130210767</v>
       </c>
       <c r="B125" t="n">
-        <v>75201</v>
+        <v>97202</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14458,21 +14458,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14482,10 +14482,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>317405</v>
+        <v>317271</v>
       </c>
       <c r="R125" t="n">
-        <v>6550943</v>
+        <v>6550985</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14531,17 +14531,17 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -14562,7 +14562,7 @@
         <v>130177671</v>
       </c>
       <c r="B126" t="n">
-        <v>75201</v>
+        <v>75286</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -10434,10 +10434,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130177708</v>
+        <v>130177180</v>
       </c>
       <c r="B88" t="n">
-        <v>75286</v>
+        <v>97202</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10445,30 +10445,27 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -10476,10 +10473,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>317400</v>
+        <v>317344</v>
       </c>
       <c r="R88" t="n">
-        <v>6550946</v>
+        <v>6550753</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10526,22 +10523,22 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Mosseblåbärgranskog</t>
+          <t>Blåbärgranskog</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>På bark # Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10559,10 +10556,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130177180</v>
+        <v>130177708</v>
       </c>
       <c r="B89" t="n">
-        <v>97202</v>
+        <v>75286</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10570,27 +10567,30 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>317344</v>
+        <v>317400</v>
       </c>
       <c r="R89" t="n">
-        <v>6550753</v>
+        <v>6550946</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10648,22 +10648,22 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
+          <t>Mosseblåbärgranskog</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>På bark # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -4736,10 +4736,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130063338</v>
+        <v>130063320</v>
       </c>
       <c r="B36" t="n">
-        <v>75286</v>
+        <v>80245</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4747,21 +4747,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4771,10 +4771,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>317422</v>
+        <v>317410</v>
       </c>
       <c r="R36" t="n">
-        <v>6550917</v>
+        <v>6550877</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4820,17 +4820,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130063320</v>
+        <v>130063338</v>
       </c>
       <c r="B37" t="n">
-        <v>80245</v>
+        <v>75286</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,21 +4859,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>317410</v>
+        <v>317422</v>
       </c>
       <c r="R37" t="n">
-        <v>6550877</v>
+        <v>6550917</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4932,17 +4932,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5445,10 +5445,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130063322</v>
+        <v>130063357</v>
       </c>
       <c r="B43" t="n">
-        <v>80245</v>
+        <v>57016</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5456,34 +5456,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229497</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>317366</v>
+        <v>317515</v>
       </c>
       <c r="R43" t="n">
-        <v>6550944</v>
+        <v>6550638</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5526,21 +5531,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5557,10 +5547,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130063357</v>
+        <v>130063322</v>
       </c>
       <c r="B44" t="n">
-        <v>57016</v>
+        <v>80245</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5568,39 +5558,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>229497</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>317515</v>
+        <v>317366</v>
       </c>
       <c r="R44" t="n">
-        <v>6550638</v>
+        <v>6550944</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5643,6 +5628,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5659,10 +5659,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130063350</v>
+        <v>130063355</v>
       </c>
       <c r="B45" t="n">
-        <v>91110</v>
+        <v>8451</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5670,34 +5670,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5685</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>317461</v>
+        <v>317544</v>
       </c>
       <c r="R45" t="n">
-        <v>6550934</v>
+        <v>6550707</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5771,10 +5776,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130063355</v>
+        <v>130063350</v>
       </c>
       <c r="B46" t="n">
-        <v>8451</v>
+        <v>91110</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5782,39 +5787,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>5685</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>317544</v>
+        <v>317461</v>
       </c>
       <c r="R46" t="n">
-        <v>6550707</v>
+        <v>6550934</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5888,10 +5888,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130063323</v>
+        <v>130063345</v>
       </c>
       <c r="B47" t="n">
-        <v>75286</v>
+        <v>97202</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5899,21 +5899,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>317366</v>
+        <v>317456</v>
       </c>
       <c r="R47" t="n">
-        <v>6550944</v>
+        <v>6550897</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5985,10 +5985,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130063345</v>
+        <v>130063323</v>
       </c>
       <c r="B48" t="n">
-        <v>97202</v>
+        <v>75286</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5996,21 +5996,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6020,10 +6020,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>317456</v>
+        <v>317366</v>
       </c>
       <c r="R48" t="n">
-        <v>6550897</v>
+        <v>6550944</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6316,10 +6316,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130063336</v>
+        <v>130063353</v>
       </c>
       <c r="B51" t="n">
-        <v>75286</v>
+        <v>91110</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6327,21 +6327,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6426</v>
+        <v>5685</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>317424</v>
+        <v>317478</v>
       </c>
       <c r="R51" t="n">
-        <v>6550930</v>
+        <v>6550898</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6397,6 +6397,21 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6413,10 +6428,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130063330</v>
+        <v>130063336</v>
       </c>
       <c r="B52" t="n">
-        <v>91692</v>
+        <v>75286</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6424,21 +6439,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6448,10 +6463,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>317408</v>
+        <v>317424</v>
       </c>
       <c r="R52" t="n">
-        <v>6550961</v>
+        <v>6550930</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6494,21 +6509,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6525,10 +6525,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130063318</v>
+        <v>130063330</v>
       </c>
       <c r="B53" t="n">
-        <v>8451</v>
+        <v>91692</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6536,39 +6536,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>317387</v>
+        <v>317408</v>
       </c>
       <c r="R53" t="n">
-        <v>6550788</v>
+        <v>6550961</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6614,17 +6609,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6642,10 +6637,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130063353</v>
+        <v>130063318</v>
       </c>
       <c r="B54" t="n">
-        <v>91110</v>
+        <v>8451</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6653,34 +6648,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5685</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>317478</v>
+        <v>317387</v>
       </c>
       <c r="R54" t="n">
-        <v>6550898</v>
+        <v>6550788</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6754,50 +6754,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130063339</v>
+        <v>130063319</v>
       </c>
       <c r="B55" t="n">
-        <v>5197</v>
+        <v>97166</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>317422</v>
+        <v>317401</v>
       </c>
       <c r="R55" t="n">
-        <v>6550917</v>
+        <v>6550860</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6840,21 +6835,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6871,32 +6851,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130063346</v>
+        <v>130063344</v>
       </c>
       <c r="B56" t="n">
-        <v>97202</v>
+        <v>97166</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6906,10 +6886,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>317457</v>
+        <v>317456</v>
       </c>
       <c r="R56" t="n">
-        <v>6550912</v>
+        <v>6550897</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6968,10 +6948,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130063319</v>
+        <v>130063343</v>
       </c>
       <c r="B57" t="n">
-        <v>97166</v>
+        <v>91728</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6979,21 +6959,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7003,10 +6983,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>317401</v>
+        <v>317442</v>
       </c>
       <c r="R57" t="n">
-        <v>6550860</v>
+        <v>6550932</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7049,6 +7029,21 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7065,32 +7060,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130063343</v>
+        <v>130063346</v>
       </c>
       <c r="B58" t="n">
-        <v>91728</v>
+        <v>97202</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>2590</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7100,10 +7095,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>317442</v>
+        <v>317457</v>
       </c>
       <c r="R58" t="n">
-        <v>6550932</v>
+        <v>6550912</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7146,21 +7141,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7177,45 +7157,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130063344</v>
+        <v>130063339</v>
       </c>
       <c r="B59" t="n">
-        <v>97166</v>
+        <v>5197</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>317456</v>
+        <v>317422</v>
       </c>
       <c r="R59" t="n">
-        <v>6550897</v>
+        <v>6550917</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7258,6 +7243,21 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7565,10 +7565,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130063342</v>
+        <v>130063341</v>
       </c>
       <c r="B63" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7576,21 +7576,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7799,10 +7799,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130063341</v>
+        <v>130063342</v>
       </c>
       <c r="B65" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7810,21 +7810,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8145,10 +8145,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130063326</v>
+        <v>130063354</v>
       </c>
       <c r="B68" t="n">
-        <v>91692</v>
+        <v>93010</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8156,21 +8156,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8180,10 +8180,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>317328</v>
+        <v>317491</v>
       </c>
       <c r="R68" t="n">
-        <v>6550975</v>
+        <v>6550822</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8226,21 +8226,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8257,10 +8242,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130063354</v>
+        <v>130063326</v>
       </c>
       <c r="B69" t="n">
-        <v>93010</v>
+        <v>91692</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8268,21 +8253,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8292,10 +8277,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>317491</v>
+        <v>317328</v>
       </c>
       <c r="R69" t="n">
-        <v>6550822</v>
+        <v>6550975</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8338,6 +8323,21 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8471,10 +8471,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130063329</v>
+        <v>130063340</v>
       </c>
       <c r="B71" t="n">
-        <v>97541</v>
+        <v>5177</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8482,21 +8482,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2569</v>
+        <v>100526</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8506,10 +8506,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>317411</v>
+        <v>317439</v>
       </c>
       <c r="R71" t="n">
-        <v>6550970</v>
+        <v>6550940</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8550,6 +8550,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8568,10 +8569,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130063340</v>
+        <v>130063329</v>
       </c>
       <c r="B72" t="n">
-        <v>5177</v>
+        <v>97541</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8579,21 +8580,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100526</v>
+        <v>2569</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8603,10 +8604,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>317439</v>
+        <v>317411</v>
       </c>
       <c r="R72" t="n">
-        <v>6550940</v>
+        <v>6550970</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8647,7 +8648,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8666,10 +8666,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130063359</v>
+        <v>130063335</v>
       </c>
       <c r="B73" t="n">
-        <v>8440</v>
+        <v>93010</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8677,21 +8677,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106554</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>317525</v>
+        <v>317426</v>
       </c>
       <c r="R73" t="n">
-        <v>6550630</v>
+        <v>6550926</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8763,10 +8763,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130063335</v>
+        <v>130063328</v>
       </c>
       <c r="B74" t="n">
-        <v>93010</v>
+        <v>80245</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8774,21 +8774,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>229497</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8798,10 +8798,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>317426</v>
+        <v>317351</v>
       </c>
       <c r="R74" t="n">
-        <v>6550926</v>
+        <v>6550971</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8844,6 +8844,21 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8957,10 +8972,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130063351</v>
+        <v>130063359</v>
       </c>
       <c r="B76" t="n">
-        <v>75286</v>
+        <v>8440</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8968,21 +8983,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6426</v>
+        <v>106554</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8992,10 +9007,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>317464</v>
+        <v>317525</v>
       </c>
       <c r="R76" t="n">
-        <v>6550904</v>
+        <v>6550630</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9038,21 +9053,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9069,10 +9069,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130063328</v>
+        <v>130063351</v>
       </c>
       <c r="B77" t="n">
-        <v>80245</v>
+        <v>75286</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9080,21 +9080,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9104,10 +9104,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>317351</v>
+        <v>317464</v>
       </c>
       <c r="R77" t="n">
-        <v>6550971</v>
+        <v>6550904</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9153,17 +9153,17 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10434,10 +10434,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130177180</v>
+        <v>130177708</v>
       </c>
       <c r="B88" t="n">
-        <v>97202</v>
+        <v>75286</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10445,27 +10445,30 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -10473,10 +10476,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>317344</v>
+        <v>317400</v>
       </c>
       <c r="R88" t="n">
-        <v>6550753</v>
+        <v>6550946</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10523,22 +10526,22 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
+          <t>Mosseblåbärgranskog</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>På bark # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10556,10 +10559,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130177708</v>
+        <v>130177180</v>
       </c>
       <c r="B89" t="n">
-        <v>75286</v>
+        <v>97202</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10567,30 +10570,27 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>317400</v>
+        <v>317344</v>
       </c>
       <c r="R89" t="n">
-        <v>6550946</v>
+        <v>6550753</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10648,22 +10648,22 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Mosseblåbärgranskog</t>
+          <t>Blåbärgranskog</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>På bark # Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10875,32 +10875,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130210783</v>
+        <v>130210782</v>
       </c>
       <c r="B92" t="n">
-        <v>97202</v>
+        <v>97166</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10987,32 +10987,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130210782</v>
+        <v>130210783</v>
       </c>
       <c r="B93" t="n">
-        <v>97166</v>
+        <v>97202</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11099,10 +11099,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130210755</v>
+        <v>130210766</v>
       </c>
       <c r="B94" t="n">
-        <v>91692</v>
+        <v>97202</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11110,21 +11110,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5447</v>
+        <v>2590</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11134,10 +11134,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>317405</v>
+        <v>317236</v>
       </c>
       <c r="R94" t="n">
-        <v>6550943</v>
+        <v>6550997</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11180,21 +11180,6 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -11211,10 +11196,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130210766</v>
+        <v>130210755</v>
       </c>
       <c r="B95" t="n">
-        <v>97202</v>
+        <v>91692</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11222,21 +11207,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2590</v>
+        <v>5447</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11246,10 +11231,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>317236</v>
+        <v>317405</v>
       </c>
       <c r="R95" t="n">
-        <v>6550997</v>
+        <v>6550943</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11292,6 +11277,21 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11518,54 +11518,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130210778</v>
+        <v>130210765</v>
       </c>
       <c r="B98" t="n">
-        <v>44080</v>
+        <v>97166</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>101735</v>
+        <v>53</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>317266</v>
+        <v>317236</v>
       </c>
       <c r="R98" t="n">
-        <v>6550821</v>
+        <v>6550997</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11606,7 +11597,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11625,45 +11615,54 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130210765</v>
+        <v>130210778</v>
       </c>
       <c r="B99" t="n">
-        <v>97166</v>
+        <v>44080</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>53</v>
+        <v>101735</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>317236</v>
+        <v>317266</v>
       </c>
       <c r="R99" t="n">
-        <v>6550997</v>
+        <v>6550821</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11704,6 +11703,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -12297,7 +12297,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130210772</v>
+        <v>130210779</v>
       </c>
       <c r="B105" t="n">
         <v>8440</v>
@@ -12337,10 +12337,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>317242</v>
+        <v>317266</v>
       </c>
       <c r="R105" t="n">
-        <v>6550921</v>
+        <v>6550821</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12414,7 +12414,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130210779</v>
+        <v>130210772</v>
       </c>
       <c r="B106" t="n">
         <v>8440</v>
@@ -12454,10 +12454,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>317266</v>
+        <v>317242</v>
       </c>
       <c r="R106" t="n">
-        <v>6550821</v>
+        <v>6550921</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12643,10 +12643,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130210756</v>
+        <v>130210759</v>
       </c>
       <c r="B108" t="n">
-        <v>91692</v>
+        <v>75286</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12654,21 +12654,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12678,10 +12678,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>317409</v>
+        <v>317390</v>
       </c>
       <c r="R108" t="n">
-        <v>6550951</v>
+        <v>6550928</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12755,10 +12755,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130210759</v>
+        <v>130210756</v>
       </c>
       <c r="B109" t="n">
-        <v>75286</v>
+        <v>91692</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12766,21 +12766,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12790,10 +12790,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>317390</v>
+        <v>317409</v>
       </c>
       <c r="R109" t="n">
-        <v>6550928</v>
+        <v>6550951</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12867,32 +12867,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130210789</v>
+        <v>130210769</v>
       </c>
       <c r="B110" t="n">
-        <v>97202</v>
+        <v>97166</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12902,10 +12902,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>317326</v>
+        <v>317269</v>
       </c>
       <c r="R110" t="n">
-        <v>6550738</v>
+        <v>6550970</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12948,6 +12948,21 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
@@ -12964,10 +12979,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>130210770</v>
+        <v>130210789</v>
       </c>
       <c r="B111" t="n">
-        <v>8451</v>
+        <v>97202</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12975,39 +12990,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>317245</v>
+        <v>317326</v>
       </c>
       <c r="R111" t="n">
-        <v>6550930</v>
+        <v>6550738</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -13050,21 +13060,6 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
@@ -13081,45 +13076,50 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130210769</v>
+        <v>130210770</v>
       </c>
       <c r="B112" t="n">
-        <v>97166</v>
+        <v>8451</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>317269</v>
+        <v>317245</v>
       </c>
       <c r="R112" t="n">
-        <v>6550970</v>
+        <v>6550930</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13193,32 +13193,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130210761</v>
+        <v>130210760</v>
       </c>
       <c r="B113" t="n">
-        <v>97202</v>
+        <v>97166</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13228,10 +13228,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>317337</v>
+        <v>317334</v>
       </c>
       <c r="R113" t="n">
-        <v>6550964</v>
+        <v>6550938</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13387,32 +13387,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130210760</v>
+        <v>130210764</v>
       </c>
       <c r="B115" t="n">
-        <v>97166</v>
+        <v>97202</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13422,10 +13422,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>317334</v>
+        <v>317268</v>
       </c>
       <c r="R115" t="n">
-        <v>6550938</v>
+        <v>6550998</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13484,7 +13484,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130210764</v>
+        <v>130210761</v>
       </c>
       <c r="B116" t="n">
         <v>97202</v>
@@ -13519,10 +13519,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>317268</v>
+        <v>317337</v>
       </c>
       <c r="R116" t="n">
-        <v>6550998</v>
+        <v>6550964</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13897,32 +13897,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130210757</v>
+        <v>130210768</v>
       </c>
       <c r="B120" t="n">
-        <v>75286</v>
+        <v>97166</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13932,10 +13932,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>317402</v>
+        <v>317274</v>
       </c>
       <c r="R120" t="n">
-        <v>6550941</v>
+        <v>6550981</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13981,17 +13981,17 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -14009,32 +14009,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130210768</v>
+        <v>130210757</v>
       </c>
       <c r="B121" t="n">
-        <v>97166</v>
+        <v>75286</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14044,10 +14044,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>317274</v>
+        <v>317402</v>
       </c>
       <c r="R121" t="n">
-        <v>6550981</v>
+        <v>6550941</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14093,17 +14093,17 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14335,10 +14335,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130210754</v>
+        <v>130210767</v>
       </c>
       <c r="B124" t="n">
-        <v>75286</v>
+        <v>97202</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14346,21 +14346,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14370,10 +14370,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>317405</v>
+        <v>317271</v>
       </c>
       <c r="R124" t="n">
-        <v>6550943</v>
+        <v>6550985</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14419,17 +14419,17 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -14447,10 +14447,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130210767</v>
+        <v>130210754</v>
       </c>
       <c r="B125" t="n">
-        <v>97202</v>
+        <v>75286</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14458,21 +14458,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14482,10 +14482,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>317271</v>
+        <v>317405</v>
       </c>
       <c r="R125" t="n">
-        <v>6550985</v>
+        <v>6550943</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14531,17 +14531,17 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -4736,10 +4736,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130063320</v>
+        <v>130063338</v>
       </c>
       <c r="B36" t="n">
-        <v>80245</v>
+        <v>75286</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4747,21 +4747,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4771,10 +4771,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>317410</v>
+        <v>317422</v>
       </c>
       <c r="R36" t="n">
-        <v>6550877</v>
+        <v>6550917</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4820,17 +4820,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130063338</v>
+        <v>130063320</v>
       </c>
       <c r="B37" t="n">
-        <v>75286</v>
+        <v>80245</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,21 +4859,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>317422</v>
+        <v>317410</v>
       </c>
       <c r="R37" t="n">
-        <v>6550917</v>
+        <v>6550877</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4932,17 +4932,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5154,10 +5154,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130063356</v>
+        <v>130063358</v>
       </c>
       <c r="B40" t="n">
-        <v>93010</v>
+        <v>97202</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5165,21 +5165,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>2590</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>317537</v>
+        <v>317521</v>
       </c>
       <c r="R40" t="n">
-        <v>6550669</v>
+        <v>6550632</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5251,10 +5251,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130063358</v>
+        <v>130063356</v>
       </c>
       <c r="B41" t="n">
-        <v>97202</v>
+        <v>93010</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5262,21 +5262,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5286,10 +5286,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>317521</v>
+        <v>317537</v>
       </c>
       <c r="R41" t="n">
-        <v>6550632</v>
+        <v>6550669</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5348,10 +5348,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130063331</v>
+        <v>130063322</v>
       </c>
       <c r="B42" t="n">
-        <v>97541</v>
+        <v>80245</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5359,21 +5359,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2569</v>
+        <v>229497</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5383,10 +5383,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>317408</v>
+        <v>317366</v>
       </c>
       <c r="R42" t="n">
-        <v>6550956</v>
+        <v>6550944</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5429,6 +5429,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5445,10 +5460,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130063357</v>
+        <v>130063331</v>
       </c>
       <c r="B43" t="n">
-        <v>57016</v>
+        <v>97541</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5456,39 +5471,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>2569</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>317515</v>
+        <v>317408</v>
       </c>
       <c r="R43" t="n">
-        <v>6550638</v>
+        <v>6550956</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5547,10 +5557,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130063322</v>
+        <v>130063357</v>
       </c>
       <c r="B44" t="n">
-        <v>80245</v>
+        <v>57016</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5558,34 +5568,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>317366</v>
+        <v>317515</v>
       </c>
       <c r="R44" t="n">
-        <v>6550944</v>
+        <v>6550638</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5628,21 +5643,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5659,10 +5659,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130063355</v>
+        <v>130063350</v>
       </c>
       <c r="B45" t="n">
-        <v>8451</v>
+        <v>91110</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5670,39 +5670,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>5685</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>317544</v>
+        <v>317461</v>
       </c>
       <c r="R45" t="n">
-        <v>6550707</v>
+        <v>6550934</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5776,10 +5771,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130063350</v>
+        <v>130063355</v>
       </c>
       <c r="B46" t="n">
-        <v>91110</v>
+        <v>8451</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5787,34 +5782,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5685</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>317461</v>
+        <v>317544</v>
       </c>
       <c r="R46" t="n">
-        <v>6550934</v>
+        <v>6550707</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6316,10 +6316,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130063353</v>
+        <v>130063336</v>
       </c>
       <c r="B51" t="n">
-        <v>91110</v>
+        <v>75286</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6327,21 +6327,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5685</v>
+        <v>6426</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>317478</v>
+        <v>317424</v>
       </c>
       <c r="R51" t="n">
-        <v>6550898</v>
+        <v>6550930</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6397,21 +6397,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6428,10 +6413,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130063336</v>
+        <v>130063318</v>
       </c>
       <c r="B52" t="n">
-        <v>75286</v>
+        <v>8451</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6439,34 +6424,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6426</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>317424</v>
+        <v>317387</v>
       </c>
       <c r="R52" t="n">
-        <v>6550930</v>
+        <v>6550788</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6509,6 +6499,21 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6525,10 +6530,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130063330</v>
+        <v>130063353</v>
       </c>
       <c r="B53" t="n">
-        <v>91692</v>
+        <v>91110</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6536,21 +6541,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>5685</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6560,10 +6565,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>317408</v>
+        <v>317478</v>
       </c>
       <c r="R53" t="n">
-        <v>6550961</v>
+        <v>6550898</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6609,17 +6614,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6637,10 +6642,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130063318</v>
+        <v>130063330</v>
       </c>
       <c r="B54" t="n">
-        <v>8451</v>
+        <v>91692</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6648,39 +6653,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>317387</v>
+        <v>317408</v>
       </c>
       <c r="R54" t="n">
-        <v>6550788</v>
+        <v>6550961</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6726,17 +6726,17 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6754,45 +6754,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130063319</v>
+        <v>130063339</v>
       </c>
       <c r="B55" t="n">
-        <v>97166</v>
+        <v>5197</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>317401</v>
+        <v>317422</v>
       </c>
       <c r="R55" t="n">
-        <v>6550860</v>
+        <v>6550917</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6835,6 +6840,21 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6851,7 +6871,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130063344</v>
+        <v>130063319</v>
       </c>
       <c r="B56" t="n">
         <v>97166</v>
@@ -6886,10 +6906,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>317456</v>
+        <v>317401</v>
       </c>
       <c r="R56" t="n">
-        <v>6550897</v>
+        <v>6550860</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6948,10 +6968,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130063343</v>
+        <v>130063344</v>
       </c>
       <c r="B57" t="n">
-        <v>91728</v>
+        <v>97166</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6959,21 +6979,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6983,10 +7003,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>317442</v>
+        <v>317456</v>
       </c>
       <c r="R57" t="n">
-        <v>6550932</v>
+        <v>6550897</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7029,21 +7049,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7157,50 +7162,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130063339</v>
+        <v>130063343</v>
       </c>
       <c r="B59" t="n">
-        <v>5197</v>
+        <v>91728</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>317422</v>
+        <v>317442</v>
       </c>
       <c r="R59" t="n">
-        <v>6550917</v>
+        <v>6550932</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7565,10 +7565,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130063341</v>
+        <v>130063342</v>
       </c>
       <c r="B63" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7576,21 +7576,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7682,10 +7682,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130063317</v>
+        <v>130063341</v>
       </c>
       <c r="B64" t="n">
-        <v>8451</v>
+        <v>5197</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7693,27 +7693,27 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7722,10 +7722,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>317378</v>
+        <v>317442</v>
       </c>
       <c r="R64" t="n">
-        <v>6550754</v>
+        <v>6550932</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7771,17 +7771,17 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7799,10 +7799,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130063342</v>
+        <v>130063317</v>
       </c>
       <c r="B65" t="n">
-        <v>5177</v>
+        <v>8451</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7810,27 +7810,27 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>317442</v>
+        <v>317378</v>
       </c>
       <c r="R65" t="n">
-        <v>6550932</v>
+        <v>6550754</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7888,17 +7888,17 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8145,10 +8145,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130063354</v>
+        <v>130063333</v>
       </c>
       <c r="B68" t="n">
-        <v>93010</v>
+        <v>5177</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8156,34 +8156,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>317491</v>
+        <v>317428</v>
       </c>
       <c r="R68" t="n">
-        <v>6550822</v>
+        <v>6550930</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8226,6 +8231,21 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8242,10 +8262,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130063326</v>
+        <v>130063354</v>
       </c>
       <c r="B69" t="n">
-        <v>91692</v>
+        <v>93010</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8253,21 +8273,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8277,10 +8297,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>317328</v>
+        <v>317491</v>
       </c>
       <c r="R69" t="n">
-        <v>6550975</v>
+        <v>6550822</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8323,21 +8343,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8354,10 +8359,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130063333</v>
+        <v>130063326</v>
       </c>
       <c r="B70" t="n">
-        <v>5177</v>
+        <v>91692</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8365,39 +8370,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>317428</v>
+        <v>317328</v>
       </c>
       <c r="R70" t="n">
-        <v>6550930</v>
+        <v>6550975</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8471,10 +8471,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130063340</v>
+        <v>130063329</v>
       </c>
       <c r="B71" t="n">
-        <v>5177</v>
+        <v>97541</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8482,21 +8482,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100526</v>
+        <v>2569</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8506,10 +8506,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>317439</v>
+        <v>317411</v>
       </c>
       <c r="R71" t="n">
-        <v>6550940</v>
+        <v>6550970</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8550,7 +8550,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8569,10 +8568,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130063329</v>
+        <v>130063340</v>
       </c>
       <c r="B72" t="n">
-        <v>97541</v>
+        <v>5177</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8580,21 +8579,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2569</v>
+        <v>100526</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8604,10 +8603,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>317411</v>
+        <v>317439</v>
       </c>
       <c r="R72" t="n">
-        <v>6550970</v>
+        <v>6550940</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8648,6 +8647,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8666,10 +8666,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130063335</v>
+        <v>130063328</v>
       </c>
       <c r="B73" t="n">
-        <v>93010</v>
+        <v>80245</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8677,21 +8677,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>229497</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>317426</v>
+        <v>317351</v>
       </c>
       <c r="R73" t="n">
-        <v>6550926</v>
+        <v>6550971</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8747,6 +8747,21 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8763,10 +8778,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130063328</v>
+        <v>130063359</v>
       </c>
       <c r="B74" t="n">
-        <v>80245</v>
+        <v>8440</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8774,21 +8789,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229497</v>
+        <v>106554</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8798,10 +8813,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>317351</v>
+        <v>317525</v>
       </c>
       <c r="R74" t="n">
-        <v>6550971</v>
+        <v>6550630</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8844,21 +8859,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8875,32 +8875,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130063337</v>
+        <v>130063335</v>
       </c>
       <c r="B75" t="n">
-        <v>97166</v>
+        <v>93010</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8910,10 +8910,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>317425</v>
+        <v>317426</v>
       </c>
       <c r="R75" t="n">
-        <v>6550915</v>
+        <v>6550926</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8972,10 +8972,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130063359</v>
+        <v>130063351</v>
       </c>
       <c r="B76" t="n">
-        <v>8440</v>
+        <v>75286</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8983,21 +8983,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106554</v>
+        <v>6426</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9007,10 +9007,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>317525</v>
+        <v>317464</v>
       </c>
       <c r="R76" t="n">
-        <v>6550630</v>
+        <v>6550904</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9053,6 +9053,21 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9069,32 +9084,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130063351</v>
+        <v>130063337</v>
       </c>
       <c r="B77" t="n">
-        <v>75286</v>
+        <v>97166</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9104,10 +9119,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>317464</v>
+        <v>317425</v>
       </c>
       <c r="R77" t="n">
-        <v>6550904</v>
+        <v>6550915</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9150,21 +9165,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -10187,41 +10187,38 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130175870</v>
+        <v>130177191</v>
       </c>
       <c r="B86" t="n">
-        <v>92211</v>
+        <v>97202</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5467</v>
+        <v>2590</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10229,10 +10226,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>317429</v>
+        <v>317331</v>
       </c>
       <c r="R86" t="n">
-        <v>6550919</v>
+        <v>6550757</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10279,7 +10276,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Moseblåbärgranskog</t>
+          <t>Blåbärgranskog</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -10312,38 +10309,41 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130177191</v>
+        <v>130175870</v>
       </c>
       <c r="B87" t="n">
-        <v>97202</v>
+        <v>92211</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2590</v>
+        <v>5467</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -10351,10 +10351,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>317331</v>
+        <v>317429</v>
       </c>
       <c r="R87" t="n">
-        <v>6550757</v>
+        <v>6550919</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
+          <t>Moseblåbärgranskog</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
@@ -10434,10 +10434,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130177708</v>
+        <v>130177180</v>
       </c>
       <c r="B88" t="n">
-        <v>75286</v>
+        <v>97202</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10445,30 +10445,27 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -10476,10 +10473,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>317400</v>
+        <v>317344</v>
       </c>
       <c r="R88" t="n">
-        <v>6550946</v>
+        <v>6550753</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10526,22 +10523,22 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Mosseblåbärgranskog</t>
+          <t>Blåbärgranskog</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>På bark # Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10559,10 +10556,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130177180</v>
+        <v>130177708</v>
       </c>
       <c r="B89" t="n">
-        <v>97202</v>
+        <v>75286</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10570,27 +10567,30 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>317344</v>
+        <v>317400</v>
       </c>
       <c r="R89" t="n">
-        <v>6550753</v>
+        <v>6550946</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10648,22 +10648,22 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
+          <t>Mosseblåbärgranskog</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>På bark # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -13581,10 +13581,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130210777</v>
+        <v>130210771</v>
       </c>
       <c r="B117" t="n">
-        <v>8451</v>
+        <v>93010</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13592,39 +13592,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>317283</v>
+        <v>317240</v>
       </c>
       <c r="R117" t="n">
-        <v>6550823</v>
+        <v>6550922</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13683,10 +13678,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130210771</v>
+        <v>130210777</v>
       </c>
       <c r="B118" t="n">
-        <v>93010</v>
+        <v>8451</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13694,34 +13689,39 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>317240</v>
+        <v>317283</v>
       </c>
       <c r="R118" t="n">
-        <v>6550922</v>
+        <v>6550823</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13897,45 +13897,50 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130210768</v>
+        <v>130210752</v>
       </c>
       <c r="B120" t="n">
-        <v>97166</v>
+        <v>8451</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>317274</v>
+        <v>317348</v>
       </c>
       <c r="R120" t="n">
-        <v>6550981</v>
+        <v>6550887</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -14009,32 +14014,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130210757</v>
+        <v>130210768</v>
       </c>
       <c r="B121" t="n">
-        <v>75286</v>
+        <v>97166</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14044,10 +14049,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>317402</v>
+        <v>317274</v>
       </c>
       <c r="R121" t="n">
-        <v>6550941</v>
+        <v>6550981</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14093,17 +14098,17 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14121,10 +14126,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130210752</v>
+        <v>130210757</v>
       </c>
       <c r="B122" t="n">
-        <v>8451</v>
+        <v>75286</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14132,39 +14137,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>6426</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>317348</v>
+        <v>317402</v>
       </c>
       <c r="R122" t="n">
-        <v>6550887</v>
+        <v>6550941</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14210,17 +14210,17 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -2776,7 +2776,7 @@
         <v>129835851</v>
       </c>
       <c r="B20" t="n">
-        <v>91749</v>
+        <v>91662</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>129835710</v>
       </c>
       <c r="B22" t="n">
-        <v>44080</v>
+        <v>43995</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>129835991</v>
       </c>
       <c r="B24" t="n">
-        <v>91538</v>
+        <v>91451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>129835737</v>
       </c>
       <c r="B25" t="n">
-        <v>44080</v>
+        <v>43995</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>129835977</v>
       </c>
       <c r="B26" t="n">
-        <v>92001</v>
+        <v>91914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3640,10 +3640,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129835752</v>
+        <v>129835803</v>
       </c>
       <c r="B27" t="n">
-        <v>44080</v>
+        <v>8451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3651,21 +3651,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101735</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3680,14 +3680,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lögarehöljen S., Dls</t>
+          <t>Pengehöljen O., Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>317326</v>
+        <v>317185</v>
       </c>
       <c r="R27" t="n">
-        <v>6550956</v>
+        <v>6550868</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3739,17 +3739,17 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk # Fomes fomentarius</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3767,10 +3767,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129835803</v>
+        <v>129835752</v>
       </c>
       <c r="B28" t="n">
-        <v>8451</v>
+        <v>43995</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3778,21 +3778,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>101735</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3807,14 +3807,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Pengehöljen O., Dls</t>
+          <t>Lögarehöljen S., Dls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>317185</v>
+        <v>317326</v>
       </c>
       <c r="R28" t="n">
-        <v>6550868</v>
+        <v>6550956</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3866,17 +3866,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>Fnöskticka på björk # Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4151,7 +4151,7 @@
         <v>129835724</v>
       </c>
       <c r="B31" t="n">
-        <v>44080</v>
+        <v>43995</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>129607603</v>
       </c>
       <c r="B33" t="n">
-        <v>78846</v>
+        <v>78761</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130063324</v>
+        <v>130063325</v>
       </c>
       <c r="B38" t="n">
         <v>97202</v>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>317307</v>
+        <v>317315</v>
       </c>
       <c r="R38" t="n">
-        <v>6550995</v>
+        <v>6550988</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5057,7 +5057,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130063325</v>
+        <v>130063324</v>
       </c>
       <c r="B39" t="n">
         <v>97202</v>
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>317315</v>
+        <v>317307</v>
       </c>
       <c r="R39" t="n">
-        <v>6550988</v>
+        <v>6550995</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5348,10 +5348,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130063322</v>
+        <v>130063331</v>
       </c>
       <c r="B42" t="n">
-        <v>80245</v>
+        <v>97541</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5359,21 +5359,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229497</v>
+        <v>2569</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5383,10 +5383,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>317366</v>
+        <v>317408</v>
       </c>
       <c r="R42" t="n">
-        <v>6550944</v>
+        <v>6550956</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5429,21 +5429,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5460,10 +5445,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130063331</v>
+        <v>130063357</v>
       </c>
       <c r="B43" t="n">
-        <v>97541</v>
+        <v>57016</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5471,34 +5456,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2569</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>317408</v>
+        <v>317515</v>
       </c>
       <c r="R43" t="n">
-        <v>6550956</v>
+        <v>6550638</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5557,10 +5547,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130063357</v>
+        <v>130063322</v>
       </c>
       <c r="B44" t="n">
-        <v>57016</v>
+        <v>80245</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5568,39 +5558,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>229497</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>317515</v>
+        <v>317366</v>
       </c>
       <c r="R44" t="n">
-        <v>6550638</v>
+        <v>6550944</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5643,6 +5628,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5659,10 +5659,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130063350</v>
+        <v>130063355</v>
       </c>
       <c r="B45" t="n">
-        <v>91110</v>
+        <v>8451</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5670,34 +5670,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5685</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>317461</v>
+        <v>317544</v>
       </c>
       <c r="R45" t="n">
-        <v>6550934</v>
+        <v>6550707</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5771,10 +5776,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130063355</v>
+        <v>130063350</v>
       </c>
       <c r="B46" t="n">
-        <v>8451</v>
+        <v>91110</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5782,39 +5787,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>5685</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>317544</v>
+        <v>317461</v>
       </c>
       <c r="R46" t="n">
-        <v>6550707</v>
+        <v>6550934</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6413,10 +6413,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130063318</v>
+        <v>130063353</v>
       </c>
       <c r="B52" t="n">
-        <v>8451</v>
+        <v>91110</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6424,39 +6424,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>5685</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>317387</v>
+        <v>317478</v>
       </c>
       <c r="R52" t="n">
-        <v>6550788</v>
+        <v>6550898</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6530,10 +6525,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130063353</v>
+        <v>130063330</v>
       </c>
       <c r="B53" t="n">
-        <v>91110</v>
+        <v>91692</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6541,21 +6536,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5685</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6565,10 +6560,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>317478</v>
+        <v>317408</v>
       </c>
       <c r="R53" t="n">
-        <v>6550898</v>
+        <v>6550961</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6614,17 +6609,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6642,10 +6637,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130063330</v>
+        <v>130063318</v>
       </c>
       <c r="B54" t="n">
-        <v>91692</v>
+        <v>8451</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6653,34 +6648,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>317408</v>
+        <v>317387</v>
       </c>
       <c r="R54" t="n">
-        <v>6550961</v>
+        <v>6550788</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6726,17 +6726,17 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6754,50 +6754,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130063339</v>
+        <v>130063344</v>
       </c>
       <c r="B55" t="n">
-        <v>5197</v>
+        <v>97166</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>317422</v>
+        <v>317456</v>
       </c>
       <c r="R55" t="n">
-        <v>6550917</v>
+        <v>6550897</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6840,21 +6835,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6968,10 +6948,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130063344</v>
+        <v>130063343</v>
       </c>
       <c r="B57" t="n">
-        <v>97166</v>
+        <v>91728</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6979,21 +6959,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7003,10 +6983,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>317456</v>
+        <v>317442</v>
       </c>
       <c r="R57" t="n">
-        <v>6550897</v>
+        <v>6550932</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7049,6 +7029,21 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7162,45 +7157,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130063343</v>
+        <v>130063339</v>
       </c>
       <c r="B59" t="n">
-        <v>91728</v>
+        <v>5197</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>317442</v>
+        <v>317422</v>
       </c>
       <c r="R59" t="n">
-        <v>6550932</v>
+        <v>6550917</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7468,10 +7468,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130063332</v>
+        <v>130063317</v>
       </c>
       <c r="B62" t="n">
-        <v>75286</v>
+        <v>8451</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7479,34 +7479,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6426</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>317425</v>
+        <v>317378</v>
       </c>
       <c r="R62" t="n">
-        <v>6550935</v>
+        <v>6550754</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7549,6 +7554,21 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7565,10 +7585,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130063342</v>
+        <v>130063341</v>
       </c>
       <c r="B63" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7576,21 +7596,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7682,10 +7702,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130063341</v>
+        <v>130063332</v>
       </c>
       <c r="B64" t="n">
-        <v>5197</v>
+        <v>75286</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7693,39 +7713,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>317442</v>
+        <v>317425</v>
       </c>
       <c r="R64" t="n">
-        <v>6550932</v>
+        <v>6550935</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7768,21 +7783,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7799,10 +7799,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130063317</v>
+        <v>130063342</v>
       </c>
       <c r="B65" t="n">
-        <v>8451</v>
+        <v>5177</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7810,27 +7810,27 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>317378</v>
+        <v>317442</v>
       </c>
       <c r="R65" t="n">
-        <v>6550754</v>
+        <v>6550932</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7888,17 +7888,17 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8145,10 +8145,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130063333</v>
+        <v>130063326</v>
       </c>
       <c r="B68" t="n">
-        <v>5177</v>
+        <v>91692</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8156,39 +8156,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>317428</v>
+        <v>317328</v>
       </c>
       <c r="R68" t="n">
-        <v>6550930</v>
+        <v>6550975</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8262,10 +8257,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130063354</v>
+        <v>130063333</v>
       </c>
       <c r="B69" t="n">
-        <v>93010</v>
+        <v>5177</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8273,34 +8268,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>317491</v>
+        <v>317428</v>
       </c>
       <c r="R69" t="n">
-        <v>6550822</v>
+        <v>6550930</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8343,6 +8343,21 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8359,10 +8374,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130063326</v>
+        <v>130063354</v>
       </c>
       <c r="B70" t="n">
-        <v>91692</v>
+        <v>93010</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8370,21 +8385,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8394,10 +8409,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>317328</v>
+        <v>317491</v>
       </c>
       <c r="R70" t="n">
-        <v>6550975</v>
+        <v>6550822</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8440,21 +8455,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8471,10 +8471,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130063329</v>
+        <v>130063340</v>
       </c>
       <c r="B71" t="n">
-        <v>97541</v>
+        <v>5177</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8482,21 +8482,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2569</v>
+        <v>100526</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8506,10 +8506,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>317411</v>
+        <v>317439</v>
       </c>
       <c r="R71" t="n">
-        <v>6550970</v>
+        <v>6550940</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8550,6 +8550,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8568,10 +8569,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130063340</v>
+        <v>130063329</v>
       </c>
       <c r="B72" t="n">
-        <v>5177</v>
+        <v>97541</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8579,21 +8580,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100526</v>
+        <v>2569</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8603,10 +8604,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>317439</v>
+        <v>317411</v>
       </c>
       <c r="R72" t="n">
-        <v>6550940</v>
+        <v>6550970</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8647,7 +8648,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8666,32 +8666,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130063328</v>
+        <v>130063337</v>
       </c>
       <c r="B73" t="n">
-        <v>80245</v>
+        <v>97166</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229497</v>
+        <v>53</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>317351</v>
+        <v>317425</v>
       </c>
       <c r="R73" t="n">
-        <v>6550971</v>
+        <v>6550915</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8747,21 +8747,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8778,10 +8763,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130063359</v>
+        <v>130063351</v>
       </c>
       <c r="B74" t="n">
-        <v>8440</v>
+        <v>75286</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8789,21 +8774,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106554</v>
+        <v>6426</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8813,10 +8798,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>317525</v>
+        <v>317464</v>
       </c>
       <c r="R74" t="n">
-        <v>6550630</v>
+        <v>6550904</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8859,6 +8844,21 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8972,10 +8972,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130063351</v>
+        <v>130063328</v>
       </c>
       <c r="B76" t="n">
-        <v>75286</v>
+        <v>80245</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8983,21 +8983,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9007,10 +9007,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>317464</v>
+        <v>317351</v>
       </c>
       <c r="R76" t="n">
-        <v>6550904</v>
+        <v>6550971</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9056,17 +9056,17 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -9084,32 +9084,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130063337</v>
+        <v>130063359</v>
       </c>
       <c r="B77" t="n">
-        <v>97166</v>
+        <v>8440</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9119,10 +9119,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>317425</v>
+        <v>317525</v>
       </c>
       <c r="R77" t="n">
-        <v>6550915</v>
+        <v>6550630</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -10146,7 +10146,7 @@
         <v>0</v>
       </c>
       <c r="AE85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
@@ -10434,10 +10434,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130177180</v>
+        <v>130177708</v>
       </c>
       <c r="B88" t="n">
-        <v>97202</v>
+        <v>75286</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10445,27 +10445,30 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -10473,10 +10476,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>317344</v>
+        <v>317400</v>
       </c>
       <c r="R88" t="n">
-        <v>6550753</v>
+        <v>6550946</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10523,22 +10526,22 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
+          <t>Mosseblåbärgranskog</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>På bark # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10556,10 +10559,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130177708</v>
+        <v>130177180</v>
       </c>
       <c r="B89" t="n">
-        <v>75286</v>
+        <v>97202</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10567,30 +10570,27 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>317400</v>
+        <v>317344</v>
       </c>
       <c r="R89" t="n">
-        <v>6550946</v>
+        <v>6550753</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10648,22 +10648,22 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Mosseblåbärgranskog</t>
+          <t>Blåbärgranskog</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>På bark # Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10875,32 +10875,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130210782</v>
+        <v>130210783</v>
       </c>
       <c r="B92" t="n">
-        <v>97166</v>
+        <v>97202</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10987,7 +10987,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130210783</v>
+        <v>130210766</v>
       </c>
       <c r="B93" t="n">
         <v>97202</v>
@@ -11022,10 +11022,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>317282</v>
+        <v>317236</v>
       </c>
       <c r="R93" t="n">
-        <v>6550790</v>
+        <v>6550997</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11068,21 +11068,6 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11099,32 +11084,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130210766</v>
+        <v>130210782</v>
       </c>
       <c r="B94" t="n">
-        <v>97202</v>
+        <v>97166</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11134,10 +11119,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>317236</v>
+        <v>317282</v>
       </c>
       <c r="R94" t="n">
-        <v>6550997</v>
+        <v>6550790</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11180,6 +11165,21 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -12531,32 +12531,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>130210780</v>
+        <v>130210759</v>
       </c>
       <c r="B107" t="n">
-        <v>97166</v>
+        <v>75286</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12566,10 +12566,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>317275</v>
+        <v>317390</v>
       </c>
       <c r="R107" t="n">
-        <v>6550801</v>
+        <v>6550928</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12615,17 +12615,17 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12643,32 +12643,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130210759</v>
+        <v>130210780</v>
       </c>
       <c r="B108" t="n">
-        <v>75286</v>
+        <v>97166</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12678,10 +12678,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>317390</v>
+        <v>317275</v>
       </c>
       <c r="R108" t="n">
-        <v>6550928</v>
+        <v>6550801</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12727,17 +12727,17 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12867,32 +12867,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130210769</v>
+        <v>130210789</v>
       </c>
       <c r="B110" t="n">
-        <v>97166</v>
+        <v>97202</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12902,10 +12902,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>317269</v>
+        <v>317326</v>
       </c>
       <c r="R110" t="n">
-        <v>6550970</v>
+        <v>6550738</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12948,21 +12948,6 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
@@ -12979,32 +12964,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>130210789</v>
+        <v>130210769</v>
       </c>
       <c r="B111" t="n">
-        <v>97202</v>
+        <v>97166</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -13014,10 +12999,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>317326</v>
+        <v>317269</v>
       </c>
       <c r="R111" t="n">
-        <v>6550738</v>
+        <v>6550970</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -13060,6 +13045,21 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
@@ -13193,32 +13193,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130210760</v>
+        <v>130210790</v>
       </c>
       <c r="B113" t="n">
-        <v>97166</v>
+        <v>97202</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13228,10 +13228,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>317334</v>
+        <v>317336</v>
       </c>
       <c r="R113" t="n">
-        <v>6550938</v>
+        <v>6550733</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13290,7 +13290,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130210790</v>
+        <v>130210764</v>
       </c>
       <c r="B114" t="n">
         <v>97202</v>
@@ -13325,10 +13325,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>317336</v>
+        <v>317268</v>
       </c>
       <c r="R114" t="n">
-        <v>6550733</v>
+        <v>6550998</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13387,7 +13387,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130210764</v>
+        <v>130210761</v>
       </c>
       <c r="B115" t="n">
         <v>97202</v>
@@ -13422,10 +13422,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>317268</v>
+        <v>317337</v>
       </c>
       <c r="R115" t="n">
-        <v>6550998</v>
+        <v>6550964</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13484,32 +13484,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130210761</v>
+        <v>130210760</v>
       </c>
       <c r="B116" t="n">
-        <v>97202</v>
+        <v>97166</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13519,10 +13519,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>317337</v>
+        <v>317334</v>
       </c>
       <c r="R116" t="n">
-        <v>6550964</v>
+        <v>6550938</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13581,10 +13581,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130210771</v>
+        <v>130210777</v>
       </c>
       <c r="B117" t="n">
-        <v>93010</v>
+        <v>8451</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13592,34 +13592,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>317240</v>
+        <v>317283</v>
       </c>
       <c r="R117" t="n">
-        <v>6550922</v>
+        <v>6550823</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13678,10 +13683,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130210777</v>
+        <v>130210771</v>
       </c>
       <c r="B118" t="n">
-        <v>8451</v>
+        <v>93010</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13689,39 +13694,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>317283</v>
+        <v>317240</v>
       </c>
       <c r="R118" t="n">
-        <v>6550823</v>
+        <v>6550922</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13897,50 +13897,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130210752</v>
+        <v>130210768</v>
       </c>
       <c r="B120" t="n">
-        <v>8451</v>
+        <v>97166</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>317348</v>
+        <v>317274</v>
       </c>
       <c r="R120" t="n">
-        <v>6550887</v>
+        <v>6550981</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -14014,32 +14009,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130210768</v>
+        <v>130210757</v>
       </c>
       <c r="B121" t="n">
-        <v>97166</v>
+        <v>75286</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14049,10 +14044,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>317274</v>
+        <v>317402</v>
       </c>
       <c r="R121" t="n">
-        <v>6550981</v>
+        <v>6550941</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14098,17 +14093,17 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14126,10 +14121,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130210757</v>
+        <v>130210752</v>
       </c>
       <c r="B122" t="n">
-        <v>75286</v>
+        <v>8451</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14137,34 +14132,39 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6426</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>317402</v>
+        <v>317348</v>
       </c>
       <c r="R122" t="n">
-        <v>6550941</v>
+        <v>6550887</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14210,17 +14210,17 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -14335,10 +14335,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130210767</v>
+        <v>130210754</v>
       </c>
       <c r="B124" t="n">
-        <v>97202</v>
+        <v>75286</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14346,21 +14346,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14370,10 +14370,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>317271</v>
+        <v>317405</v>
       </c>
       <c r="R124" t="n">
-        <v>6550985</v>
+        <v>6550943</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14419,17 +14419,17 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -14447,10 +14447,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130210754</v>
+        <v>130210767</v>
       </c>
       <c r="B125" t="n">
-        <v>75286</v>
+        <v>97202</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14458,21 +14458,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14482,10 +14482,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>317405</v>
+        <v>317271</v>
       </c>
       <c r="R125" t="n">
-        <v>6550943</v>
+        <v>6550985</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14531,17 +14531,17 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -4736,10 +4736,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130063320</v>
+        <v>130063338</v>
       </c>
       <c r="B36" t="n">
-        <v>80245</v>
+        <v>75286</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4747,21 +4747,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4771,10 +4771,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>317410</v>
+        <v>317422</v>
       </c>
       <c r="R36" t="n">
-        <v>6550877</v>
+        <v>6550917</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4820,17 +4820,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130063338</v>
+        <v>130063320</v>
       </c>
       <c r="B37" t="n">
-        <v>75286</v>
+        <v>80245</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4859,21 +4859,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>317422</v>
+        <v>317410</v>
       </c>
       <c r="R37" t="n">
-        <v>6550917</v>
+        <v>6550877</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4932,17 +4932,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -6316,10 +6316,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130063336</v>
+        <v>130063318</v>
       </c>
       <c r="B51" t="n">
-        <v>75286</v>
+        <v>8451</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6327,34 +6327,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6426</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>317424</v>
+        <v>317387</v>
       </c>
       <c r="R51" t="n">
-        <v>6550930</v>
+        <v>6550788</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6397,6 +6402,21 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6413,10 +6433,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130063318</v>
+        <v>130063336</v>
       </c>
       <c r="B52" t="n">
-        <v>8451</v>
+        <v>75286</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6424,39 +6444,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6426</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>317387</v>
+        <v>317424</v>
       </c>
       <c r="R52" t="n">
-        <v>6550788</v>
+        <v>6550930</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6499,21 +6514,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -7468,10 +7468,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130063332</v>
+        <v>130063341</v>
       </c>
       <c r="B62" t="n">
-        <v>75286</v>
+        <v>5197</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7479,34 +7479,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>317425</v>
+        <v>317442</v>
       </c>
       <c r="R62" t="n">
-        <v>6550935</v>
+        <v>6550932</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7549,6 +7554,21 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7565,10 +7585,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130063342</v>
+        <v>130063317</v>
       </c>
       <c r="B63" t="n">
-        <v>5177</v>
+        <v>8451</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7576,27 +7596,27 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7605,10 +7625,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>317442</v>
+        <v>317378</v>
       </c>
       <c r="R63" t="n">
-        <v>6550932</v>
+        <v>6550754</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7654,17 +7674,17 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7682,10 +7702,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130063341</v>
+        <v>130063332</v>
       </c>
       <c r="B64" t="n">
-        <v>5197</v>
+        <v>75286</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7693,39 +7713,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>317442</v>
+        <v>317425</v>
       </c>
       <c r="R64" t="n">
-        <v>6550932</v>
+        <v>6550935</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7768,21 +7783,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7799,10 +7799,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130063317</v>
+        <v>130063342</v>
       </c>
       <c r="B65" t="n">
-        <v>8451</v>
+        <v>5177</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7810,27 +7810,27 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>317378</v>
+        <v>317442</v>
       </c>
       <c r="R65" t="n">
-        <v>6550754</v>
+        <v>6550932</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7888,17 +7888,17 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8471,10 +8471,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130063329</v>
+        <v>130063340</v>
       </c>
       <c r="B71" t="n">
-        <v>97541</v>
+        <v>5177</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8482,21 +8482,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2569</v>
+        <v>100526</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8506,10 +8506,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>317411</v>
+        <v>317439</v>
       </c>
       <c r="R71" t="n">
-        <v>6550970</v>
+        <v>6550940</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8550,6 +8550,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8568,10 +8569,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130063340</v>
+        <v>130063329</v>
       </c>
       <c r="B72" t="n">
-        <v>5177</v>
+        <v>97541</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8579,21 +8580,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100526</v>
+        <v>2569</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8603,10 +8604,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>317439</v>
+        <v>317411</v>
       </c>
       <c r="R72" t="n">
-        <v>6550940</v>
+        <v>6550970</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8647,7 +8648,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -10187,38 +10187,41 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130177191</v>
+        <v>130175870</v>
       </c>
       <c r="B86" t="n">
-        <v>97202</v>
+        <v>92211</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2590</v>
+        <v>5467</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10226,10 +10229,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>317331</v>
+        <v>317429</v>
       </c>
       <c r="R86" t="n">
-        <v>6550757</v>
+        <v>6550919</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10276,7 +10279,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
+          <t>Moseblåbärgranskog</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -10309,41 +10312,38 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130175870</v>
+        <v>130177191</v>
       </c>
       <c r="B87" t="n">
-        <v>92211</v>
+        <v>97202</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5467</v>
+        <v>2590</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -10351,10 +10351,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>317429</v>
+        <v>317331</v>
       </c>
       <c r="R87" t="n">
-        <v>6550919</v>
+        <v>6550757</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Moseblåbärgranskog</t>
+          <t>Blåbärgranskog</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
@@ -10875,32 +10875,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130210755</v>
+        <v>130210782</v>
       </c>
       <c r="B92" t="n">
-        <v>91692</v>
+        <v>97166</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10910,10 +10910,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>317405</v>
+        <v>317282</v>
       </c>
       <c r="R92" t="n">
-        <v>6550943</v>
+        <v>6550790</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10959,17 +10959,17 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -10987,32 +10987,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130210782</v>
+        <v>130210766</v>
       </c>
       <c r="B93" t="n">
-        <v>97166</v>
+        <v>97202</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11022,10 +11022,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>317282</v>
+        <v>317236</v>
       </c>
       <c r="R93" t="n">
-        <v>6550790</v>
+        <v>6550997</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11068,21 +11068,6 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11099,7 +11084,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130210766</v>
+        <v>130210783</v>
       </c>
       <c r="B94" t="n">
         <v>97202</v>
@@ -11134,10 +11119,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>317236</v>
+        <v>317282</v>
       </c>
       <c r="R94" t="n">
-        <v>6550997</v>
+        <v>6550790</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11180,6 +11165,21 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -11196,10 +11196,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130210783</v>
+        <v>130210755</v>
       </c>
       <c r="B95" t="n">
-        <v>97202</v>
+        <v>91692</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11207,21 +11207,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2590</v>
+        <v>5447</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11231,10 +11231,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>317282</v>
+        <v>317405</v>
       </c>
       <c r="R95" t="n">
-        <v>6550790</v>
+        <v>6550943</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11280,17 +11280,17 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -13897,32 +13897,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130210757</v>
+        <v>130210768</v>
       </c>
       <c r="B120" t="n">
-        <v>75286</v>
+        <v>97166</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13932,10 +13932,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>317402</v>
+        <v>317274</v>
       </c>
       <c r="R120" t="n">
-        <v>6550941</v>
+        <v>6550981</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13981,17 +13981,17 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -14009,32 +14009,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130210768</v>
+        <v>130210757</v>
       </c>
       <c r="B121" t="n">
-        <v>97166</v>
+        <v>75286</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14044,10 +14044,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>317274</v>
+        <v>317402</v>
       </c>
       <c r="R121" t="n">
-        <v>6550981</v>
+        <v>6550941</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14093,17 +14093,17 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -5659,10 +5659,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130063355</v>
+        <v>130063350</v>
       </c>
       <c r="B45" t="n">
-        <v>8451</v>
+        <v>91110</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5670,39 +5670,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>5685</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>317544</v>
+        <v>317461</v>
       </c>
       <c r="R45" t="n">
-        <v>6550707</v>
+        <v>6550934</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5776,10 +5771,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130063350</v>
+        <v>130063355</v>
       </c>
       <c r="B46" t="n">
-        <v>91110</v>
+        <v>8451</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5787,34 +5782,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5685</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>317461</v>
+        <v>317544</v>
       </c>
       <c r="R46" t="n">
-        <v>6550934</v>
+        <v>6550707</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6316,10 +6316,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130063318</v>
+        <v>130063336</v>
       </c>
       <c r="B51" t="n">
-        <v>8451</v>
+        <v>75286</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6327,39 +6327,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6426</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>317387</v>
+        <v>317424</v>
       </c>
       <c r="R51" t="n">
-        <v>6550788</v>
+        <v>6550930</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6402,21 +6397,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6433,10 +6413,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130063336</v>
+        <v>130063318</v>
       </c>
       <c r="B52" t="n">
-        <v>75286</v>
+        <v>8451</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6444,34 +6424,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6426</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>317424</v>
+        <v>317387</v>
       </c>
       <c r="R52" t="n">
-        <v>6550930</v>
+        <v>6550788</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6514,6 +6499,21 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -7468,10 +7468,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130063341</v>
+        <v>130063332</v>
       </c>
       <c r="B62" t="n">
-        <v>5197</v>
+        <v>75286</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7479,39 +7479,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>317442</v>
+        <v>317425</v>
       </c>
       <c r="R62" t="n">
-        <v>6550932</v>
+        <v>6550935</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7554,21 +7549,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7585,10 +7565,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130063317</v>
+        <v>130063342</v>
       </c>
       <c r="B63" t="n">
-        <v>8451</v>
+        <v>5177</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7596,27 +7576,27 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7625,10 +7605,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>317378</v>
+        <v>317442</v>
       </c>
       <c r="R63" t="n">
-        <v>6550754</v>
+        <v>6550932</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7674,17 +7654,17 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7702,10 +7682,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130063332</v>
+        <v>130063341</v>
       </c>
       <c r="B64" t="n">
-        <v>75286</v>
+        <v>5197</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7713,34 +7693,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>317425</v>
+        <v>317442</v>
       </c>
       <c r="R64" t="n">
-        <v>6550935</v>
+        <v>6550932</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7783,6 +7768,21 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7799,10 +7799,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130063342</v>
+        <v>130063317</v>
       </c>
       <c r="B65" t="n">
-        <v>5177</v>
+        <v>8451</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7810,27 +7810,27 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>317442</v>
+        <v>317378</v>
       </c>
       <c r="R65" t="n">
-        <v>6550932</v>
+        <v>6550754</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7888,17 +7888,17 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8471,10 +8471,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130063340</v>
+        <v>130063329</v>
       </c>
       <c r="B71" t="n">
-        <v>5177</v>
+        <v>97541</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8482,21 +8482,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100526</v>
+        <v>2569</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8506,10 +8506,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>317439</v>
+        <v>317411</v>
       </c>
       <c r="R71" t="n">
-        <v>6550940</v>
+        <v>6550970</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8550,7 +8550,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8569,10 +8568,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130063329</v>
+        <v>130063340</v>
       </c>
       <c r="B72" t="n">
-        <v>97541</v>
+        <v>5177</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8580,21 +8579,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2569</v>
+        <v>100526</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8604,10 +8603,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>317411</v>
+        <v>317439</v>
       </c>
       <c r="R72" t="n">
-        <v>6550970</v>
+        <v>6550940</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8648,6 +8647,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8666,10 +8666,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130063328</v>
+        <v>130063351</v>
       </c>
       <c r="B73" t="n">
-        <v>80245</v>
+        <v>75286</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8677,21 +8677,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>317351</v>
+        <v>317464</v>
       </c>
       <c r="R73" t="n">
-        <v>6550971</v>
+        <v>6550904</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8750,17 +8750,17 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8972,10 +8972,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130063351</v>
+        <v>130063359</v>
       </c>
       <c r="B76" t="n">
-        <v>75286</v>
+        <v>8440</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8983,21 +8983,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6426</v>
+        <v>106554</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9007,10 +9007,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>317464</v>
+        <v>317525</v>
       </c>
       <c r="R76" t="n">
-        <v>6550904</v>
+        <v>6550630</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9053,21 +9053,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9084,10 +9069,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130063359</v>
+        <v>130063328</v>
       </c>
       <c r="B77" t="n">
-        <v>8440</v>
+        <v>80245</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9095,21 +9080,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106554</v>
+        <v>229497</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9119,10 +9104,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>317525</v>
+        <v>317351</v>
       </c>
       <c r="R77" t="n">
-        <v>6550630</v>
+        <v>6550971</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9165,6 +9150,21 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -10434,10 +10434,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130177180</v>
+        <v>130177708</v>
       </c>
       <c r="B88" t="n">
-        <v>97202</v>
+        <v>75286</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10445,27 +10445,30 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -10473,10 +10476,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>317344</v>
+        <v>317400</v>
       </c>
       <c r="R88" t="n">
-        <v>6550753</v>
+        <v>6550946</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10523,22 +10526,22 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
+          <t>Mosseblåbärgranskog</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>På bark # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10556,10 +10559,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130177708</v>
+        <v>130177180</v>
       </c>
       <c r="B89" t="n">
-        <v>75286</v>
+        <v>97202</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10567,30 +10570,27 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>317400</v>
+        <v>317344</v>
       </c>
       <c r="R89" t="n">
-        <v>6550946</v>
+        <v>6550753</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10648,22 +10648,22 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Mosseblåbärgranskog</t>
+          <t>Blåbärgranskog</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>På bark # Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10875,32 +10875,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130210782</v>
+        <v>130210755</v>
       </c>
       <c r="B92" t="n">
-        <v>97166</v>
+        <v>91692</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10910,10 +10910,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>317282</v>
+        <v>317405</v>
       </c>
       <c r="R92" t="n">
-        <v>6550790</v>
+        <v>6550943</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10959,17 +10959,17 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -10987,32 +10987,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130210766</v>
+        <v>130210782</v>
       </c>
       <c r="B93" t="n">
-        <v>97202</v>
+        <v>97166</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11022,10 +11022,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>317236</v>
+        <v>317282</v>
       </c>
       <c r="R93" t="n">
-        <v>6550997</v>
+        <v>6550790</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11068,6 +11068,21 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11084,7 +11099,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130210783</v>
+        <v>130210766</v>
       </c>
       <c r="B94" t="n">
         <v>97202</v>
@@ -11119,10 +11134,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>317282</v>
+        <v>317236</v>
       </c>
       <c r="R94" t="n">
-        <v>6550790</v>
+        <v>6550997</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11165,21 +11180,6 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -11196,10 +11196,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130210755</v>
+        <v>130210783</v>
       </c>
       <c r="B95" t="n">
-        <v>91692</v>
+        <v>97202</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11207,21 +11207,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5447</v>
+        <v>2590</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11231,10 +11231,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>317405</v>
+        <v>317282</v>
       </c>
       <c r="R95" t="n">
-        <v>6550943</v>
+        <v>6550790</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11280,17 +11280,17 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -12867,32 +12867,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130210769</v>
+        <v>130210789</v>
       </c>
       <c r="B110" t="n">
-        <v>97166</v>
+        <v>97202</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12902,10 +12902,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>317269</v>
+        <v>317326</v>
       </c>
       <c r="R110" t="n">
-        <v>6550970</v>
+        <v>6550738</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12948,21 +12948,6 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
@@ -12979,32 +12964,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>130210789</v>
+        <v>130210769</v>
       </c>
       <c r="B111" t="n">
-        <v>97202</v>
+        <v>97166</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -13014,10 +12999,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>317326</v>
+        <v>317269</v>
       </c>
       <c r="R111" t="n">
-        <v>6550738</v>
+        <v>6550970</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -13060,6 +13045,21 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
@@ -13193,32 +13193,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130210760</v>
+        <v>130210761</v>
       </c>
       <c r="B113" t="n">
-        <v>97166</v>
+        <v>97202</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13228,10 +13228,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>317334</v>
+        <v>317337</v>
       </c>
       <c r="R113" t="n">
-        <v>6550938</v>
+        <v>6550964</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13290,7 +13290,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130210761</v>
+        <v>130210790</v>
       </c>
       <c r="B114" t="n">
         <v>97202</v>
@@ -13325,10 +13325,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>317337</v>
+        <v>317336</v>
       </c>
       <c r="R114" t="n">
-        <v>6550964</v>
+        <v>6550733</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13387,7 +13387,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130210790</v>
+        <v>130210764</v>
       </c>
       <c r="B115" t="n">
         <v>97202</v>
@@ -13422,10 +13422,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>317336</v>
+        <v>317268</v>
       </c>
       <c r="R115" t="n">
-        <v>6550733</v>
+        <v>6550998</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13484,32 +13484,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130210764</v>
+        <v>130210760</v>
       </c>
       <c r="B116" t="n">
-        <v>97202</v>
+        <v>97166</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13519,10 +13519,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>317268</v>
+        <v>317334</v>
       </c>
       <c r="R116" t="n">
-        <v>6550998</v>
+        <v>6550938</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13897,32 +13897,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130210768</v>
+        <v>130210757</v>
       </c>
       <c r="B120" t="n">
-        <v>97166</v>
+        <v>75286</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13932,10 +13932,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>317274</v>
+        <v>317402</v>
       </c>
       <c r="R120" t="n">
-        <v>6550981</v>
+        <v>6550941</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13981,17 +13981,17 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -14009,32 +14009,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130210757</v>
+        <v>130210768</v>
       </c>
       <c r="B121" t="n">
-        <v>75286</v>
+        <v>97166</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14044,10 +14044,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>317402</v>
+        <v>317274</v>
       </c>
       <c r="R121" t="n">
-        <v>6550941</v>
+        <v>6550981</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14093,17 +14093,17 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -10187,41 +10187,38 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130175870</v>
+        <v>130177191</v>
       </c>
       <c r="B86" t="n">
-        <v>92211</v>
+        <v>97202</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5467</v>
+        <v>2590</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10229,10 +10226,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>317429</v>
+        <v>317331</v>
       </c>
       <c r="R86" t="n">
-        <v>6550919</v>
+        <v>6550757</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10279,7 +10276,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Moseblåbärgranskog</t>
+          <t>Blåbärgranskog</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -10312,38 +10309,41 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130177191</v>
+        <v>130175870</v>
       </c>
       <c r="B87" t="n">
-        <v>97202</v>
+        <v>92211</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2590</v>
+        <v>5467</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -10351,10 +10351,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>317331</v>
+        <v>317429</v>
       </c>
       <c r="R87" t="n">
-        <v>6550757</v>
+        <v>6550919</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
+          <t>Moseblåbärgranskog</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
@@ -10434,10 +10434,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130177708</v>
+        <v>130177180</v>
       </c>
       <c r="B88" t="n">
-        <v>75286</v>
+        <v>97202</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10445,30 +10445,27 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -10476,10 +10473,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>317400</v>
+        <v>317344</v>
       </c>
       <c r="R88" t="n">
-        <v>6550946</v>
+        <v>6550753</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10526,22 +10523,22 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Mosseblåbärgranskog</t>
+          <t>Blåbärgranskog</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>På bark # Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10559,10 +10556,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130177180</v>
+        <v>130177708</v>
       </c>
       <c r="B89" t="n">
-        <v>97202</v>
+        <v>75286</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10570,27 +10567,30 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>317344</v>
+        <v>317400</v>
       </c>
       <c r="R89" t="n">
-        <v>6550753</v>
+        <v>6550946</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10648,22 +10648,22 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
+          <t>Mosseblåbärgranskog</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>På bark # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -12867,32 +12867,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130210789</v>
+        <v>130210769</v>
       </c>
       <c r="B110" t="n">
-        <v>97202</v>
+        <v>97166</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12902,10 +12902,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>317326</v>
+        <v>317269</v>
       </c>
       <c r="R110" t="n">
-        <v>6550738</v>
+        <v>6550970</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12948,6 +12948,21 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
@@ -12964,32 +12979,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>130210769</v>
+        <v>130210789</v>
       </c>
       <c r="B111" t="n">
-        <v>97166</v>
+        <v>97202</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12999,10 +13014,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>317269</v>
+        <v>317326</v>
       </c>
       <c r="R111" t="n">
-        <v>6550970</v>
+        <v>6550738</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -13045,21 +13060,6 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
@@ -13193,32 +13193,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130210761</v>
+        <v>130210760</v>
       </c>
       <c r="B113" t="n">
-        <v>97202</v>
+        <v>97166</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13228,10 +13228,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>317337</v>
+        <v>317334</v>
       </c>
       <c r="R113" t="n">
-        <v>6550964</v>
+        <v>6550938</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13290,7 +13290,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130210790</v>
+        <v>130210761</v>
       </c>
       <c r="B114" t="n">
         <v>97202</v>
@@ -13325,10 +13325,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>317336</v>
+        <v>317337</v>
       </c>
       <c r="R114" t="n">
-        <v>6550733</v>
+        <v>6550964</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13387,7 +13387,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130210764</v>
+        <v>130210790</v>
       </c>
       <c r="B115" t="n">
         <v>97202</v>
@@ -13422,10 +13422,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>317268</v>
+        <v>317336</v>
       </c>
       <c r="R115" t="n">
-        <v>6550998</v>
+        <v>6550733</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13484,32 +13484,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130210760</v>
+        <v>130210764</v>
       </c>
       <c r="B116" t="n">
-        <v>97166</v>
+        <v>97202</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13519,10 +13519,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>317334</v>
+        <v>317268</v>
       </c>
       <c r="R116" t="n">
-        <v>6550938</v>
+        <v>6550998</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13897,32 +13897,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130210757</v>
+        <v>130210768</v>
       </c>
       <c r="B120" t="n">
-        <v>75286</v>
+        <v>97166</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13932,10 +13932,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>317402</v>
+        <v>317274</v>
       </c>
       <c r="R120" t="n">
-        <v>6550941</v>
+        <v>6550981</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13981,17 +13981,17 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -14009,32 +14009,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130210768</v>
+        <v>130210757</v>
       </c>
       <c r="B121" t="n">
-        <v>97166</v>
+        <v>75286</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14044,10 +14044,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>317274</v>
+        <v>317402</v>
       </c>
       <c r="R121" t="n">
-        <v>6550981</v>
+        <v>6550941</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14093,17 +14093,17 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -9184,7 +9184,7 @@
         <v>130104814</v>
       </c>
       <c r="B78" t="n">
-        <v>78846</v>
+        <v>78849</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
         <v>130104706</v>
       </c>
       <c r="B79" t="n">
-        <v>92370</v>
+        <v>92373</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>130104411</v>
       </c>
       <c r="B80" t="n">
-        <v>78846</v>
+        <v>78849</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>130177928</v>
       </c>
       <c r="B81" t="n">
-        <v>75286</v>
+        <v>75289</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>130175963</v>
       </c>
       <c r="B82" t="n">
-        <v>78846</v>
+        <v>78849</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>130177344</v>
       </c>
       <c r="B84" t="n">
-        <v>97202</v>
+        <v>97205</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>130175755</v>
       </c>
       <c r="B85" t="n">
-        <v>92514</v>
+        <v>92517</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>130177191</v>
       </c>
       <c r="B86" t="n">
-        <v>97202</v>
+        <v>97205</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>130175870</v>
       </c>
       <c r="B87" t="n">
-        <v>92211</v>
+        <v>92214</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10434,10 +10434,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130177180</v>
+        <v>130177708</v>
       </c>
       <c r="B88" t="n">
-        <v>97202</v>
+        <v>75289</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10445,27 +10445,30 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -10473,10 +10476,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>317344</v>
+        <v>317400</v>
       </c>
       <c r="R88" t="n">
-        <v>6550753</v>
+        <v>6550946</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10523,22 +10526,22 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
+          <t>Mosseblåbärgranskog</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>På bark # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10556,10 +10559,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130177708</v>
+        <v>130177180</v>
       </c>
       <c r="B89" t="n">
-        <v>75286</v>
+        <v>97205</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10567,30 +10570,27 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>317400</v>
+        <v>317344</v>
       </c>
       <c r="R89" t="n">
-        <v>6550946</v>
+        <v>6550753</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10648,22 +10648,22 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Mosseblåbärgranskog</t>
+          <t>Blåbärgranskog</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>På bark # Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10684,7 +10684,7 @@
         <v>130210763</v>
       </c>
       <c r="B90" t="n">
-        <v>97202</v>
+        <v>97205</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>130210762</v>
       </c>
       <c r="B91" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10875,10 +10875,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130210755</v>
+        <v>130210783</v>
       </c>
       <c r="B92" t="n">
-        <v>91692</v>
+        <v>97205</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10886,21 +10886,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5447</v>
+        <v>2590</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10910,10 +10910,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>317405</v>
+        <v>317282</v>
       </c>
       <c r="R92" t="n">
-        <v>6550943</v>
+        <v>6550790</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10959,17 +10959,17 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -10987,32 +10987,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130210782</v>
+        <v>130210766</v>
       </c>
       <c r="B93" t="n">
-        <v>97166</v>
+        <v>97205</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11022,10 +11022,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>317282</v>
+        <v>317236</v>
       </c>
       <c r="R93" t="n">
-        <v>6550790</v>
+        <v>6550997</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11068,21 +11068,6 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11099,32 +11084,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130210766</v>
+        <v>130210782</v>
       </c>
       <c r="B94" t="n">
-        <v>97202</v>
+        <v>97169</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11134,10 +11119,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>317236</v>
+        <v>317282</v>
       </c>
       <c r="R94" t="n">
-        <v>6550997</v>
+        <v>6550790</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11180,6 +11165,21 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -11196,10 +11196,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130210783</v>
+        <v>130210755</v>
       </c>
       <c r="B95" t="n">
-        <v>97202</v>
+        <v>91695</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11207,21 +11207,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2590</v>
+        <v>5447</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11231,10 +11231,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>317282</v>
+        <v>317405</v>
       </c>
       <c r="R95" t="n">
-        <v>6550790</v>
+        <v>6550943</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11280,17 +11280,17 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -11311,7 +11311,7 @@
         <v>130210781</v>
       </c>
       <c r="B96" t="n">
-        <v>97202</v>
+        <v>97205</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>130210758</v>
       </c>
       <c r="B97" t="n">
-        <v>97541</v>
+        <v>97544</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>130210765</v>
       </c>
       <c r="B98" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>130210753</v>
       </c>
       <c r="B100" t="n">
-        <v>75286</v>
+        <v>75289</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>130210787</v>
       </c>
       <c r="B101" t="n">
-        <v>97202</v>
+        <v>97205</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>130210780</v>
       </c>
       <c r="B107" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12643,10 +12643,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130210756</v>
+        <v>130210759</v>
       </c>
       <c r="B108" t="n">
-        <v>91692</v>
+        <v>75289</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12654,21 +12654,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12678,10 +12678,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>317409</v>
+        <v>317390</v>
       </c>
       <c r="R108" t="n">
-        <v>6550951</v>
+        <v>6550928</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12755,10 +12755,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130210759</v>
+        <v>130210756</v>
       </c>
       <c r="B109" t="n">
-        <v>75286</v>
+        <v>91695</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12766,21 +12766,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12790,10 +12790,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>317390</v>
+        <v>317409</v>
       </c>
       <c r="R109" t="n">
-        <v>6550928</v>
+        <v>6550951</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12870,7 +12870,7 @@
         <v>130210769</v>
       </c>
       <c r="B110" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>130210789</v>
       </c>
       <c r="B111" t="n">
-        <v>97202</v>
+        <v>97205</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>130210760</v>
       </c>
       <c r="B113" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13290,10 +13290,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130210761</v>
+        <v>130210790</v>
       </c>
       <c r="B114" t="n">
-        <v>97202</v>
+        <v>97205</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13325,10 +13325,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>317337</v>
+        <v>317336</v>
       </c>
       <c r="R114" t="n">
-        <v>6550964</v>
+        <v>6550733</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13387,10 +13387,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130210790</v>
+        <v>130210764</v>
       </c>
       <c r="B115" t="n">
-        <v>97202</v>
+        <v>97205</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13422,10 +13422,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>317336</v>
+        <v>317268</v>
       </c>
       <c r="R115" t="n">
-        <v>6550733</v>
+        <v>6550998</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13484,10 +13484,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130210764</v>
+        <v>130210761</v>
       </c>
       <c r="B116" t="n">
-        <v>97202</v>
+        <v>97205</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13519,10 +13519,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>317268</v>
+        <v>317337</v>
       </c>
       <c r="R116" t="n">
-        <v>6550998</v>
+        <v>6550964</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13584,7 +13584,7 @@
         <v>130210771</v>
       </c>
       <c r="B117" t="n">
-        <v>93010</v>
+        <v>93013</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>130210768</v>
       </c>
       <c r="B120" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>130210757</v>
       </c>
       <c r="B121" t="n">
-        <v>75286</v>
+        <v>75289</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>130210773</v>
       </c>
       <c r="B123" t="n">
-        <v>93010</v>
+        <v>93013</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14335,10 +14335,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130210767</v>
+        <v>130210754</v>
       </c>
       <c r="B124" t="n">
-        <v>97202</v>
+        <v>75289</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14346,21 +14346,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14370,10 +14370,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>317271</v>
+        <v>317405</v>
       </c>
       <c r="R124" t="n">
-        <v>6550985</v>
+        <v>6550943</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14419,17 +14419,17 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -14447,10 +14447,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130210754</v>
+        <v>130210767</v>
       </c>
       <c r="B125" t="n">
-        <v>75286</v>
+        <v>97205</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14458,21 +14458,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14482,10 +14482,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>317405</v>
+        <v>317271</v>
       </c>
       <c r="R125" t="n">
-        <v>6550943</v>
+        <v>6550985</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14531,17 +14531,17 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -14562,7 +14562,7 @@
         <v>130177671</v>
       </c>
       <c r="B126" t="n">
-        <v>75286</v>
+        <v>75289</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -9559,7 +9559,7 @@
         <v>130177928</v>
       </c>
       <c r="B81" t="n">
-        <v>75289</v>
+        <v>75315</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>130175963</v>
       </c>
       <c r="B82" t="n">
-        <v>78849</v>
+        <v>78875</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>130176280</v>
       </c>
       <c r="B83" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>130177344</v>
       </c>
       <c r="B84" t="n">
-        <v>97205</v>
+        <v>97231</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>130175755</v>
       </c>
       <c r="B85" t="n">
-        <v>92517</v>
+        <v>92543</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>130177191</v>
       </c>
       <c r="B86" t="n">
-        <v>97205</v>
+        <v>97231</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>130175870</v>
       </c>
       <c r="B87" t="n">
-        <v>92214</v>
+        <v>92240</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10434,10 +10434,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130177708</v>
+        <v>130177180</v>
       </c>
       <c r="B88" t="n">
-        <v>75289</v>
+        <v>97231</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10445,30 +10445,27 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -10476,10 +10473,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>317400</v>
+        <v>317344</v>
       </c>
       <c r="R88" t="n">
-        <v>6550946</v>
+        <v>6550753</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10526,22 +10523,22 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Mosseblåbärgranskog</t>
+          <t>Blåbärgranskog</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>På bark # Picea abies</t>
+          <t>Låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10559,10 +10556,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130177180</v>
+        <v>130177708</v>
       </c>
       <c r="B89" t="n">
-        <v>97205</v>
+        <v>75315</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10570,27 +10567,30 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>317344</v>
+        <v>317400</v>
       </c>
       <c r="R89" t="n">
-        <v>6550753</v>
+        <v>6550946</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10648,22 +10648,22 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
+          <t>Mosseblåbärgranskog</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Låga # Pinus sylvestris</t>
+          <t>På bark # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10684,7 +10684,7 @@
         <v>130210763</v>
       </c>
       <c r="B90" t="n">
-        <v>97205</v>
+        <v>97231</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>130210762</v>
       </c>
       <c r="B91" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10875,32 +10875,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130210783</v>
+        <v>130210782</v>
       </c>
       <c r="B92" t="n">
-        <v>97205</v>
+        <v>97195</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10987,10 +10987,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130210766</v>
+        <v>130210755</v>
       </c>
       <c r="B93" t="n">
-        <v>97205</v>
+        <v>91721</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10998,21 +10998,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2590</v>
+        <v>5447</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11022,10 +11022,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>317236</v>
+        <v>317405</v>
       </c>
       <c r="R93" t="n">
-        <v>6550997</v>
+        <v>6550943</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11068,6 +11068,21 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11084,32 +11099,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130210782</v>
+        <v>130210783</v>
       </c>
       <c r="B94" t="n">
-        <v>97169</v>
+        <v>97231</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11196,10 +11211,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130210755</v>
+        <v>130210766</v>
       </c>
       <c r="B95" t="n">
-        <v>91695</v>
+        <v>97231</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11207,21 +11222,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5447</v>
+        <v>2590</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11231,10 +11246,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>317405</v>
+        <v>317236</v>
       </c>
       <c r="R95" t="n">
-        <v>6550943</v>
+        <v>6550997</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11277,21 +11292,6 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11311,7 +11311,7 @@
         <v>130210781</v>
       </c>
       <c r="B96" t="n">
-        <v>97205</v>
+        <v>97231</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>130210758</v>
       </c>
       <c r="B97" t="n">
-        <v>97544</v>
+        <v>97570</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>130210765</v>
       </c>
       <c r="B98" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>130210778</v>
       </c>
       <c r="B99" t="n">
-        <v>44080</v>
+        <v>44106</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>130210753</v>
       </c>
       <c r="B100" t="n">
-        <v>75289</v>
+        <v>75315</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>130210787</v>
       </c>
       <c r="B101" t="n">
-        <v>97205</v>
+        <v>97231</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>130210780</v>
       </c>
       <c r="B107" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>130210759</v>
       </c>
       <c r="B108" t="n">
-        <v>75289</v>
+        <v>75315</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>130210756</v>
       </c>
       <c r="B109" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>130210769</v>
       </c>
       <c r="B110" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>130210789</v>
       </c>
       <c r="B111" t="n">
-        <v>97205</v>
+        <v>97231</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13193,32 +13193,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130210760</v>
+        <v>130210764</v>
       </c>
       <c r="B113" t="n">
-        <v>97169</v>
+        <v>97231</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13228,10 +13228,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>317334</v>
+        <v>317268</v>
       </c>
       <c r="R113" t="n">
-        <v>6550938</v>
+        <v>6550998</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13290,32 +13290,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130210790</v>
+        <v>130210760</v>
       </c>
       <c r="B114" t="n">
-        <v>97205</v>
+        <v>97195</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13325,10 +13325,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>317336</v>
+        <v>317334</v>
       </c>
       <c r="R114" t="n">
-        <v>6550733</v>
+        <v>6550938</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13387,10 +13387,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130210764</v>
+        <v>130210790</v>
       </c>
       <c r="B115" t="n">
-        <v>97205</v>
+        <v>97231</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13422,10 +13422,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>317268</v>
+        <v>317336</v>
       </c>
       <c r="R115" t="n">
-        <v>6550998</v>
+        <v>6550733</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13487,7 +13487,7 @@
         <v>130210761</v>
       </c>
       <c r="B116" t="n">
-        <v>97205</v>
+        <v>97231</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>130210771</v>
       </c>
       <c r="B117" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>130210768</v>
       </c>
       <c r="B120" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14009,10 +14009,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130210757</v>
+        <v>130210752</v>
       </c>
       <c r="B121" t="n">
-        <v>75289</v>
+        <v>8451</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14020,34 +14020,39 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6426</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>317402</v>
+        <v>317348</v>
       </c>
       <c r="R121" t="n">
-        <v>6550941</v>
+        <v>6550887</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14093,17 +14098,17 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14121,10 +14126,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130210752</v>
+        <v>130210757</v>
       </c>
       <c r="B122" t="n">
-        <v>8451</v>
+        <v>75315</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14132,39 +14137,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>6426</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>317348</v>
+        <v>317402</v>
       </c>
       <c r="R122" t="n">
-        <v>6550887</v>
+        <v>6550941</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14210,17 +14210,17 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -14241,7 +14241,7 @@
         <v>130210773</v>
       </c>
       <c r="B123" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14335,10 +14335,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130210754</v>
+        <v>130210767</v>
       </c>
       <c r="B124" t="n">
-        <v>75289</v>
+        <v>97231</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14346,21 +14346,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14370,10 +14370,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>317405</v>
+        <v>317271</v>
       </c>
       <c r="R124" t="n">
-        <v>6550943</v>
+        <v>6550985</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14419,17 +14419,17 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -14447,10 +14447,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130210767</v>
+        <v>130210754</v>
       </c>
       <c r="B125" t="n">
-        <v>97205</v>
+        <v>75315</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14458,21 +14458,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14482,10 +14482,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>317271</v>
+        <v>317405</v>
       </c>
       <c r="R125" t="n">
-        <v>6550985</v>
+        <v>6550943</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14531,17 +14531,17 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -14562,7 +14562,7 @@
         <v>130177671</v>
       </c>
       <c r="B126" t="n">
-        <v>75289</v>
+        <v>75315</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY126"/>
+  <dimension ref="A1:AY128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14682,6 +14682,240 @@
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>130645363</v>
+      </c>
+      <c r="B127" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>317385</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6550932</v>
+      </c>
+      <c r="S127" t="n">
+        <v>5</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>130645364</v>
+      </c>
+      <c r="B128" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>O om Pengehöljen, Dls</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>317337</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6550964</v>
+      </c>
+      <c r="S128" t="n">
+        <v>5</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -9943,7 +9943,7 @@
         <v>130177344</v>
       </c>
       <c r="B84" t="n">
-        <v>97231</v>
+        <v>97232</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>130175755</v>
       </c>
       <c r="B85" t="n">
-        <v>92543</v>
+        <v>92544</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>130177191</v>
       </c>
       <c r="B86" t="n">
-        <v>97231</v>
+        <v>97232</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>130175870</v>
       </c>
       <c r="B87" t="n">
-        <v>92240</v>
+        <v>92241</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>130177180</v>
       </c>
       <c r="B88" t="n">
-        <v>97231</v>
+        <v>97232</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>130210763</v>
       </c>
       <c r="B90" t="n">
-        <v>97231</v>
+        <v>97232</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>130210762</v>
       </c>
       <c r="B91" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>130210782</v>
       </c>
       <c r="B92" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10987,10 +10987,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130210755</v>
+        <v>130210783</v>
       </c>
       <c r="B93" t="n">
-        <v>91721</v>
+        <v>97232</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10998,21 +10998,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5447</v>
+        <v>2590</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11022,10 +11022,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>317405</v>
+        <v>317282</v>
       </c>
       <c r="R93" t="n">
-        <v>6550943</v>
+        <v>6550790</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11071,17 +11071,17 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11099,10 +11099,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130210783</v>
+        <v>130210766</v>
       </c>
       <c r="B94" t="n">
-        <v>97231</v>
+        <v>97232</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11134,10 +11134,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>317282</v>
+        <v>317236</v>
       </c>
       <c r="R94" t="n">
-        <v>6550790</v>
+        <v>6550997</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11180,21 +11180,6 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -11211,10 +11196,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130210766</v>
+        <v>130210755</v>
       </c>
       <c r="B95" t="n">
-        <v>97231</v>
+        <v>91722</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11222,21 +11207,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2590</v>
+        <v>5447</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11246,10 +11231,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>317236</v>
+        <v>317405</v>
       </c>
       <c r="R95" t="n">
-        <v>6550997</v>
+        <v>6550943</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11292,6 +11277,21 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11311,7 +11311,7 @@
         <v>130210781</v>
       </c>
       <c r="B96" t="n">
-        <v>97231</v>
+        <v>97232</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>130210758</v>
       </c>
       <c r="B97" t="n">
-        <v>97570</v>
+        <v>97571</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>130210765</v>
       </c>
       <c r="B98" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>130210787</v>
       </c>
       <c r="B101" t="n">
-        <v>97231</v>
+        <v>97232</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12531,32 +12531,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>130210780</v>
+        <v>130210756</v>
       </c>
       <c r="B107" t="n">
-        <v>97195</v>
+        <v>91722</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12566,10 +12566,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>317275</v>
+        <v>317409</v>
       </c>
       <c r="R107" t="n">
-        <v>6550801</v>
+        <v>6550951</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12615,17 +12615,17 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12755,32 +12755,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130210756</v>
+        <v>130210780</v>
       </c>
       <c r="B109" t="n">
-        <v>91721</v>
+        <v>97196</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12790,10 +12790,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>317409</v>
+        <v>317275</v>
       </c>
       <c r="R109" t="n">
-        <v>6550951</v>
+        <v>6550801</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12839,17 +12839,17 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12867,32 +12867,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130210769</v>
+        <v>130210789</v>
       </c>
       <c r="B110" t="n">
-        <v>97195</v>
+        <v>97232</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12902,10 +12902,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>317269</v>
+        <v>317326</v>
       </c>
       <c r="R110" t="n">
-        <v>6550970</v>
+        <v>6550738</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12948,21 +12948,6 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
@@ -12979,10 +12964,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>130210789</v>
+        <v>130210770</v>
       </c>
       <c r="B111" t="n">
-        <v>97231</v>
+        <v>8451</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12990,34 +12975,39 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>317326</v>
+        <v>317245</v>
       </c>
       <c r="R111" t="n">
-        <v>6550738</v>
+        <v>6550930</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -13060,6 +13050,21 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
@@ -13076,50 +13081,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130210770</v>
+        <v>130210769</v>
       </c>
       <c r="B112" t="n">
-        <v>8451</v>
+        <v>97196</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>317245</v>
+        <v>317269</v>
       </c>
       <c r="R112" t="n">
-        <v>6550930</v>
+        <v>6550970</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13193,10 +13193,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130210764</v>
+        <v>130210790</v>
       </c>
       <c r="B113" t="n">
-        <v>97231</v>
+        <v>97232</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13228,10 +13228,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>317268</v>
+        <v>317336</v>
       </c>
       <c r="R113" t="n">
-        <v>6550998</v>
+        <v>6550733</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13290,32 +13290,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130210760</v>
+        <v>130210764</v>
       </c>
       <c r="B114" t="n">
-        <v>97195</v>
+        <v>97232</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13325,10 +13325,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>317334</v>
+        <v>317268</v>
       </c>
       <c r="R114" t="n">
-        <v>6550938</v>
+        <v>6550998</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13387,10 +13387,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130210790</v>
+        <v>130210761</v>
       </c>
       <c r="B115" t="n">
-        <v>97231</v>
+        <v>97232</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13422,10 +13422,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>317336</v>
+        <v>317337</v>
       </c>
       <c r="R115" t="n">
-        <v>6550733</v>
+        <v>6550964</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13484,32 +13484,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130210761</v>
+        <v>130210760</v>
       </c>
       <c r="B116" t="n">
-        <v>97231</v>
+        <v>97196</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13519,10 +13519,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>317337</v>
+        <v>317334</v>
       </c>
       <c r="R116" t="n">
-        <v>6550964</v>
+        <v>6550938</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13584,7 +13584,7 @@
         <v>130210771</v>
       </c>
       <c r="B117" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>130210768</v>
       </c>
       <c r="B120" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14009,10 +14009,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130210752</v>
+        <v>130210757</v>
       </c>
       <c r="B121" t="n">
-        <v>8451</v>
+        <v>75315</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14020,39 +14020,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>6426</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>317348</v>
+        <v>317402</v>
       </c>
       <c r="R121" t="n">
-        <v>6550887</v>
+        <v>6550941</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14098,17 +14093,17 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14126,10 +14121,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130210757</v>
+        <v>130210752</v>
       </c>
       <c r="B122" t="n">
-        <v>75315</v>
+        <v>8451</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14137,34 +14132,39 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6426</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>317402</v>
+        <v>317348</v>
       </c>
       <c r="R122" t="n">
-        <v>6550941</v>
+        <v>6550887</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14210,17 +14210,17 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -14241,7 +14241,7 @@
         <v>130210773</v>
       </c>
       <c r="B123" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>130210767</v>
       </c>
       <c r="B124" t="n">
-        <v>97231</v>
+        <v>97232</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -9943,7 +9943,7 @@
         <v>130177344</v>
       </c>
       <c r="B84" t="n">
-        <v>97232</v>
+        <v>97233</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>130175755</v>
       </c>
       <c r="B85" t="n">
-        <v>92544</v>
+        <v>92545</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>130177191</v>
       </c>
       <c r="B86" t="n">
-        <v>97232</v>
+        <v>97233</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>130175870</v>
       </c>
       <c r="B87" t="n">
-        <v>92241</v>
+        <v>92242</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>130177180</v>
       </c>
       <c r="B88" t="n">
-        <v>97232</v>
+        <v>97233</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>130210763</v>
       </c>
       <c r="B90" t="n">
-        <v>97232</v>
+        <v>97233</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>130210762</v>
       </c>
       <c r="B91" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>130210782</v>
       </c>
       <c r="B92" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>130210783</v>
       </c>
       <c r="B93" t="n">
-        <v>97232</v>
+        <v>97233</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>130210766</v>
       </c>
       <c r="B94" t="n">
-        <v>97232</v>
+        <v>97233</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>130210755</v>
       </c>
       <c r="B95" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>130210781</v>
       </c>
       <c r="B96" t="n">
-        <v>97232</v>
+        <v>97233</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>130210758</v>
       </c>
       <c r="B97" t="n">
-        <v>97571</v>
+        <v>97572</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>130210765</v>
       </c>
       <c r="B98" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>130210787</v>
       </c>
       <c r="B101" t="n">
-        <v>97232</v>
+        <v>97233</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12531,32 +12531,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>130210756</v>
+        <v>130210780</v>
       </c>
       <c r="B107" t="n">
-        <v>91722</v>
+        <v>97197</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12566,10 +12566,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>317409</v>
+        <v>317275</v>
       </c>
       <c r="R107" t="n">
-        <v>6550951</v>
+        <v>6550801</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12615,17 +12615,17 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12643,10 +12643,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130210759</v>
+        <v>130210756</v>
       </c>
       <c r="B108" t="n">
-        <v>75315</v>
+        <v>91723</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12654,21 +12654,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12678,10 +12678,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>317390</v>
+        <v>317409</v>
       </c>
       <c r="R108" t="n">
-        <v>6550928</v>
+        <v>6550951</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12755,32 +12755,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130210780</v>
+        <v>130210759</v>
       </c>
       <c r="B109" t="n">
-        <v>97196</v>
+        <v>75315</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12790,10 +12790,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>317275</v>
+        <v>317390</v>
       </c>
       <c r="R109" t="n">
-        <v>6550801</v>
+        <v>6550928</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12839,17 +12839,17 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12867,32 +12867,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130210789</v>
+        <v>130210769</v>
       </c>
       <c r="B110" t="n">
-        <v>97232</v>
+        <v>97197</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12902,10 +12902,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>317326</v>
+        <v>317269</v>
       </c>
       <c r="R110" t="n">
-        <v>6550738</v>
+        <v>6550970</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12948,6 +12948,21 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
@@ -13081,32 +13096,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130210769</v>
+        <v>130210789</v>
       </c>
       <c r="B112" t="n">
-        <v>97196</v>
+        <v>97233</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13116,10 +13131,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>317269</v>
+        <v>317326</v>
       </c>
       <c r="R112" t="n">
-        <v>6550970</v>
+        <v>6550738</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13162,21 +13177,6 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
@@ -13193,32 +13193,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130210790</v>
+        <v>130210760</v>
       </c>
       <c r="B113" t="n">
-        <v>97232</v>
+        <v>97197</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13228,10 +13228,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>317336</v>
+        <v>317334</v>
       </c>
       <c r="R113" t="n">
-        <v>6550733</v>
+        <v>6550938</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13290,10 +13290,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130210764</v>
+        <v>130210790</v>
       </c>
       <c r="B114" t="n">
-        <v>97232</v>
+        <v>97233</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13325,10 +13325,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>317268</v>
+        <v>317336</v>
       </c>
       <c r="R114" t="n">
-        <v>6550998</v>
+        <v>6550733</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13387,10 +13387,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130210761</v>
+        <v>130210764</v>
       </c>
       <c r="B115" t="n">
-        <v>97232</v>
+        <v>97233</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13422,10 +13422,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>317337</v>
+        <v>317268</v>
       </c>
       <c r="R115" t="n">
-        <v>6550964</v>
+        <v>6550998</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13484,32 +13484,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130210760</v>
+        <v>130210761</v>
       </c>
       <c r="B116" t="n">
-        <v>97196</v>
+        <v>97233</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13519,10 +13519,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>317334</v>
+        <v>317337</v>
       </c>
       <c r="R116" t="n">
-        <v>6550938</v>
+        <v>6550964</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13581,10 +13581,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130210771</v>
+        <v>130210777</v>
       </c>
       <c r="B117" t="n">
-        <v>93040</v>
+        <v>8451</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13592,34 +13592,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>317240</v>
+        <v>317283</v>
       </c>
       <c r="R117" t="n">
-        <v>6550922</v>
+        <v>6550823</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13678,10 +13683,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130210777</v>
+        <v>130210771</v>
       </c>
       <c r="B118" t="n">
-        <v>8451</v>
+        <v>93041</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13689,39 +13694,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>317283</v>
+        <v>317240</v>
       </c>
       <c r="R118" t="n">
-        <v>6550823</v>
+        <v>6550922</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13897,32 +13897,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130210768</v>
+        <v>130210757</v>
       </c>
       <c r="B120" t="n">
-        <v>97196</v>
+        <v>75315</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13932,10 +13932,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>317274</v>
+        <v>317402</v>
       </c>
       <c r="R120" t="n">
-        <v>6550981</v>
+        <v>6550941</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13981,17 +13981,17 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -14009,32 +14009,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130210757</v>
+        <v>130210768</v>
       </c>
       <c r="B121" t="n">
-        <v>75315</v>
+        <v>97197</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14044,10 +14044,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>317402</v>
+        <v>317274</v>
       </c>
       <c r="R121" t="n">
-        <v>6550941</v>
+        <v>6550981</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14093,17 +14093,17 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14241,7 +14241,7 @@
         <v>130210773</v>
       </c>
       <c r="B123" t="n">
-        <v>93040</v>
+        <v>93041</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>130210767</v>
       </c>
       <c r="B124" t="n">
-        <v>97232</v>
+        <v>97233</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -9559,7 +9559,7 @@
         <v>130177928</v>
       </c>
       <c r="B81" t="n">
-        <v>75315</v>
+        <v>75317</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>130175963</v>
       </c>
       <c r="B82" t="n">
-        <v>78875</v>
+        <v>78877</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>130176280</v>
       </c>
       <c r="B83" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>130177344</v>
       </c>
       <c r="B84" t="n">
-        <v>97233</v>
+        <v>97235</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>130175755</v>
       </c>
       <c r="B85" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10187,38 +10187,41 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130177191</v>
+        <v>130175870</v>
       </c>
       <c r="B86" t="n">
-        <v>97233</v>
+        <v>92244</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2590</v>
+        <v>5467</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10226,10 +10229,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>317331</v>
+        <v>317429</v>
       </c>
       <c r="R86" t="n">
-        <v>6550757</v>
+        <v>6550919</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10276,7 +10279,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Blåbärgranskog</t>
+          <t>Moseblåbärgranskog</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -10309,41 +10312,38 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130175870</v>
+        <v>130177191</v>
       </c>
       <c r="B87" t="n">
-        <v>92242</v>
+        <v>97235</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5467</v>
+        <v>2590</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -10351,10 +10351,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>317429</v>
+        <v>317331</v>
       </c>
       <c r="R87" t="n">
-        <v>6550919</v>
+        <v>6550757</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Moseblåbärgranskog</t>
+          <t>Blåbärgranskog</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
@@ -10437,7 +10437,7 @@
         <v>130177180</v>
       </c>
       <c r="B88" t="n">
-        <v>97233</v>
+        <v>97235</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>130177708</v>
       </c>
       <c r="B89" t="n">
-        <v>75315</v>
+        <v>75317</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>130210763</v>
       </c>
       <c r="B90" t="n">
-        <v>97233</v>
+        <v>97235</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>130210762</v>
       </c>
       <c r="B91" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>130210782</v>
       </c>
       <c r="B92" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>130210783</v>
       </c>
       <c r="B93" t="n">
-        <v>97233</v>
+        <v>97235</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>130210766</v>
       </c>
       <c r="B94" t="n">
-        <v>97233</v>
+        <v>97235</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>130210755</v>
       </c>
       <c r="B95" t="n">
-        <v>91723</v>
+        <v>91725</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>130210781</v>
       </c>
       <c r="B96" t="n">
-        <v>97233</v>
+        <v>97235</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>130210758</v>
       </c>
       <c r="B97" t="n">
-        <v>97572</v>
+        <v>97574</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>130210765</v>
       </c>
       <c r="B98" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>130210778</v>
       </c>
       <c r="B99" t="n">
-        <v>44106</v>
+        <v>44108</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>130210753</v>
       </c>
       <c r="B100" t="n">
-        <v>75315</v>
+        <v>75317</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>130210787</v>
       </c>
       <c r="B101" t="n">
-        <v>97233</v>
+        <v>97235</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130210779</v>
+        <v>130210772</v>
       </c>
       <c r="B105" t="n">
         <v>8440</v>
@@ -12337,10 +12337,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>317266</v>
+        <v>317242</v>
       </c>
       <c r="R105" t="n">
-        <v>6550821</v>
+        <v>6550921</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12414,7 +12414,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130210772</v>
+        <v>130210779</v>
       </c>
       <c r="B106" t="n">
         <v>8440</v>
@@ -12454,10 +12454,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>317242</v>
+        <v>317266</v>
       </c>
       <c r="R106" t="n">
-        <v>6550921</v>
+        <v>6550821</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12534,7 +12534,7 @@
         <v>130210780</v>
       </c>
       <c r="B107" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12643,10 +12643,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130210756</v>
+        <v>130210759</v>
       </c>
       <c r="B108" t="n">
-        <v>91723</v>
+        <v>75317</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12654,21 +12654,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12678,10 +12678,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>317409</v>
+        <v>317390</v>
       </c>
       <c r="R108" t="n">
-        <v>6550951</v>
+        <v>6550928</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12755,10 +12755,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130210759</v>
+        <v>130210756</v>
       </c>
       <c r="B109" t="n">
-        <v>75315</v>
+        <v>91725</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12766,21 +12766,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12790,10 +12790,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>317390</v>
+        <v>317409</v>
       </c>
       <c r="R109" t="n">
-        <v>6550928</v>
+        <v>6550951</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12867,45 +12867,50 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130210769</v>
+        <v>130210770</v>
       </c>
       <c r="B110" t="n">
-        <v>97197</v>
+        <v>8451</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>317269</v>
+        <v>317245</v>
       </c>
       <c r="R110" t="n">
-        <v>6550970</v>
+        <v>6550930</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12979,50 +12984,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>130210770</v>
+        <v>130210769</v>
       </c>
       <c r="B111" t="n">
-        <v>8451</v>
+        <v>97199</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>317245</v>
+        <v>317269</v>
       </c>
       <c r="R111" t="n">
-        <v>6550930</v>
+        <v>6550970</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -13099,7 +13099,7 @@
         <v>130210789</v>
       </c>
       <c r="B112" t="n">
-        <v>97233</v>
+        <v>97235</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>130210760</v>
       </c>
       <c r="B113" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>130210790</v>
       </c>
       <c r="B114" t="n">
-        <v>97233</v>
+        <v>97235</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>130210764</v>
       </c>
       <c r="B115" t="n">
-        <v>97233</v>
+        <v>97235</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>130210761</v>
       </c>
       <c r="B116" t="n">
-        <v>97233</v>
+        <v>97235</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>130210771</v>
       </c>
       <c r="B118" t="n">
-        <v>93041</v>
+        <v>93043</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13897,32 +13897,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130210757</v>
+        <v>130210768</v>
       </c>
       <c r="B120" t="n">
-        <v>75315</v>
+        <v>97199</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13932,10 +13932,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>317402</v>
+        <v>317274</v>
       </c>
       <c r="R120" t="n">
-        <v>6550941</v>
+        <v>6550981</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13981,17 +13981,17 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -14009,32 +14009,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130210768</v>
+        <v>130210757</v>
       </c>
       <c r="B121" t="n">
-        <v>97197</v>
+        <v>75317</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14044,10 +14044,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>317274</v>
+        <v>317402</v>
       </c>
       <c r="R121" t="n">
-        <v>6550981</v>
+        <v>6550941</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14093,17 +14093,17 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14241,7 +14241,7 @@
         <v>130210773</v>
       </c>
       <c r="B123" t="n">
-        <v>93041</v>
+        <v>93043</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14335,10 +14335,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130210767</v>
+        <v>130210754</v>
       </c>
       <c r="B124" t="n">
-        <v>97233</v>
+        <v>75317</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14346,21 +14346,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14370,10 +14370,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>317271</v>
+        <v>317405</v>
       </c>
       <c r="R124" t="n">
-        <v>6550985</v>
+        <v>6550943</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14419,17 +14419,17 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -14447,10 +14447,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130210754</v>
+        <v>130210767</v>
       </c>
       <c r="B125" t="n">
-        <v>75315</v>
+        <v>97235</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14458,21 +14458,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14482,10 +14482,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>317405</v>
+        <v>317271</v>
       </c>
       <c r="R125" t="n">
-        <v>6550943</v>
+        <v>6550985</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14531,17 +14531,17 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -14562,7 +14562,7 @@
         <v>130177671</v>
       </c>
       <c r="B126" t="n">
-        <v>75315</v>
+        <v>75317</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -10684,7 +10684,7 @@
         <v>130210763</v>
       </c>
       <c r="B90" t="n">
-        <v>97235</v>
+        <v>97239</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>130210762</v>
       </c>
       <c r="B91" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>130210782</v>
       </c>
       <c r="B92" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10987,10 +10987,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130210783</v>
+        <v>130210755</v>
       </c>
       <c r="B93" t="n">
-        <v>97235</v>
+        <v>91725</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10998,21 +10998,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2590</v>
+        <v>5447</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11022,10 +11022,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>317282</v>
+        <v>317405</v>
       </c>
       <c r="R93" t="n">
-        <v>6550790</v>
+        <v>6550943</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11071,17 +11071,17 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11099,10 +11099,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130210766</v>
+        <v>130210783</v>
       </c>
       <c r="B94" t="n">
-        <v>97235</v>
+        <v>97239</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11134,10 +11134,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>317236</v>
+        <v>317282</v>
       </c>
       <c r="R94" t="n">
-        <v>6550997</v>
+        <v>6550790</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11180,6 +11180,21 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -11196,10 +11211,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130210755</v>
+        <v>130210766</v>
       </c>
       <c r="B95" t="n">
-        <v>91725</v>
+        <v>97239</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11207,21 +11222,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5447</v>
+        <v>2590</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11231,10 +11246,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>317405</v>
+        <v>317236</v>
       </c>
       <c r="R95" t="n">
-        <v>6550943</v>
+        <v>6550997</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11277,21 +11292,6 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -11311,7 +11311,7 @@
         <v>130210781</v>
       </c>
       <c r="B96" t="n">
-        <v>97235</v>
+        <v>97239</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>130210758</v>
       </c>
       <c r="B97" t="n">
-        <v>97574</v>
+        <v>97578</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>130210765</v>
       </c>
       <c r="B98" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>130210787</v>
       </c>
       <c r="B101" t="n">
-        <v>97235</v>
+        <v>97239</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130210772</v>
+        <v>130210779</v>
       </c>
       <c r="B105" t="n">
         <v>8440</v>
@@ -12337,10 +12337,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>317242</v>
+        <v>317266</v>
       </c>
       <c r="R105" t="n">
-        <v>6550921</v>
+        <v>6550821</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12414,7 +12414,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130210779</v>
+        <v>130210772</v>
       </c>
       <c r="B106" t="n">
         <v>8440</v>
@@ -12454,10 +12454,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>317266</v>
+        <v>317242</v>
       </c>
       <c r="R106" t="n">
-        <v>6550821</v>
+        <v>6550921</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12531,32 +12531,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>130210780</v>
+        <v>130210756</v>
       </c>
       <c r="B107" t="n">
-        <v>97199</v>
+        <v>91725</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12566,10 +12566,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>317275</v>
+        <v>317409</v>
       </c>
       <c r="R107" t="n">
-        <v>6550801</v>
+        <v>6550951</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12615,17 +12615,17 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12755,32 +12755,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130210756</v>
+        <v>130210780</v>
       </c>
       <c r="B109" t="n">
-        <v>91725</v>
+        <v>97203</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12790,10 +12790,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>317409</v>
+        <v>317275</v>
       </c>
       <c r="R109" t="n">
-        <v>6550951</v>
+        <v>6550801</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -12839,17 +12839,17 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12987,7 +12987,7 @@
         <v>130210769</v>
       </c>
       <c r="B111" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>130210789</v>
       </c>
       <c r="B112" t="n">
-        <v>97235</v>
+        <v>97239</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>130210760</v>
       </c>
       <c r="B113" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>130210790</v>
       </c>
       <c r="B114" t="n">
-        <v>97235</v>
+        <v>97239</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>130210764</v>
       </c>
       <c r="B115" t="n">
-        <v>97235</v>
+        <v>97239</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>130210761</v>
       </c>
       <c r="B116" t="n">
-        <v>97235</v>
+        <v>97239</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13581,10 +13581,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130210777</v>
+        <v>130210771</v>
       </c>
       <c r="B117" t="n">
-        <v>8451</v>
+        <v>93047</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13592,39 +13592,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>317283</v>
+        <v>317240</v>
       </c>
       <c r="R117" t="n">
-        <v>6550823</v>
+        <v>6550922</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -13683,10 +13678,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130210771</v>
+        <v>130210777</v>
       </c>
       <c r="B118" t="n">
-        <v>93043</v>
+        <v>8451</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13694,34 +13689,39 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>317240</v>
+        <v>317283</v>
       </c>
       <c r="R118" t="n">
-        <v>6550922</v>
+        <v>6550823</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13897,45 +13897,50 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130210768</v>
+        <v>130210752</v>
       </c>
       <c r="B120" t="n">
-        <v>97199</v>
+        <v>8451</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>317274</v>
+        <v>317348</v>
       </c>
       <c r="R120" t="n">
-        <v>6550981</v>
+        <v>6550887</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -14121,50 +14126,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130210752</v>
+        <v>130210768</v>
       </c>
       <c r="B122" t="n">
-        <v>8451</v>
+        <v>97203</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>317348</v>
+        <v>317274</v>
       </c>
       <c r="R122" t="n">
-        <v>6550887</v>
+        <v>6550981</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -14241,7 +14241,7 @@
         <v>130210773</v>
       </c>
       <c r="B123" t="n">
-        <v>93043</v>
+        <v>93047</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14335,10 +14335,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130210754</v>
+        <v>130210767</v>
       </c>
       <c r="B124" t="n">
-        <v>75317</v>
+        <v>97239</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14346,21 +14346,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14370,10 +14370,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>317405</v>
+        <v>317271</v>
       </c>
       <c r="R124" t="n">
-        <v>6550943</v>
+        <v>6550985</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -14419,17 +14419,17 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -14447,10 +14447,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130210767</v>
+        <v>130210754</v>
       </c>
       <c r="B125" t="n">
-        <v>97235</v>
+        <v>75317</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14458,21 +14458,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14482,10 +14482,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>317271</v>
+        <v>317405</v>
       </c>
       <c r="R125" t="n">
-        <v>6550985</v>
+        <v>6550943</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -14531,17 +14531,17 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -12531,10 +12531,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>130210756</v>
+        <v>130210759</v>
       </c>
       <c r="B107" t="n">
-        <v>91725</v>
+        <v>75317</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12542,21 +12542,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12566,10 +12566,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>317409</v>
+        <v>317390</v>
       </c>
       <c r="R107" t="n">
-        <v>6550951</v>
+        <v>6550928</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12643,10 +12643,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130210759</v>
+        <v>130210756</v>
       </c>
       <c r="B108" t="n">
-        <v>75317</v>
+        <v>91725</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12654,21 +12654,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12678,10 +12678,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>317390</v>
+        <v>317409</v>
       </c>
       <c r="R108" t="n">
-        <v>6550928</v>
+        <v>6550951</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12867,10 +12867,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130210770</v>
+        <v>130210789</v>
       </c>
       <c r="B110" t="n">
-        <v>8451</v>
+        <v>97239</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12878,39 +12878,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>317245</v>
+        <v>317326</v>
       </c>
       <c r="R110" t="n">
-        <v>6550930</v>
+        <v>6550738</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12953,21 +12948,6 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
@@ -13096,10 +13076,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130210789</v>
+        <v>130210770</v>
       </c>
       <c r="B112" t="n">
-        <v>97239</v>
+        <v>8451</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13107,34 +13087,39 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>317326</v>
+        <v>317245</v>
       </c>
       <c r="R112" t="n">
-        <v>6550738</v>
+        <v>6550930</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -13177,6 +13162,21 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
@@ -13193,32 +13193,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130210760</v>
+        <v>130210790</v>
       </c>
       <c r="B113" t="n">
-        <v>97203</v>
+        <v>97239</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13228,10 +13228,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>317334</v>
+        <v>317336</v>
       </c>
       <c r="R113" t="n">
-        <v>6550938</v>
+        <v>6550733</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -13290,7 +13290,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130210790</v>
+        <v>130210764</v>
       </c>
       <c r="B114" t="n">
         <v>97239</v>
@@ -13325,10 +13325,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>317336</v>
+        <v>317268</v>
       </c>
       <c r="R114" t="n">
-        <v>6550733</v>
+        <v>6550998</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -13387,7 +13387,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130210764</v>
+        <v>130210761</v>
       </c>
       <c r="B115" t="n">
         <v>97239</v>
@@ -13422,10 +13422,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>317268</v>
+        <v>317337</v>
       </c>
       <c r="R115" t="n">
-        <v>6550998</v>
+        <v>6550964</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13484,32 +13484,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130210761</v>
+        <v>130210760</v>
       </c>
       <c r="B116" t="n">
-        <v>97239</v>
+        <v>97203</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13519,10 +13519,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>317337</v>
+        <v>317334</v>
       </c>
       <c r="R116" t="n">
-        <v>6550964</v>
+        <v>6550938</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -13897,10 +13897,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130210752</v>
+        <v>130210757</v>
       </c>
       <c r="B120" t="n">
-        <v>8451</v>
+        <v>75317</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13908,39 +13908,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>6426</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>317348</v>
+        <v>317402</v>
       </c>
       <c r="R120" t="n">
-        <v>6550887</v>
+        <v>6550941</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13986,17 +13981,17 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -14014,32 +14009,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130210757</v>
+        <v>130210768</v>
       </c>
       <c r="B121" t="n">
-        <v>75317</v>
+        <v>97203</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14049,10 +14044,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>317402</v>
+        <v>317274</v>
       </c>
       <c r="R121" t="n">
-        <v>6550941</v>
+        <v>6550981</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -14098,17 +14093,17 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14126,45 +14121,50 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130210768</v>
+        <v>130210752</v>
       </c>
       <c r="B122" t="n">
-        <v>97203</v>
+        <v>8451</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>O om Pengehöljen, Dls</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>317274</v>
+        <v>317348</v>
       </c>
       <c r="R122" t="n">
-        <v>6550981</v>
+        <v>6550887</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -5351,7 +5351,7 @@
         <v>130063357</v>
       </c>
       <c r="B42" t="n">
-        <v>57016</v>
+        <v>57053</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY139"/>
+  <dimension ref="A1:AZ139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063319</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063337</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063344</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130072825</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210760</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210762</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210765</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1463,6 +1503,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210768</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,6 +1620,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210769</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210780</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1799,6 +1854,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210782</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1924,6 +1984,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129835977</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2049,6 +2114,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129607603</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2174,6 +2244,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130104411</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2299,6 +2374,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130104814</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2424,6 +2504,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130175963</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2536,6 +2621,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063343</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2661,6 +2751,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129607900</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2758,6 +2853,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129221379</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2883,6 +2983,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130175755</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2995,6 +3100,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129221369</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3120,6 +3230,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129605837</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3217,6 +3332,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063329</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3314,6 +3434,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063331</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3411,6 +3536,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210758</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3508,6 +3638,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129221371</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3605,6 +3740,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129221374</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3702,6 +3842,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063315</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3799,6 +3944,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063316</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3896,6 +4046,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063324</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3993,6 +4148,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063325</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4090,6 +4250,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063345</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4187,6 +4352,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063346</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4284,6 +4454,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063358</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4381,6 +4556,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063360</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4503,6 +4683,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177180</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4625,6 +4810,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177191</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4747,6 +4937,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177344</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4844,6 +5039,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210761</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4941,6 +5141,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210763</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5038,6 +5243,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210764</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5135,6 +5345,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210766</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5247,6 +5462,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210767</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5360,6 +5580,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210781</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5472,6 +5697,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210783</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5584,6 +5814,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210787</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5681,6 +5916,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210789</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5778,6 +6018,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210790</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5875,6 +6120,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129221368</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5972,6 +6222,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129221376</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6073,6 +6328,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063314</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6170,6 +6430,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063321</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6267,6 +6532,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063335</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6364,6 +6634,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063354</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6461,6 +6736,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063356</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6558,6 +6838,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210771</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6655,6 +6940,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210773</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6774,6 +7064,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129835851</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6886,6 +7181,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063326</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6998,6 +7298,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063330</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7110,6 +7415,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210755</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7222,6 +7532,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210756</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7347,6 +7662,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129607034</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7472,6 +7792,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130104706</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7602,6 +7927,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129605988</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7727,6 +8057,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129606816</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7852,6 +8187,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129606938</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7977,6 +8317,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130175870</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8102,6 +8447,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129606260</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8214,6 +8564,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063350</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8326,6 +8681,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063353</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8451,6 +8811,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129835991</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8548,6 +8913,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063323</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8645,6 +9015,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063332</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8742,6 +9117,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063336</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8854,6 +9234,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063338</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8966,6 +9351,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063347</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9078,6 +9468,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063348</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9190,6 +9585,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063351</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9315,6 +9715,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177671</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9440,6 +9845,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177708</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9565,6 +9975,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130177928</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9677,6 +10092,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210753</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9789,6 +10209,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210754</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9901,6 +10326,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210757</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10013,6 +10443,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210759</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10138,6 +10573,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129607723</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10263,6 +10703,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129654925</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10397,6 +10842,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130176248</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10531,6 +10981,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130176280</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10633,6 +11088,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063357</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10750,6 +11210,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063333</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10848,6 +11313,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063340</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10965,6 +11435,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063342</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11082,6 +11557,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129221372</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11199,6 +11679,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129835690</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11316,6 +11801,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129835710</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11443,6 +11933,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129835724</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11570,6 +12065,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129835737</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11697,6 +12197,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129835752</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11824,6 +12329,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129836107</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11951,6 +12461,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130175923</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12058,6 +12573,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210778</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12175,6 +12695,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130645364</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12292,6 +12817,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063327</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12409,6 +12939,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063334</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12526,6 +13061,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063339</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12643,6 +13183,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063341</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12760,6 +13305,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063352</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12877,6 +13427,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130645363</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12994,6 +13549,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129221370</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13111,6 +13671,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129221378</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13238,6 +13803,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129654794</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13365,6 +13935,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129835769</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13492,6 +14067,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129835778</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13619,6 +14199,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129835784</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13746,6 +14331,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129835794</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13873,6 +14463,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129835803</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14000,6 +14595,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129835810</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14127,6 +14727,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129835818</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14244,6 +14849,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063317</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14361,6 +14971,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063318</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14478,6 +15093,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063355</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14595,6 +15215,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210752</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14712,6 +15337,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210770</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14829,6 +15459,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210775</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14946,6 +15581,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210776</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15048,6 +15688,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210777</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15165,6 +15810,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210786</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15282,6 +15932,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210788</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15399,6 +16054,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129221367</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15526,6 +16186,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129835838</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15623,6 +16288,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063359</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15740,6 +16410,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210772</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15857,6 +16532,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210779</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15969,6 +16649,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063320</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16081,6 +16766,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063322</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16193,8 +16883,153 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130063328</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>